--- a/sensitivity_results/legacy/Resnet50_Correlation_matrices.xlsx
+++ b/sensitivity_results/legacy/Resnet50_Correlation_matrices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\ToGIT\Legacy\pearson_corelation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B42A89-3A54-4AF2-94DB-DC0FF6E5A065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4FA8AD-5B59-49D1-9CA3-7F02F58FFECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sensitivity" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="153">
   <si>
     <t>conv1_0.6</t>
   </si>
@@ -419,12 +419,94 @@
   <si>
     <t>Layerw4.2</t>
   </si>
+  <si>
+    <t>conv1</t>
+  </si>
+  <si>
+    <t>maxpool</t>
+  </si>
+  <si>
+    <t>layer1.0.conv1</t>
+  </si>
+  <si>
+    <t>layer1.0.conv2</t>
+  </si>
+  <si>
+    <t>layer1.0.conv3</t>
+  </si>
+  <si>
+    <t>layer1.0.downsample.0</t>
+  </si>
+  <si>
+    <t>layer1.1.conv1</t>
+  </si>
+  <si>
+    <t>layer1.2.conv1</t>
+  </si>
+  <si>
+    <t>layer1.2.conv2</t>
+  </si>
+  <si>
+    <t>layer1.2.conv3</t>
+  </si>
+  <si>
+    <t>layer2.0.conv1</t>
+  </si>
+  <si>
+    <t>layer2.0.conv3</t>
+  </si>
+  <si>
+    <t>layer2.0.downsample.0</t>
+  </si>
+  <si>
+    <t>layer2.1.conv1</t>
+  </si>
+  <si>
+    <t>layer2.1.conv2</t>
+  </si>
+  <si>
+    <t>layer2.2.conv2</t>
+  </si>
+  <si>
+    <t>layer2.3.conv3</t>
+  </si>
+  <si>
+    <t>layer3.0.conv1</t>
+  </si>
+  <si>
+    <t>layer3.1.conv2</t>
+  </si>
+  <si>
+    <t>layer3.2.conv2</t>
+  </si>
+  <si>
+    <t>layer3.2.conv3</t>
+  </si>
+  <si>
+    <t>layer3.5.conv1</t>
+  </si>
+  <si>
+    <t>layer3.5.conv2</t>
+  </si>
+  <si>
+    <t>layer4.2.conv3</t>
+  </si>
+  <si>
+    <t>Layer Name</t>
+  </si>
+  <si>
+    <t>Layer
+Index</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,6 +518,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -444,16 +527,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -476,22 +571,204 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -811,10 +1088,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5076939-FD7A-4490-AD6B-A59D0940C5AC}">
-  <dimension ref="A1:BD43"/>
+  <dimension ref="A1:BF109"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="21" bestFit="1" customWidth="1"/>
     <col min="51" max="53" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1715,437 +1992,437 @@
       <c r="A6" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <f>MIN(B2:B4)</f>
         <v>-3.9205289864607543E-2</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <f t="shared" ref="C6:R6" si="0">MIN(C2:C4)</f>
         <v>-0.20959560481224809</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <f t="shared" si="0"/>
         <v>-0.1673342218938704</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <f t="shared" si="0"/>
         <v>-9.8309841373890164E-2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <f t="shared" si="0"/>
         <v>-0.16027267316236959</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>-0.15163553369947641</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <f t="shared" si="0"/>
         <v>-1.2772903830628891E-2</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6">
         <f t="shared" si="0"/>
         <v>2.625153820569915E-2</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6">
         <f t="shared" si="0"/>
         <v>3.7408355533243093E-2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <f t="shared" si="0"/>
         <v>-7.533378168605627E-2</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <f t="shared" si="0"/>
         <v>-0.10181265361790599</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <f t="shared" si="0"/>
         <v>-8.7285287743320603E-2</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <f t="shared" si="0"/>
         <v>-4.486516237915144E-2</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6">
         <f t="shared" si="0"/>
         <v>3.2097520601861869E-3</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6">
         <f t="shared" si="0"/>
         <v>-5.376066942243958E-2</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <f t="shared" si="0"/>
         <v>-0.10357434500119531</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6">
         <f t="shared" si="0"/>
         <v>-7.0813725264993951E-2</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6">
         <f t="shared" ref="S6:BC6" si="1">MIN(S2:S4)</f>
         <v>-2.830569098078789E-2</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6">
         <f t="shared" si="1"/>
         <v>3.9943603255472172E-2</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U6">
         <f t="shared" si="1"/>
         <v>1.0792005263127751E-2</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6">
         <f t="shared" si="1"/>
         <v>-1.7361048567772371E-2</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6">
         <f t="shared" si="1"/>
         <v>0.1348923116212096</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6">
         <f t="shared" si="1"/>
         <v>3.5321533662841027E-2</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6">
         <f t="shared" si="1"/>
         <v>1.8907885139653659E-2</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6">
         <f t="shared" si="1"/>
         <v>-5.7978308235964879E-2</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6">
         <f t="shared" si="1"/>
         <v>-7.7467091417019587E-2</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AB6">
         <f t="shared" si="1"/>
         <v>5.9265450245938718E-2</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AC6">
         <f t="shared" si="1"/>
         <v>3.1094673211520759E-2</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AD6">
         <f t="shared" si="1"/>
         <v>0.1072523003189309</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AE6">
         <f t="shared" si="1"/>
         <v>0.1021002901160966</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AF6">
         <f t="shared" si="1"/>
         <v>-5.4600960981041639E-3</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AG6">
         <f t="shared" si="1"/>
         <v>8.8007125545544462E-2</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AH6">
         <f t="shared" si="1"/>
         <v>3.7974863953095427E-2</v>
       </c>
-      <c r="AI6" s="2">
+      <c r="AI6">
         <f t="shared" si="1"/>
         <v>-8.3604781198440489E-3</v>
       </c>
-      <c r="AJ6" s="2">
+      <c r="AJ6">
         <f t="shared" si="1"/>
         <v>-1.8975632400012151E-2</v>
       </c>
-      <c r="AK6" s="2">
+      <c r="AK6">
         <f t="shared" si="1"/>
         <v>9.1968497330287197E-2</v>
       </c>
-      <c r="AL6" s="2">
+      <c r="AL6">
         <f t="shared" si="1"/>
         <v>4.6970050037940213E-2</v>
       </c>
-      <c r="AM6" s="2">
+      <c r="AM6">
         <f t="shared" si="1"/>
         <v>0.13171131723969101</v>
       </c>
-      <c r="AN6" s="2">
+      <c r="AN6">
         <f t="shared" si="1"/>
         <v>2.6091947536313921E-2</v>
       </c>
-      <c r="AO6" s="2">
+      <c r="AO6">
         <f t="shared" si="1"/>
         <v>0.1554139787457629</v>
       </c>
-      <c r="AP6" s="2">
+      <c r="AP6">
         <f t="shared" si="1"/>
         <v>0.1479559136532527</v>
       </c>
-      <c r="AQ6" s="2">
+      <c r="AQ6">
         <f t="shared" si="1"/>
         <v>-6.312503013285356E-2</v>
       </c>
-      <c r="AR6" s="2">
+      <c r="AR6">
         <f t="shared" si="1"/>
         <v>-3.6011752676771251E-2</v>
       </c>
-      <c r="AS6" s="2">
+      <c r="AS6">
         <f t="shared" si="1"/>
         <v>8.3415716832728928E-2</v>
       </c>
-      <c r="AT6" s="2">
+      <c r="AT6">
         <f t="shared" si="1"/>
         <v>0.13430656450442921</v>
       </c>
-      <c r="AU6" s="2">
+      <c r="AU6">
         <f t="shared" si="1"/>
         <v>0.1080952975276763</v>
       </c>
-      <c r="AV6" s="2">
+      <c r="AV6">
         <f t="shared" si="1"/>
         <v>0.16240057842138439</v>
       </c>
-      <c r="AW6" s="2">
+      <c r="AW6">
         <f t="shared" si="1"/>
         <v>0.23755604846746151</v>
       </c>
-      <c r="AX6" s="2">
+      <c r="AX6">
         <f t="shared" si="1"/>
         <v>8.1312280633123499E-2</v>
       </c>
-      <c r="AY6" s="2">
+      <c r="AY6">
         <f t="shared" si="1"/>
         <v>9.374671678220764E-2</v>
       </c>
-      <c r="AZ6" s="2">
+      <c r="AZ6">
         <f t="shared" si="1"/>
         <v>0.17846821579833819</v>
       </c>
-      <c r="BA6" s="2">
+      <c r="BA6">
         <f t="shared" si="1"/>
         <v>0.27265719348865142</v>
       </c>
-      <c r="BB6" s="2">
+      <c r="BB6">
         <f t="shared" si="1"/>
         <v>8.000804492912815E-2</v>
       </c>
-      <c r="BC6" s="2">
+      <c r="BC6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:56" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="b">
+      <c r="B7" t="b">
         <f t="shared" ref="B7:R7" si="2">IF(AND(B2&gt;0,B3&gt;0,B4&gt;0),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="b">
+      <c r="C7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D7" s="2" t="b">
+      <c r="D7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="E7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="b">
+      <c r="F7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="b">
+      <c r="G7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="b">
+      <c r="H7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="b">
+      <c r="I7" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="b">
+      <c r="J7" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K7" s="2" t="b">
+      <c r="K7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="b">
+      <c r="L7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M7" s="2" t="b">
+      <c r="M7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N7" s="2" t="b">
+      <c r="N7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="b">
+      <c r="O7" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="P7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="2" t="b">
+      <c r="Q7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="b">
+      <c r="R7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S7" s="2" t="b">
+      <c r="S7" t="b">
         <f t="shared" ref="S7:BC7" si="3">IF(AND(S2&gt;0,S3&gt;0,S4&gt;0),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="b">
+      <c r="T7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="U7" s="2" t="b">
+      <c r="U7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="b">
+      <c r="V7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W7" s="2" t="b">
+      <c r="W7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X7" s="2" t="b">
+      <c r="X7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Y7" s="2" t="b">
+      <c r="Y7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="Z7" s="2" t="b">
+      <c r="Z7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA7" s="2" t="b">
+      <c r="AA7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB7" s="2" t="b">
+      <c r="AB7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AC7" s="2" t="b">
+      <c r="AC7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AD7" s="2" t="b">
+      <c r="AD7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AE7" s="2" t="b">
+      <c r="AE7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AF7" s="2" t="b">
+      <c r="AF7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG7" s="2" t="b">
+      <c r="AG7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AH7" s="2" t="b">
+      <c r="AH7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AI7" s="2" t="b">
+      <c r="AI7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AJ7" s="2" t="b">
+      <c r="AJ7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK7" s="2" t="b">
+      <c r="AK7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AL7" s="2" t="b">
+      <c r="AL7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AM7" s="2" t="b">
+      <c r="AM7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AN7" s="2" t="b">
+      <c r="AN7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AO7" s="2" t="b">
+      <c r="AO7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AP7" s="2" t="b">
+      <c r="AP7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AQ7" s="2" t="b">
+      <c r="AQ7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="2" t="b">
+      <c r="AR7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AS7" s="2" t="b">
+      <c r="AS7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AT7" s="2" t="b">
+      <c r="AT7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AU7" s="2" t="b">
+      <c r="AU7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AV7" s="2" t="b">
+      <c r="AV7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AW7" s="2" t="b">
+      <c r="AW7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AX7" s="2" t="b">
+      <c r="AX7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AY7" s="2" t="b">
+      <c r="AY7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AZ7" s="2" t="b">
+      <c r="AZ7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="BA7" s="2" t="b">
+      <c r="BA7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="BB7" s="2" t="b">
+      <c r="BB7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="BC7" s="2" t="b">
+      <c r="BC7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -2154,241 +2431,224 @@
       <c r="A8" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <f>MAX(B6:BB6)</f>
         <v>0.27265719348865142</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="2" t="b">
+      <c r="B9" t="b">
         <f>IF(OR(AND(B2&gt;0,B3&gt;0), AND(B2&gt;0,B4&gt;0), AND(B3&gt;0,B4&gt;0)), TRUE, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="2" t="b">
+      <c r="C9" t="b">
         <f t="shared" ref="C9:BB9" si="4">IF(OR(AND(C2&gt;0,C3&gt;0), AND(C2&gt;0,C4&gt;0), AND(C3&gt;0,C4&gt;0)), TRUE, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="b">
+      <c r="D9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="E9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="b">
+      <c r="F9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G9" s="2" t="b">
+      <c r="G9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H9" s="2" t="b">
+      <c r="H9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="b">
+      <c r="I9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="b">
+      <c r="J9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K9" s="2" t="b">
+      <c r="K9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="2" t="b">
+      <c r="L9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="2" t="b">
+      <c r="M9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="N9" s="2" t="b">
+      <c r="N9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O9" s="2" t="b">
+      <c r="O9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="P9" s="2" t="b">
+      <c r="P9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="2" t="b">
+      <c r="Q9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="R9" s="2" t="b">
+      <c r="R9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S9" s="2" t="b">
+      <c r="S9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="T9" s="2" t="b">
+      <c r="T9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="U9" s="2" t="b">
+      <c r="U9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="b">
+      <c r="V9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="b">
+      <c r="W9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="X9" s="2" t="b">
+      <c r="X9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="Y9" s="2" t="b">
+      <c r="Y9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="Z9" s="2" t="b">
+      <c r="Z9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AA9" s="2" t="b">
+      <c r="AA9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AB9" s="2" t="b">
+      <c r="AB9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AC9" s="2" t="b">
+      <c r="AC9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AD9" s="2" t="b">
+      <c r="AD9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AE9" s="2" t="b">
+      <c r="AE9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AF9" s="2" t="b">
+      <c r="AF9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AG9" s="2" t="b">
+      <c r="AG9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH9" s="2" t="b">
+      <c r="AH9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AI9" s="2" t="b">
+      <c r="AI9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AJ9" s="2" t="b">
+      <c r="AJ9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AK9" s="2" t="b">
+      <c r="AK9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AL9" s="2" t="b">
+      <c r="AL9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AM9" s="2" t="b">
+      <c r="AM9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AN9" s="2" t="b">
+      <c r="AN9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AO9" s="2" t="b">
+      <c r="AO9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AP9" s="2" t="b">
+      <c r="AP9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AQ9" s="2" t="b">
+      <c r="AQ9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AR9" s="2" t="b">
+      <c r="AR9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AS9" s="2" t="b">
+      <c r="AS9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AT9" s="2" t="b">
+      <c r="AT9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AU9" s="2" t="b">
+      <c r="AU9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AV9" s="2" t="b">
+      <c r="AV9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AW9" s="2" t="b">
+      <c r="AW9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AX9" s="2" t="b">
+      <c r="AX9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AY9" s="2" t="b">
+      <c r="AY9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AZ9" s="2" t="b">
+      <c r="AZ9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="BA9" s="2" t="b">
+      <c r="BA9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="BB9" s="2" t="b">
+      <c r="BB9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
@@ -2775,12 +3035,12 @@
       </c>
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>87</v>
       </c>
       <c r="Z40" t="s">
@@ -2788,7 +3048,7 @@
       </c>
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
       <c r="Z41" t="s">
@@ -2796,29 +3056,8173 @@
       </c>
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>90</v>
       </c>
+    </row>
+    <row r="53" spans="3:58" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="54" spans="3:58" ht="29" x14ac:dyDescent="0.35">
+      <c r="C54" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7">
+        <f>E54+1</f>
+        <v>2</v>
+      </c>
+      <c r="G54" s="7">
+        <f>F54+1</f>
+        <v>3</v>
+      </c>
+      <c r="H54" s="7">
+        <f>G54+1</f>
+        <v>4</v>
+      </c>
+      <c r="I54" s="7">
+        <f>H54+1</f>
+        <v>5</v>
+      </c>
+      <c r="J54" s="7">
+        <f>I54+1</f>
+        <v>6</v>
+      </c>
+      <c r="K54" s="7">
+        <f>J54+1</f>
+        <v>7</v>
+      </c>
+      <c r="L54" s="7">
+        <f>K54+1</f>
+        <v>8</v>
+      </c>
+      <c r="M54" s="7">
+        <f>L54+1</f>
+        <v>9</v>
+      </c>
+      <c r="N54" s="7">
+        <f>M54+1</f>
+        <v>10</v>
+      </c>
+      <c r="O54" s="7">
+        <f>N54+1</f>
+        <v>11</v>
+      </c>
+      <c r="P54" s="7">
+        <f>O54+1</f>
+        <v>12</v>
+      </c>
+      <c r="Q54" s="7">
+        <f>P54+1</f>
+        <v>13</v>
+      </c>
+      <c r="R54" s="7">
+        <f>Q54+1</f>
+        <v>14</v>
+      </c>
+      <c r="S54" s="7">
+        <f>R54+1</f>
+        <v>15</v>
+      </c>
+      <c r="T54" s="7">
+        <f>S54+1</f>
+        <v>16</v>
+      </c>
+      <c r="U54" s="7">
+        <f>T54+1</f>
+        <v>17</v>
+      </c>
+      <c r="V54" s="7">
+        <f>U54+1</f>
+        <v>18</v>
+      </c>
+      <c r="W54" s="7">
+        <f>V54+1</f>
+        <v>19</v>
+      </c>
+      <c r="X54" s="7">
+        <f>W54+1</f>
+        <v>20</v>
+      </c>
+      <c r="Y54" s="7">
+        <f>X54+1</f>
+        <v>21</v>
+      </c>
+      <c r="Z54" s="7">
+        <f>Y54+1</f>
+        <v>22</v>
+      </c>
+      <c r="AA54" s="7">
+        <f>Z54+1</f>
+        <v>23</v>
+      </c>
+      <c r="AB54" s="7">
+        <f>AA54+1</f>
+        <v>24</v>
+      </c>
+      <c r="AC54" s="7">
+        <f>AB54+1</f>
+        <v>25</v>
+      </c>
+      <c r="AD54" s="7">
+        <f>AC54+1</f>
+        <v>26</v>
+      </c>
+      <c r="AE54" s="7">
+        <f>AD54+1</f>
+        <v>27</v>
+      </c>
+      <c r="AF54" s="7">
+        <f>AE54+1</f>
+        <v>28</v>
+      </c>
+      <c r="AG54" s="7">
+        <f>AF54+1</f>
+        <v>29</v>
+      </c>
+      <c r="AH54" s="7">
+        <f>AG54+1</f>
+        <v>30</v>
+      </c>
+      <c r="AI54" s="7">
+        <f>AH54+1</f>
+        <v>31</v>
+      </c>
+      <c r="AJ54" s="7">
+        <f>AI54+1</f>
+        <v>32</v>
+      </c>
+      <c r="AK54" s="7">
+        <f>AJ54+1</f>
+        <v>33</v>
+      </c>
+      <c r="AL54" s="7">
+        <f>AK54+1</f>
+        <v>34</v>
+      </c>
+      <c r="AM54" s="7">
+        <f>AL54+1</f>
+        <v>35</v>
+      </c>
+      <c r="AN54" s="7">
+        <f>AM54+1</f>
+        <v>36</v>
+      </c>
+      <c r="AO54" s="7">
+        <f>AN54+1</f>
+        <v>37</v>
+      </c>
+      <c r="AP54" s="7">
+        <f>AO54+1</f>
+        <v>38</v>
+      </c>
+      <c r="AQ54" s="7">
+        <f>AP54+1</f>
+        <v>39</v>
+      </c>
+      <c r="AR54" s="7">
+        <f>AQ54+1</f>
+        <v>40</v>
+      </c>
+      <c r="AS54" s="7">
+        <f>AR54+1</f>
+        <v>41</v>
+      </c>
+      <c r="AT54" s="7">
+        <f>AS54+1</f>
+        <v>42</v>
+      </c>
+      <c r="AU54" s="7">
+        <f>AT54+1</f>
+        <v>43</v>
+      </c>
+      <c r="AV54" s="7">
+        <f>AU54+1</f>
+        <v>44</v>
+      </c>
+      <c r="AW54" s="7">
+        <f>AV54+1</f>
+        <v>45</v>
+      </c>
+      <c r="AX54" s="7">
+        <f>AW54+1</f>
+        <v>46</v>
+      </c>
+      <c r="AY54" s="7">
+        <f>AX54+1</f>
+        <v>47</v>
+      </c>
+      <c r="AZ54" s="7">
+        <f>AY54+1</f>
+        <v>48</v>
+      </c>
+      <c r="BA54" s="7">
+        <f>AZ54+1</f>
+        <v>49</v>
+      </c>
+      <c r="BB54" s="7">
+        <f>BA54+1</f>
+        <v>50</v>
+      </c>
+      <c r="BC54" s="7">
+        <f>BB54+1</f>
+        <v>51</v>
+      </c>
+      <c r="BD54" s="7">
+        <f>BC54+1</f>
+        <v>52</v>
+      </c>
+      <c r="BE54" s="7">
+        <f>BD54+1</f>
+        <v>53</v>
+      </c>
+      <c r="BF54" s="8">
+        <f>BE54+1</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C55" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="10">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4" t="str">
+        <f>IF(MIN(Class_0!B2,Class_1!B2,Class_2!B2) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+      <c r="T55" s="11"/>
+      <c r="U55" s="11"/>
+      <c r="V55" s="11"/>
+      <c r="W55" s="11"/>
+      <c r="X55" s="11"/>
+      <c r="Y55" s="11"/>
+      <c r="Z55" s="11"/>
+      <c r="AA55" s="11"/>
+      <c r="AB55" s="11"/>
+      <c r="AC55" s="11"/>
+      <c r="AD55" s="11"/>
+      <c r="AE55" s="11"/>
+      <c r="AF55" s="11"/>
+      <c r="AG55" s="11"/>
+      <c r="AH55" s="11"/>
+      <c r="AI55" s="11"/>
+      <c r="AJ55" s="11"/>
+      <c r="AK55" s="11"/>
+      <c r="AL55" s="11"/>
+      <c r="AM55" s="11"/>
+      <c r="AN55" s="11"/>
+      <c r="AO55" s="11"/>
+      <c r="AP55" s="11"/>
+      <c r="AQ55" s="11"/>
+      <c r="AR55" s="11"/>
+      <c r="AS55" s="11"/>
+      <c r="AT55" s="11"/>
+      <c r="AU55" s="11"/>
+      <c r="AV55" s="11"/>
+      <c r="AW55" s="11"/>
+      <c r="AX55" s="11"/>
+      <c r="AY55" s="11"/>
+      <c r="AZ55" s="11"/>
+      <c r="BA55" s="11"/>
+      <c r="BB55" s="11"/>
+      <c r="BC55" s="11"/>
+      <c r="BD55" s="11"/>
+      <c r="BE55" s="11"/>
+      <c r="BF55" s="12"/>
+    </row>
+    <row r="56" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C56" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" s="10">
+        <f>D55+1</f>
+        <v>2</v>
+      </c>
+      <c r="E56" s="14" t="str">
+        <f>IF(MIN(Class_0!B3,Class_1!B3,Class_2!B3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F56" s="14" t="str">
+        <f>IF(MIN(Class_0!C3,Class_1!C3,Class_2!C3) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+      <c r="P56" s="14"/>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="14"/>
+      <c r="V56" s="14"/>
+      <c r="W56" s="14"/>
+      <c r="X56" s="14"/>
+      <c r="Y56" s="14"/>
+      <c r="Z56" s="14"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="14"/>
+      <c r="AC56" s="14"/>
+      <c r="AD56" s="14"/>
+      <c r="AE56" s="14"/>
+      <c r="AF56" s="14"/>
+      <c r="AG56" s="14"/>
+      <c r="AH56" s="14"/>
+      <c r="AI56" s="14"/>
+      <c r="AJ56" s="14"/>
+      <c r="AK56" s="14"/>
+      <c r="AL56" s="14"/>
+      <c r="AM56" s="14"/>
+      <c r="AN56" s="14"/>
+      <c r="AO56" s="14"/>
+      <c r="AP56" s="14"/>
+      <c r="AQ56" s="14"/>
+      <c r="AR56" s="14"/>
+      <c r="AS56" s="14"/>
+      <c r="AT56" s="14"/>
+      <c r="AU56" s="14"/>
+      <c r="AV56" s="14"/>
+      <c r="AW56" s="14"/>
+      <c r="AX56" s="14"/>
+      <c r="AY56" s="14"/>
+      <c r="AZ56" s="14"/>
+      <c r="BA56" s="14"/>
+      <c r="BB56" s="14"/>
+      <c r="BC56" s="14"/>
+      <c r="BD56" s="14"/>
+      <c r="BE56" s="14"/>
+      <c r="BF56" s="15"/>
+    </row>
+    <row r="57" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C57" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" s="10">
+        <f t="shared" ref="D57:D108" si="6">D56+1</f>
+        <v>3</v>
+      </c>
+      <c r="E57" s="14" t="str">
+        <f>IF(MIN(Class_0!B4,Class_1!B4,Class_2!B4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F57" s="14" t="str">
+        <f>IF(MIN(Class_0!C4,Class_1!C4,Class_2!C4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G57" s="14" t="str">
+        <f>IF(MIN(Class_0!D4,Class_1!D4,Class_2!D4) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
+      <c r="P57" s="14"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
+      <c r="V57" s="14"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="14"/>
+      <c r="Y57" s="14"/>
+      <c r="Z57" s="14"/>
+      <c r="AA57" s="14"/>
+      <c r="AB57" s="14"/>
+      <c r="AC57" s="14"/>
+      <c r="AD57" s="14"/>
+      <c r="AE57" s="14"/>
+      <c r="AF57" s="14"/>
+      <c r="AG57" s="14"/>
+      <c r="AH57" s="14"/>
+      <c r="AI57" s="14"/>
+      <c r="AJ57" s="14"/>
+      <c r="AK57" s="14"/>
+      <c r="AL57" s="14"/>
+      <c r="AM57" s="14"/>
+      <c r="AN57" s="14"/>
+      <c r="AO57" s="14"/>
+      <c r="AP57" s="14"/>
+      <c r="AQ57" s="14"/>
+      <c r="AR57" s="14"/>
+      <c r="AS57" s="14"/>
+      <c r="AT57" s="14"/>
+      <c r="AU57" s="14"/>
+      <c r="AV57" s="14"/>
+      <c r="AW57" s="14"/>
+      <c r="AX57" s="14"/>
+      <c r="AY57" s="14"/>
+      <c r="AZ57" s="14"/>
+      <c r="BA57" s="14"/>
+      <c r="BB57" s="14"/>
+      <c r="BC57" s="14"/>
+      <c r="BD57" s="14"/>
+      <c r="BE57" s="14"/>
+      <c r="BF57" s="15"/>
+    </row>
+    <row r="58" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C58" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="10">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="E58" s="14" t="str">
+        <f>IF(MIN(Class_0!B5,Class_1!B5,Class_2!B5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F58" s="14" t="str">
+        <f>IF(MIN(Class_0!C5,Class_1!C5,Class_2!C5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G58" s="14" t="str">
+        <f>IF(MIN(Class_0!D5,Class_1!D5,Class_2!D5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H58" s="14" t="str">
+        <f>IF(MIN(Class_0!E5,Class_1!E5,Class_2!E5) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
+      <c r="O58" s="14"/>
+      <c r="P58" s="14"/>
+      <c r="Q58" s="14"/>
+      <c r="R58" s="14"/>
+      <c r="S58" s="14"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="14"/>
+      <c r="V58" s="14"/>
+      <c r="W58" s="14"/>
+      <c r="X58" s="14"/>
+      <c r="Y58" s="14"/>
+      <c r="Z58" s="14"/>
+      <c r="AA58" s="14"/>
+      <c r="AB58" s="14"/>
+      <c r="AC58" s="14"/>
+      <c r="AD58" s="14"/>
+      <c r="AE58" s="14"/>
+      <c r="AF58" s="14"/>
+      <c r="AG58" s="14"/>
+      <c r="AH58" s="14"/>
+      <c r="AI58" s="14"/>
+      <c r="AJ58" s="14"/>
+      <c r="AK58" s="14"/>
+      <c r="AL58" s="14"/>
+      <c r="AM58" s="14"/>
+      <c r="AN58" s="14"/>
+      <c r="AO58" s="14"/>
+      <c r="AP58" s="14"/>
+      <c r="AQ58" s="14"/>
+      <c r="AR58" s="14"/>
+      <c r="AS58" s="14"/>
+      <c r="AT58" s="14"/>
+      <c r="AU58" s="14"/>
+      <c r="AV58" s="14"/>
+      <c r="AW58" s="14"/>
+      <c r="AX58" s="14"/>
+      <c r="AY58" s="14"/>
+      <c r="AZ58" s="14"/>
+      <c r="BA58" s="14"/>
+      <c r="BB58" s="14"/>
+      <c r="BC58" s="14"/>
+      <c r="BD58" s="14"/>
+      <c r="BE58" s="14"/>
+      <c r="BF58" s="15"/>
+    </row>
+    <row r="59" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C59" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" s="10">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="E59" s="14" t="str">
+        <f>IF(MIN(Class_0!B6,Class_1!B6,Class_2!B6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F59" s="14" t="str">
+        <f>IF(MIN(Class_0!C6,Class_1!C6,Class_2!C6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G59" s="14" t="str">
+        <f>IF(MIN(Class_0!D6,Class_1!D6,Class_2!D6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H59" s="14" t="str">
+        <f>IF(MIN(Class_0!E6,Class_1!E6,Class_2!E6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I59" s="14" t="str">
+        <f>IF(MIN(Class_0!F6,Class_1!F6,Class_2!F6) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
+      <c r="P59" s="14"/>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="14"/>
+      <c r="V59" s="14"/>
+      <c r="W59" s="14"/>
+      <c r="X59" s="14"/>
+      <c r="Y59" s="14"/>
+      <c r="Z59" s="14"/>
+      <c r="AA59" s="14"/>
+      <c r="AB59" s="14"/>
+      <c r="AC59" s="14"/>
+      <c r="AD59" s="14"/>
+      <c r="AE59" s="14"/>
+      <c r="AF59" s="14"/>
+      <c r="AG59" s="14"/>
+      <c r="AH59" s="14"/>
+      <c r="AI59" s="14"/>
+      <c r="AJ59" s="14"/>
+      <c r="AK59" s="14"/>
+      <c r="AL59" s="14"/>
+      <c r="AM59" s="14"/>
+      <c r="AN59" s="14"/>
+      <c r="AO59" s="14"/>
+      <c r="AP59" s="14"/>
+      <c r="AQ59" s="14"/>
+      <c r="AR59" s="14"/>
+      <c r="AS59" s="14"/>
+      <c r="AT59" s="14"/>
+      <c r="AU59" s="14"/>
+      <c r="AV59" s="14"/>
+      <c r="AW59" s="14"/>
+      <c r="AX59" s="14"/>
+      <c r="AY59" s="14"/>
+      <c r="AZ59" s="14"/>
+      <c r="BA59" s="14"/>
+      <c r="BB59" s="14"/>
+      <c r="BC59" s="14"/>
+      <c r="BD59" s="14"/>
+      <c r="BE59" s="14"/>
+      <c r="BF59" s="15"/>
+    </row>
+    <row r="60" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C60" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" s="10">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="E60" s="14" t="str">
+        <f>IF(MIN(Class_0!B7,Class_1!B7,Class_2!B7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F60" s="14" t="str">
+        <f>IF(MIN(Class_0!C7,Class_1!C7,Class_2!C7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G60" s="14" t="str">
+        <f>IF(MIN(Class_0!D7,Class_1!D7,Class_2!D7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H60" s="14" t="str">
+        <f>IF(MIN(Class_0!E7,Class_1!E7,Class_2!E7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I60" s="14" t="str">
+        <f>IF(MIN(Class_0!F7,Class_1!F7,Class_2!F7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J60" s="14" t="str">
+        <f>IF(MIN(Class_0!G7,Class_1!G7,Class_2!G7) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="14"/>
+      <c r="S60" s="14"/>
+      <c r="T60" s="14"/>
+      <c r="U60" s="14"/>
+      <c r="V60" s="14"/>
+      <c r="W60" s="14"/>
+      <c r="X60" s="14"/>
+      <c r="Y60" s="14"/>
+      <c r="Z60" s="14"/>
+      <c r="AA60" s="14"/>
+      <c r="AB60" s="14"/>
+      <c r="AC60" s="14"/>
+      <c r="AD60" s="14"/>
+      <c r="AE60" s="14"/>
+      <c r="AF60" s="14"/>
+      <c r="AG60" s="14"/>
+      <c r="AH60" s="14"/>
+      <c r="AI60" s="14"/>
+      <c r="AJ60" s="14"/>
+      <c r="AK60" s="14"/>
+      <c r="AL60" s="14"/>
+      <c r="AM60" s="14"/>
+      <c r="AN60" s="14"/>
+      <c r="AO60" s="14"/>
+      <c r="AP60" s="14"/>
+      <c r="AQ60" s="14"/>
+      <c r="AR60" s="14"/>
+      <c r="AS60" s="14"/>
+      <c r="AT60" s="14"/>
+      <c r="AU60" s="14"/>
+      <c r="AV60" s="14"/>
+      <c r="AW60" s="14"/>
+      <c r="AX60" s="14"/>
+      <c r="AY60" s="14"/>
+      <c r="AZ60" s="14"/>
+      <c r="BA60" s="14"/>
+      <c r="BB60" s="14"/>
+      <c r="BC60" s="14"/>
+      <c r="BD60" s="14"/>
+      <c r="BE60" s="14"/>
+      <c r="BF60" s="15"/>
+    </row>
+    <row r="61" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C61" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D61" s="10">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="E61" s="14" t="str">
+        <f>IF(MIN(Class_0!B8,Class_1!B8,Class_2!B8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F61" s="14" t="str">
+        <f>IF(MIN(Class_0!C8,Class_1!C8,Class_2!C8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G61" s="14" t="str">
+        <f>IF(MIN(Class_0!D8,Class_1!D8,Class_2!D8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H61" s="14" t="str">
+        <f>IF(MIN(Class_0!E8,Class_1!E8,Class_2!E8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I61" s="14" t="str">
+        <f>IF(MIN(Class_0!F8,Class_1!F8,Class_2!F8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J61" s="14" t="str">
+        <f>IF(MIN(Class_0!G8,Class_1!G8,Class_2!G8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K61" s="14" t="str">
+        <f>IF(MIN(Class_0!H8,Class_1!H8,Class_2!H8) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
+      <c r="O61" s="14"/>
+      <c r="P61" s="14"/>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="14"/>
+      <c r="S61" s="14"/>
+      <c r="T61" s="14"/>
+      <c r="U61" s="14"/>
+      <c r="V61" s="14"/>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
+      <c r="Y61" s="14"/>
+      <c r="Z61" s="14"/>
+      <c r="AA61" s="14"/>
+      <c r="AB61" s="14"/>
+      <c r="AC61" s="14"/>
+      <c r="AD61" s="14"/>
+      <c r="AE61" s="14"/>
+      <c r="AF61" s="14"/>
+      <c r="AG61" s="14"/>
+      <c r="AH61" s="14"/>
+      <c r="AI61" s="14"/>
+      <c r="AJ61" s="14"/>
+      <c r="AK61" s="14"/>
+      <c r="AL61" s="14"/>
+      <c r="AM61" s="14"/>
+      <c r="AN61" s="14"/>
+      <c r="AO61" s="14"/>
+      <c r="AP61" s="14"/>
+      <c r="AQ61" s="14"/>
+      <c r="AR61" s="14"/>
+      <c r="AS61" s="14"/>
+      <c r="AT61" s="14"/>
+      <c r="AU61" s="14"/>
+      <c r="AV61" s="14"/>
+      <c r="AW61" s="14"/>
+      <c r="AX61" s="14"/>
+      <c r="AY61" s="14"/>
+      <c r="AZ61" s="14"/>
+      <c r="BA61" s="14"/>
+      <c r="BB61" s="14"/>
+      <c r="BC61" s="14"/>
+      <c r="BD61" s="14"/>
+      <c r="BE61" s="14"/>
+      <c r="BF61" s="15"/>
+    </row>
+    <row r="62" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C62" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" s="10">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E62" s="14" t="str">
+        <f>IF(MIN(Class_0!B9,Class_1!B9,Class_2!B9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F62" s="14" t="str">
+        <f>IF(MIN(Class_0!C9,Class_1!C9,Class_2!C9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G62" s="14" t="str">
+        <f>IF(MIN(Class_0!D9,Class_1!D9,Class_2!D9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H62" s="14" t="str">
+        <f>IF(MIN(Class_0!E9,Class_1!E9,Class_2!E9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I62" s="14" t="str">
+        <f>IF(MIN(Class_0!F9,Class_1!F9,Class_2!F9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J62" s="14" t="str">
+        <f>IF(MIN(Class_0!G9,Class_1!G9,Class_2!G9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K62" s="14" t="str">
+        <f>IF(MIN(Class_0!H9,Class_1!H9,Class_2!H9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L62" s="14" t="str">
+        <f>IF(MIN(Class_0!I9,Class_1!I9,Class_2!I9) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="14"/>
+      <c r="P62" s="14"/>
+      <c r="Q62" s="14"/>
+      <c r="R62" s="14"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="14"/>
+      <c r="V62" s="14"/>
+      <c r="W62" s="14"/>
+      <c r="X62" s="14"/>
+      <c r="Y62" s="14"/>
+      <c r="Z62" s="14"/>
+      <c r="AA62" s="14"/>
+      <c r="AB62" s="14"/>
+      <c r="AC62" s="14"/>
+      <c r="AD62" s="14"/>
+      <c r="AE62" s="14"/>
+      <c r="AF62" s="14"/>
+      <c r="AG62" s="14"/>
+      <c r="AH62" s="14"/>
+      <c r="AI62" s="14"/>
+      <c r="AJ62" s="14"/>
+      <c r="AK62" s="14"/>
+      <c r="AL62" s="14"/>
+      <c r="AM62" s="14"/>
+      <c r="AN62" s="14"/>
+      <c r="AO62" s="14"/>
+      <c r="AP62" s="14"/>
+      <c r="AQ62" s="14"/>
+      <c r="AR62" s="14"/>
+      <c r="AS62" s="14"/>
+      <c r="AT62" s="14"/>
+      <c r="AU62" s="14"/>
+      <c r="AV62" s="14"/>
+      <c r="AW62" s="14"/>
+      <c r="AX62" s="14"/>
+      <c r="AY62" s="14"/>
+      <c r="AZ62" s="14"/>
+      <c r="BA62" s="14"/>
+      <c r="BB62" s="14"/>
+      <c r="BC62" s="14"/>
+      <c r="BD62" s="14"/>
+      <c r="BE62" s="14"/>
+      <c r="BF62" s="15"/>
+    </row>
+    <row r="63" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C63" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" s="10">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="E63" s="14" t="str">
+        <f>IF(MIN(Class_0!B10,Class_1!B10,Class_2!B10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F63" s="14" t="str">
+        <f>IF(MIN(Class_0!C10,Class_1!C10,Class_2!C10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G63" s="14" t="str">
+        <f>IF(MIN(Class_0!D10,Class_1!D10,Class_2!D10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H63" s="14" t="str">
+        <f>IF(MIN(Class_0!E10,Class_1!E10,Class_2!E10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I63" s="14" t="str">
+        <f>IF(MIN(Class_0!F10,Class_1!F10,Class_2!F10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J63" s="14" t="str">
+        <f>IF(MIN(Class_0!G10,Class_1!G10,Class_2!G10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K63" s="14" t="str">
+        <f>IF(MIN(Class_0!H10,Class_1!H10,Class_2!H10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L63" s="14" t="str">
+        <f>IF(MIN(Class_0!I10,Class_1!I10,Class_2!I10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M63" s="14" t="str">
+        <f>IF(MIN(Class_0!J10,Class_1!J10,Class_2!J10) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
+      <c r="Y63" s="14"/>
+      <c r="Z63" s="14"/>
+      <c r="AA63" s="14"/>
+      <c r="AB63" s="14"/>
+      <c r="AC63" s="14"/>
+      <c r="AD63" s="14"/>
+      <c r="AE63" s="14"/>
+      <c r="AF63" s="14"/>
+      <c r="AG63" s="14"/>
+      <c r="AH63" s="14"/>
+      <c r="AI63" s="14"/>
+      <c r="AJ63" s="14"/>
+      <c r="AK63" s="14"/>
+      <c r="AL63" s="14"/>
+      <c r="AM63" s="14"/>
+      <c r="AN63" s="14"/>
+      <c r="AO63" s="14"/>
+      <c r="AP63" s="14"/>
+      <c r="AQ63" s="14"/>
+      <c r="AR63" s="14"/>
+      <c r="AS63" s="14"/>
+      <c r="AT63" s="14"/>
+      <c r="AU63" s="14"/>
+      <c r="AV63" s="14"/>
+      <c r="AW63" s="14"/>
+      <c r="AX63" s="14"/>
+      <c r="AY63" s="14"/>
+      <c r="AZ63" s="14"/>
+      <c r="BA63" s="14"/>
+      <c r="BB63" s="14"/>
+      <c r="BC63" s="14"/>
+      <c r="BD63" s="14"/>
+      <c r="BE63" s="14"/>
+      <c r="BF63" s="15"/>
+    </row>
+    <row r="64" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C64" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D64" s="10">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="E64" s="14" t="str">
+        <f>IF(MIN(Class_0!B11,Class_1!B11,Class_2!B11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F64" s="14" t="str">
+        <f>IF(MIN(Class_0!C11,Class_1!C11,Class_2!C11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G64" s="14" t="str">
+        <f>IF(MIN(Class_0!D11,Class_1!D11,Class_2!D11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H64" s="14" t="str">
+        <f>IF(MIN(Class_0!E11,Class_1!E11,Class_2!E11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I64" s="14" t="str">
+        <f>IF(MIN(Class_0!F11,Class_1!F11,Class_2!F11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J64" s="14" t="str">
+        <f>IF(MIN(Class_0!G11,Class_1!G11,Class_2!G11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K64" s="14" t="str">
+        <f>IF(MIN(Class_0!H11,Class_1!H11,Class_2!H11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L64" s="14" t="str">
+        <f>IF(MIN(Class_0!I11,Class_1!I11,Class_2!I11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M64" s="14" t="str">
+        <f>IF(MIN(Class_0!J11,Class_1!J11,Class_2!J11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N64" s="14" t="str">
+        <f>IF(MIN(Class_0!K11,Class_1!K11,Class_2!K11) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O64" s="14"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="14"/>
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="14"/>
+      <c r="V64" s="14"/>
+      <c r="W64" s="14"/>
+      <c r="X64" s="14"/>
+      <c r="Y64" s="14"/>
+      <c r="Z64" s="14"/>
+      <c r="AA64" s="14"/>
+      <c r="AB64" s="14"/>
+      <c r="AC64" s="14"/>
+      <c r="AD64" s="14"/>
+      <c r="AE64" s="14"/>
+      <c r="AF64" s="14"/>
+      <c r="AG64" s="14"/>
+      <c r="AH64" s="14"/>
+      <c r="AI64" s="14"/>
+      <c r="AJ64" s="14"/>
+      <c r="AK64" s="14"/>
+      <c r="AL64" s="14"/>
+      <c r="AM64" s="14"/>
+      <c r="AN64" s="14"/>
+      <c r="AO64" s="14"/>
+      <c r="AP64" s="14"/>
+      <c r="AQ64" s="14"/>
+      <c r="AR64" s="14"/>
+      <c r="AS64" s="14"/>
+      <c r="AT64" s="14"/>
+      <c r="AU64" s="14"/>
+      <c r="AV64" s="14"/>
+      <c r="AW64" s="14"/>
+      <c r="AX64" s="14"/>
+      <c r="AY64" s="14"/>
+      <c r="AZ64" s="14"/>
+      <c r="BA64" s="14"/>
+      <c r="BB64" s="14"/>
+      <c r="BC64" s="14"/>
+      <c r="BD64" s="14"/>
+      <c r="BE64" s="14"/>
+      <c r="BF64" s="15"/>
+    </row>
+    <row r="65" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C65" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="10">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="E65" s="14" t="str">
+        <f>IF(MIN(Class_0!B12,Class_1!B12,Class_2!B12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F65" s="14" t="str">
+        <f>IF(MIN(Class_0!C12,Class_1!C12,Class_2!C12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G65" s="14" t="str">
+        <f>IF(MIN(Class_0!D12,Class_1!D12,Class_2!D12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H65" s="14" t="str">
+        <f>IF(MIN(Class_0!E12,Class_1!E12,Class_2!E12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I65" s="14" t="str">
+        <f>IF(MIN(Class_0!F12,Class_1!F12,Class_2!F12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J65" s="14" t="str">
+        <f>IF(MIN(Class_0!G12,Class_1!G12,Class_2!G12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K65" s="14" t="str">
+        <f>IF(MIN(Class_0!H12,Class_1!H12,Class_2!H12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L65" s="14" t="str">
+        <f>IF(MIN(Class_0!I12,Class_1!I12,Class_2!I12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M65" s="14" t="str">
+        <f>IF(MIN(Class_0!J12,Class_1!J12,Class_2!J12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N65" s="14" t="str">
+        <f>IF(MIN(Class_0!K12,Class_1!K12,Class_2!K12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O65" s="14" t="str">
+        <f>IF(MIN(Class_0!L12,Class_1!L12,Class_2!L12) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P65" s="14"/>
+      <c r="Q65" s="14"/>
+      <c r="R65" s="14"/>
+      <c r="S65" s="14"/>
+      <c r="T65" s="14"/>
+      <c r="U65" s="14"/>
+      <c r="V65" s="14"/>
+      <c r="W65" s="14"/>
+      <c r="X65" s="14"/>
+      <c r="Y65" s="14"/>
+      <c r="Z65" s="14"/>
+      <c r="AA65" s="14"/>
+      <c r="AB65" s="14"/>
+      <c r="AC65" s="14"/>
+      <c r="AD65" s="14"/>
+      <c r="AE65" s="14"/>
+      <c r="AF65" s="14"/>
+      <c r="AG65" s="14"/>
+      <c r="AH65" s="14"/>
+      <c r="AI65" s="14"/>
+      <c r="AJ65" s="14"/>
+      <c r="AK65" s="14"/>
+      <c r="AL65" s="14"/>
+      <c r="AM65" s="14"/>
+      <c r="AN65" s="14"/>
+      <c r="AO65" s="14"/>
+      <c r="AP65" s="14"/>
+      <c r="AQ65" s="14"/>
+      <c r="AR65" s="14"/>
+      <c r="AS65" s="14"/>
+      <c r="AT65" s="14"/>
+      <c r="AU65" s="14"/>
+      <c r="AV65" s="14"/>
+      <c r="AW65" s="14"/>
+      <c r="AX65" s="14"/>
+      <c r="AY65" s="14"/>
+      <c r="AZ65" s="14"/>
+      <c r="BA65" s="14"/>
+      <c r="BB65" s="14"/>
+      <c r="BC65" s="14"/>
+      <c r="BD65" s="14"/>
+      <c r="BE65" s="14"/>
+      <c r="BF65" s="15"/>
+    </row>
+    <row r="66" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C66" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D66" s="10">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="E66" s="14" t="str">
+        <f>IF(MIN(Class_0!B13,Class_1!B13,Class_2!B13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F66" s="14" t="str">
+        <f>IF(MIN(Class_0!C13,Class_1!C13,Class_2!C13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G66" s="14" t="str">
+        <f>IF(MIN(Class_0!D13,Class_1!D13,Class_2!D13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H66" s="14" t="str">
+        <f>IF(MIN(Class_0!E13,Class_1!E13,Class_2!E13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I66" s="14" t="str">
+        <f>IF(MIN(Class_0!F13,Class_1!F13,Class_2!F13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J66" s="14" t="str">
+        <f>IF(MIN(Class_0!G13,Class_1!G13,Class_2!G13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K66" s="14" t="str">
+        <f>IF(MIN(Class_0!H13,Class_1!H13,Class_2!H13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L66" s="14" t="str">
+        <f>IF(MIN(Class_0!I13,Class_1!I13,Class_2!I13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M66" s="14" t="str">
+        <f>IF(MIN(Class_0!J13,Class_1!J13,Class_2!J13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N66" s="14" t="str">
+        <f>IF(MIN(Class_0!K13,Class_1!K13,Class_2!K13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O66" s="14" t="str">
+        <f>IF(MIN(Class_0!L13,Class_1!L13,Class_2!L13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P66" s="14" t="str">
+        <f>IF(MIN(Class_0!M13,Class_1!M13,Class_2!M13) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q66" s="14"/>
+      <c r="R66" s="14"/>
+      <c r="S66" s="14"/>
+      <c r="T66" s="14"/>
+      <c r="U66" s="14"/>
+      <c r="V66" s="14"/>
+      <c r="W66" s="14"/>
+      <c r="X66" s="14"/>
+      <c r="Y66" s="14"/>
+      <c r="Z66" s="14"/>
+      <c r="AA66" s="14"/>
+      <c r="AB66" s="14"/>
+      <c r="AC66" s="14"/>
+      <c r="AD66" s="14"/>
+      <c r="AE66" s="14"/>
+      <c r="AF66" s="14"/>
+      <c r="AG66" s="14"/>
+      <c r="AH66" s="14"/>
+      <c r="AI66" s="14"/>
+      <c r="AJ66" s="14"/>
+      <c r="AK66" s="14"/>
+      <c r="AL66" s="14"/>
+      <c r="AM66" s="14"/>
+      <c r="AN66" s="14"/>
+      <c r="AO66" s="14"/>
+      <c r="AP66" s="14"/>
+      <c r="AQ66" s="14"/>
+      <c r="AR66" s="14"/>
+      <c r="AS66" s="14"/>
+      <c r="AT66" s="14"/>
+      <c r="AU66" s="14"/>
+      <c r="AV66" s="14"/>
+      <c r="AW66" s="14"/>
+      <c r="AX66" s="14"/>
+      <c r="AY66" s="14"/>
+      <c r="AZ66" s="14"/>
+      <c r="BA66" s="14"/>
+      <c r="BB66" s="14"/>
+      <c r="BC66" s="14"/>
+      <c r="BD66" s="14"/>
+      <c r="BE66" s="14"/>
+      <c r="BF66" s="15"/>
+    </row>
+    <row r="67" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C67" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D67" s="10">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="E67" s="14" t="str">
+        <f>IF(MIN(Class_0!B14,Class_1!B14,Class_2!B14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F67" s="14" t="str">
+        <f>IF(MIN(Class_0!C14,Class_1!C14,Class_2!C14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G67" s="14" t="str">
+        <f>IF(MIN(Class_0!D14,Class_1!D14,Class_2!D14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H67" s="14" t="str">
+        <f>IF(MIN(Class_0!E14,Class_1!E14,Class_2!E14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I67" s="14" t="str">
+        <f>IF(MIN(Class_0!F14,Class_1!F14,Class_2!F14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J67" s="14" t="str">
+        <f>IF(MIN(Class_0!G14,Class_1!G14,Class_2!G14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K67" s="14" t="str">
+        <f>IF(MIN(Class_0!H14,Class_1!H14,Class_2!H14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L67" s="14" t="str">
+        <f>IF(MIN(Class_0!I14,Class_1!I14,Class_2!I14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M67" s="14" t="str">
+        <f>IF(MIN(Class_0!J14,Class_1!J14,Class_2!J14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N67" s="14" t="str">
+        <f>IF(MIN(Class_0!K14,Class_1!K14,Class_2!K14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O67" s="14" t="str">
+        <f>IF(MIN(Class_0!L14,Class_1!L14,Class_2!L14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P67" s="14" t="str">
+        <f>IF(MIN(Class_0!M14,Class_1!M14,Class_2!M14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q67" s="14" t="str">
+        <f>IF(MIN(Class_0!N14,Class_1!N14,Class_2!N14) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R67" s="14"/>
+      <c r="S67" s="14"/>
+      <c r="T67" s="14"/>
+      <c r="U67" s="14"/>
+      <c r="V67" s="14"/>
+      <c r="W67" s="14"/>
+      <c r="X67" s="14"/>
+      <c r="Y67" s="14"/>
+      <c r="Z67" s="14"/>
+      <c r="AA67" s="14"/>
+      <c r="AB67" s="14"/>
+      <c r="AC67" s="14"/>
+      <c r="AD67" s="14"/>
+      <c r="AE67" s="14"/>
+      <c r="AF67" s="14"/>
+      <c r="AG67" s="14"/>
+      <c r="AH67" s="14"/>
+      <c r="AI67" s="14"/>
+      <c r="AJ67" s="14"/>
+      <c r="AK67" s="14"/>
+      <c r="AL67" s="14"/>
+      <c r="AM67" s="14"/>
+      <c r="AN67" s="14"/>
+      <c r="AO67" s="14"/>
+      <c r="AP67" s="14"/>
+      <c r="AQ67" s="14"/>
+      <c r="AR67" s="14"/>
+      <c r="AS67" s="14"/>
+      <c r="AT67" s="14"/>
+      <c r="AU67" s="14"/>
+      <c r="AV67" s="14"/>
+      <c r="AW67" s="14"/>
+      <c r="AX67" s="14"/>
+      <c r="AY67" s="14"/>
+      <c r="AZ67" s="14"/>
+      <c r="BA67" s="14"/>
+      <c r="BB67" s="14"/>
+      <c r="BC67" s="14"/>
+      <c r="BD67" s="14"/>
+      <c r="BE67" s="14"/>
+      <c r="BF67" s="15"/>
+    </row>
+    <row r="68" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C68" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68" s="10">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="E68" s="14" t="str">
+        <f>IF(MIN(Class_0!B15,Class_1!B15,Class_2!B15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F68" s="14" t="str">
+        <f>IF(MIN(Class_0!C15,Class_1!C15,Class_2!C15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G68" s="14" t="str">
+        <f>IF(MIN(Class_0!D15,Class_1!D15,Class_2!D15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H68" s="14" t="str">
+        <f>IF(MIN(Class_0!E15,Class_1!E15,Class_2!E15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I68" s="14" t="str">
+        <f>IF(MIN(Class_0!F15,Class_1!F15,Class_2!F15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J68" s="14" t="str">
+        <f>IF(MIN(Class_0!G15,Class_1!G15,Class_2!G15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K68" s="14" t="str">
+        <f>IF(MIN(Class_0!H15,Class_1!H15,Class_2!H15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L68" s="14" t="str">
+        <f>IF(MIN(Class_0!I15,Class_1!I15,Class_2!I15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M68" s="14" t="str">
+        <f>IF(MIN(Class_0!J15,Class_1!J15,Class_2!J15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N68" s="14" t="str">
+        <f>IF(MIN(Class_0!K15,Class_1!K15,Class_2!K15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O68" s="14" t="str">
+        <f>IF(MIN(Class_0!L15,Class_1!L15,Class_2!L15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P68" s="14" t="str">
+        <f>IF(MIN(Class_0!M15,Class_1!M15,Class_2!M15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q68" s="14" t="str">
+        <f>IF(MIN(Class_0!N15,Class_1!N15,Class_2!N15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R68" s="14" t="str">
+        <f>IF(MIN(Class_0!O15,Class_1!O15,Class_2!O15) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S68" s="14"/>
+      <c r="T68" s="14"/>
+      <c r="U68" s="14"/>
+      <c r="V68" s="14"/>
+      <c r="W68" s="14"/>
+      <c r="X68" s="14"/>
+      <c r="Y68" s="14"/>
+      <c r="Z68" s="14"/>
+      <c r="AA68" s="14"/>
+      <c r="AB68" s="14"/>
+      <c r="AC68" s="14"/>
+      <c r="AD68" s="14"/>
+      <c r="AE68" s="14"/>
+      <c r="AF68" s="14"/>
+      <c r="AG68" s="14"/>
+      <c r="AH68" s="14"/>
+      <c r="AI68" s="14"/>
+      <c r="AJ68" s="14"/>
+      <c r="AK68" s="14"/>
+      <c r="AL68" s="14"/>
+      <c r="AM68" s="14"/>
+      <c r="AN68" s="14"/>
+      <c r="AO68" s="14"/>
+      <c r="AP68" s="14"/>
+      <c r="AQ68" s="14"/>
+      <c r="AR68" s="14"/>
+      <c r="AS68" s="14"/>
+      <c r="AT68" s="14"/>
+      <c r="AU68" s="14"/>
+      <c r="AV68" s="14"/>
+      <c r="AW68" s="14"/>
+      <c r="AX68" s="14"/>
+      <c r="AY68" s="14"/>
+      <c r="AZ68" s="14"/>
+      <c r="BA68" s="14"/>
+      <c r="BB68" s="14"/>
+      <c r="BC68" s="14"/>
+      <c r="BD68" s="14"/>
+      <c r="BE68" s="14"/>
+      <c r="BF68" s="15"/>
+    </row>
+    <row r="69" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C69" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D69" s="10">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="E69" s="14" t="str">
+        <f>IF(MIN(Class_0!B16,Class_1!B16,Class_2!B16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F69" s="14" t="str">
+        <f>IF(MIN(Class_0!C16,Class_1!C16,Class_2!C16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G69" s="14" t="str">
+        <f>IF(MIN(Class_0!D16,Class_1!D16,Class_2!D16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H69" s="14" t="str">
+        <f>IF(MIN(Class_0!E16,Class_1!E16,Class_2!E16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I69" s="14" t="str">
+        <f>IF(MIN(Class_0!F16,Class_1!F16,Class_2!F16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J69" s="14" t="str">
+        <f>IF(MIN(Class_0!G16,Class_1!G16,Class_2!G16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K69" s="14" t="str">
+        <f>IF(MIN(Class_0!H16,Class_1!H16,Class_2!H16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L69" s="14" t="str">
+        <f>IF(MIN(Class_0!I16,Class_1!I16,Class_2!I16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M69" s="14" t="str">
+        <f>IF(MIN(Class_0!J16,Class_1!J16,Class_2!J16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N69" s="14" t="str">
+        <f>IF(MIN(Class_0!K16,Class_1!K16,Class_2!K16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O69" s="14" t="str">
+        <f>IF(MIN(Class_0!L16,Class_1!L16,Class_2!L16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P69" s="14" t="str">
+        <f>IF(MIN(Class_0!M16,Class_1!M16,Class_2!M16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q69" s="14" t="str">
+        <f>IF(MIN(Class_0!N16,Class_1!N16,Class_2!N16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R69" s="14" t="str">
+        <f>IF(MIN(Class_0!O16,Class_1!O16,Class_2!O16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S69" s="14" t="str">
+        <f>IF(MIN(Class_0!P16,Class_1!P16,Class_2!P16) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T69" s="14"/>
+      <c r="U69" s="14"/>
+      <c r="V69" s="14"/>
+      <c r="W69" s="14"/>
+      <c r="X69" s="14"/>
+      <c r="Y69" s="14"/>
+      <c r="Z69" s="14"/>
+      <c r="AA69" s="14"/>
+      <c r="AB69" s="14"/>
+      <c r="AC69" s="14"/>
+      <c r="AD69" s="14"/>
+      <c r="AE69" s="14"/>
+      <c r="AF69" s="14"/>
+      <c r="AG69" s="14"/>
+      <c r="AH69" s="14"/>
+      <c r="AI69" s="14"/>
+      <c r="AJ69" s="14"/>
+      <c r="AK69" s="14"/>
+      <c r="AL69" s="14"/>
+      <c r="AM69" s="14"/>
+      <c r="AN69" s="14"/>
+      <c r="AO69" s="14"/>
+      <c r="AP69" s="14"/>
+      <c r="AQ69" s="14"/>
+      <c r="AR69" s="14"/>
+      <c r="AS69" s="14"/>
+      <c r="AT69" s="14"/>
+      <c r="AU69" s="14"/>
+      <c r="AV69" s="14"/>
+      <c r="AW69" s="14"/>
+      <c r="AX69" s="14"/>
+      <c r="AY69" s="14"/>
+      <c r="AZ69" s="14"/>
+      <c r="BA69" s="14"/>
+      <c r="BB69" s="14"/>
+      <c r="BC69" s="14"/>
+      <c r="BD69" s="14"/>
+      <c r="BE69" s="14"/>
+      <c r="BF69" s="15"/>
+    </row>
+    <row r="70" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C70" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D70" s="10">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="E70" s="14" t="str">
+        <f>IF(MIN(Class_0!B17,Class_1!B17,Class_2!B17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F70" s="14" t="str">
+        <f>IF(MIN(Class_0!C17,Class_1!C17,Class_2!C17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G70" s="14" t="str">
+        <f>IF(MIN(Class_0!D17,Class_1!D17,Class_2!D17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H70" s="14" t="str">
+        <f>IF(MIN(Class_0!E17,Class_1!E17,Class_2!E17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I70" s="14" t="str">
+        <f>IF(MIN(Class_0!F17,Class_1!F17,Class_2!F17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J70" s="14" t="str">
+        <f>IF(MIN(Class_0!G17,Class_1!G17,Class_2!G17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K70" s="14" t="str">
+        <f>IF(MIN(Class_0!H17,Class_1!H17,Class_2!H17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L70" s="14" t="str">
+        <f>IF(MIN(Class_0!I17,Class_1!I17,Class_2!I17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M70" s="14" t="str">
+        <f>IF(MIN(Class_0!J17,Class_1!J17,Class_2!J17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N70" s="14" t="str">
+        <f>IF(MIN(Class_0!K17,Class_1!K17,Class_2!K17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O70" s="14" t="str">
+        <f>IF(MIN(Class_0!L17,Class_1!L17,Class_2!L17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P70" s="14" t="str">
+        <f>IF(MIN(Class_0!M17,Class_1!M17,Class_2!M17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q70" s="14" t="str">
+        <f>IF(MIN(Class_0!N17,Class_1!N17,Class_2!N17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R70" s="14" t="str">
+        <f>IF(MIN(Class_0!O17,Class_1!O17,Class_2!O17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S70" s="14" t="str">
+        <f>IF(MIN(Class_0!P17,Class_1!P17,Class_2!P17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T70" s="14" t="str">
+        <f>IF(MIN(Class_0!Q17,Class_1!Q17,Class_2!Q17) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U70" s="14"/>
+      <c r="V70" s="14"/>
+      <c r="W70" s="14"/>
+      <c r="X70" s="14"/>
+      <c r="Y70" s="14"/>
+      <c r="Z70" s="14"/>
+      <c r="AA70" s="14"/>
+      <c r="AB70" s="14"/>
+      <c r="AC70" s="14"/>
+      <c r="AD70" s="14"/>
+      <c r="AE70" s="14"/>
+      <c r="AF70" s="14"/>
+      <c r="AG70" s="14"/>
+      <c r="AH70" s="14"/>
+      <c r="AI70" s="14"/>
+      <c r="AJ70" s="14"/>
+      <c r="AK70" s="14"/>
+      <c r="AL70" s="14"/>
+      <c r="AM70" s="14"/>
+      <c r="AN70" s="14"/>
+      <c r="AO70" s="14"/>
+      <c r="AP70" s="14"/>
+      <c r="AQ70" s="14"/>
+      <c r="AR70" s="14"/>
+      <c r="AS70" s="14"/>
+      <c r="AT70" s="14"/>
+      <c r="AU70" s="14"/>
+      <c r="AV70" s="14"/>
+      <c r="AW70" s="14"/>
+      <c r="AX70" s="14"/>
+      <c r="AY70" s="14"/>
+      <c r="AZ70" s="14"/>
+      <c r="BA70" s="14"/>
+      <c r="BB70" s="14"/>
+      <c r="BC70" s="14"/>
+      <c r="BD70" s="14"/>
+      <c r="BE70" s="14"/>
+      <c r="BF70" s="15"/>
+    </row>
+    <row r="71" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C71" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="10">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="E71" s="14" t="str">
+        <f>IF(MIN(Class_0!B18,Class_1!B18,Class_2!B18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F71" s="14" t="str">
+        <f>IF(MIN(Class_0!C18,Class_1!C18,Class_2!C18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G71" s="14" t="str">
+        <f>IF(MIN(Class_0!D18,Class_1!D18,Class_2!D18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H71" s="14" t="str">
+        <f>IF(MIN(Class_0!E18,Class_1!E18,Class_2!E18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I71" s="14" t="str">
+        <f>IF(MIN(Class_0!F18,Class_1!F18,Class_2!F18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="J71" s="14" t="str">
+        <f>IF(MIN(Class_0!G18,Class_1!G18,Class_2!G18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="K71" s="14" t="str">
+        <f>IF(MIN(Class_0!H18,Class_1!H18,Class_2!H18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L71" s="14" t="str">
+        <f>IF(MIN(Class_0!I18,Class_1!I18,Class_2!I18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M71" s="14" t="str">
+        <f>IF(MIN(Class_0!J18,Class_1!J18,Class_2!J18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N71" s="14" t="str">
+        <f>IF(MIN(Class_0!K18,Class_1!K18,Class_2!K18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O71" s="14" t="str">
+        <f>IF(MIN(Class_0!L18,Class_1!L18,Class_2!L18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="P71" s="14" t="str">
+        <f>IF(MIN(Class_0!M18,Class_1!M18,Class_2!M18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q71" s="14" t="str">
+        <f>IF(MIN(Class_0!N18,Class_1!N18,Class_2!N18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R71" s="14" t="str">
+        <f>IF(MIN(Class_0!O18,Class_1!O18,Class_2!O18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S71" s="14" t="str">
+        <f>IF(MIN(Class_0!P18,Class_1!P18,Class_2!P18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T71" s="14" t="str">
+        <f>IF(MIN(Class_0!Q18,Class_1!Q18,Class_2!Q18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U71" s="14" t="str">
+        <f>IF(MIN(Class_0!R18,Class_1!R18,Class_2!R18) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V71" s="14"/>
+      <c r="W71" s="14"/>
+      <c r="X71" s="14"/>
+      <c r="Y71" s="14"/>
+      <c r="Z71" s="14"/>
+      <c r="AA71" s="14"/>
+      <c r="AB71" s="14"/>
+      <c r="AC71" s="14"/>
+      <c r="AD71" s="14"/>
+      <c r="AE71" s="14"/>
+      <c r="AF71" s="14"/>
+      <c r="AG71" s="14"/>
+      <c r="AH71" s="14"/>
+      <c r="AI71" s="14"/>
+      <c r="AJ71" s="14"/>
+      <c r="AK71" s="14"/>
+      <c r="AL71" s="14"/>
+      <c r="AM71" s="14"/>
+      <c r="AN71" s="14"/>
+      <c r="AO71" s="14"/>
+      <c r="AP71" s="14"/>
+      <c r="AQ71" s="14"/>
+      <c r="AR71" s="14"/>
+      <c r="AS71" s="14"/>
+      <c r="AT71" s="14"/>
+      <c r="AU71" s="14"/>
+      <c r="AV71" s="14"/>
+      <c r="AW71" s="14"/>
+      <c r="AX71" s="14"/>
+      <c r="AY71" s="14"/>
+      <c r="AZ71" s="14"/>
+      <c r="BA71" s="14"/>
+      <c r="BB71" s="14"/>
+      <c r="BC71" s="14"/>
+      <c r="BD71" s="14"/>
+      <c r="BE71" s="14"/>
+      <c r="BF71" s="15"/>
+    </row>
+    <row r="72" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C72" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D72" s="10">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="E72" s="14" t="str">
+        <f>IF(MIN(Class_0!B19,Class_1!B19,Class_2!B19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F72" s="14" t="str">
+        <f>IF(MIN(Class_0!C19,Class_1!C19,Class_2!C19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G72" s="14" t="str">
+        <f>IF(MIN(Class_0!D19,Class_1!D19,Class_2!D19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="H72" s="14" t="str">
+        <f>IF(MIN(Class_0!E19,Class_1!E19,Class_2!E19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I72" s="14" t="str">
+        <f>IF(MIN(Class_0!F19,Class_1!F19,Class_2!F19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J72" s="14" t="str">
+        <f>IF(MIN(Class_0!G19,Class_1!G19,Class_2!G19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K72" s="14" t="str">
+        <f>IF(MIN(Class_0!H19,Class_1!H19,Class_2!H19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L72" s="14" t="str">
+        <f>IF(MIN(Class_0!I19,Class_1!I19,Class_2!I19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M72" s="14" t="str">
+        <f>IF(MIN(Class_0!J19,Class_1!J19,Class_2!J19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N72" s="14" t="str">
+        <f>IF(MIN(Class_0!K19,Class_1!K19,Class_2!K19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O72" s="14" t="str">
+        <f>IF(MIN(Class_0!L19,Class_1!L19,Class_2!L19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P72" s="14" t="str">
+        <f>IF(MIN(Class_0!M19,Class_1!M19,Class_2!M19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q72" s="14" t="str">
+        <f>IF(MIN(Class_0!N19,Class_1!N19,Class_2!N19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R72" s="14" t="str">
+        <f>IF(MIN(Class_0!O19,Class_1!O19,Class_2!O19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S72" s="14" t="str">
+        <f>IF(MIN(Class_0!P19,Class_1!P19,Class_2!P19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T72" s="14" t="str">
+        <f>IF(MIN(Class_0!Q19,Class_1!Q19,Class_2!Q19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U72" s="14" t="str">
+        <f>IF(MIN(Class_0!R19,Class_1!R19,Class_2!R19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V72" s="14" t="str">
+        <f>IF(MIN(Class_0!S19,Class_1!S19,Class_2!S19) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W72" s="14"/>
+      <c r="X72" s="14"/>
+      <c r="Y72" s="14"/>
+      <c r="Z72" s="14"/>
+      <c r="AA72" s="14"/>
+      <c r="AB72" s="14"/>
+      <c r="AC72" s="14"/>
+      <c r="AD72" s="14"/>
+      <c r="AE72" s="14"/>
+      <c r="AF72" s="14"/>
+      <c r="AG72" s="14"/>
+      <c r="AH72" s="14"/>
+      <c r="AI72" s="14"/>
+      <c r="AJ72" s="14"/>
+      <c r="AK72" s="14"/>
+      <c r="AL72" s="14"/>
+      <c r="AM72" s="14"/>
+      <c r="AN72" s="14"/>
+      <c r="AO72" s="14"/>
+      <c r="AP72" s="14"/>
+      <c r="AQ72" s="14"/>
+      <c r="AR72" s="14"/>
+      <c r="AS72" s="14"/>
+      <c r="AT72" s="14"/>
+      <c r="AU72" s="14"/>
+      <c r="AV72" s="14"/>
+      <c r="AW72" s="14"/>
+      <c r="AX72" s="14"/>
+      <c r="AY72" s="14"/>
+      <c r="AZ72" s="14"/>
+      <c r="BA72" s="14"/>
+      <c r="BB72" s="14"/>
+      <c r="BC72" s="14"/>
+      <c r="BD72" s="14"/>
+      <c r="BE72" s="14"/>
+      <c r="BF72" s="15"/>
+    </row>
+    <row r="73" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C73" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D73" s="10">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="E73" s="14" t="str">
+        <f>IF(MIN(Class_0!B20,Class_1!B20,Class_2!B20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F73" s="14" t="str">
+        <f>IF(MIN(Class_0!C20,Class_1!C20,Class_2!C20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G73" s="14" t="str">
+        <f>IF(MIN(Class_0!D20,Class_1!D20,Class_2!D20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H73" s="14" t="str">
+        <f>IF(MIN(Class_0!E20,Class_1!E20,Class_2!E20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I73" s="14" t="str">
+        <f>IF(MIN(Class_0!F20,Class_1!F20,Class_2!F20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J73" s="14" t="str">
+        <f>IF(MIN(Class_0!G20,Class_1!G20,Class_2!G20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K73" s="14" t="str">
+        <f>IF(MIN(Class_0!H20,Class_1!H20,Class_2!H20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L73" s="14" t="str">
+        <f>IF(MIN(Class_0!I20,Class_1!I20,Class_2!I20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M73" s="14" t="str">
+        <f>IF(MIN(Class_0!J20,Class_1!J20,Class_2!J20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N73" s="14" t="str">
+        <f>IF(MIN(Class_0!K20,Class_1!K20,Class_2!K20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="O73" s="14" t="str">
+        <f>IF(MIN(Class_0!L20,Class_1!L20,Class_2!L20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P73" s="14" t="str">
+        <f>IF(MIN(Class_0!M20,Class_1!M20,Class_2!M20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q73" s="14" t="str">
+        <f>IF(MIN(Class_0!N20,Class_1!N20,Class_2!N20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R73" s="14" t="str">
+        <f>IF(MIN(Class_0!O20,Class_1!O20,Class_2!O20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S73" s="14" t="str">
+        <f>IF(MIN(Class_0!P20,Class_1!P20,Class_2!P20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T73" s="14" t="str">
+        <f>IF(MIN(Class_0!Q20,Class_1!Q20,Class_2!Q20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U73" s="14" t="str">
+        <f>IF(MIN(Class_0!R20,Class_1!R20,Class_2!R20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V73" s="14" t="str">
+        <f>IF(MIN(Class_0!S20,Class_1!S20,Class_2!S20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W73" s="14" t="str">
+        <f>IF(MIN(Class_0!T20,Class_1!T20,Class_2!T20) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X73" s="14"/>
+      <c r="Y73" s="14"/>
+      <c r="Z73" s="14"/>
+      <c r="AA73" s="14"/>
+      <c r="AB73" s="14"/>
+      <c r="AC73" s="14"/>
+      <c r="AD73" s="14"/>
+      <c r="AE73" s="14"/>
+      <c r="AF73" s="14"/>
+      <c r="AG73" s="14"/>
+      <c r="AH73" s="14"/>
+      <c r="AI73" s="14"/>
+      <c r="AJ73" s="14"/>
+      <c r="AK73" s="14"/>
+      <c r="AL73" s="14"/>
+      <c r="AM73" s="14"/>
+      <c r="AN73" s="14"/>
+      <c r="AO73" s="14"/>
+      <c r="AP73" s="14"/>
+      <c r="AQ73" s="14"/>
+      <c r="AR73" s="14"/>
+      <c r="AS73" s="14"/>
+      <c r="AT73" s="14"/>
+      <c r="AU73" s="14"/>
+      <c r="AV73" s="14"/>
+      <c r="AW73" s="14"/>
+      <c r="AX73" s="14"/>
+      <c r="AY73" s="14"/>
+      <c r="AZ73" s="14"/>
+      <c r="BA73" s="14"/>
+      <c r="BB73" s="14"/>
+      <c r="BC73" s="14"/>
+      <c r="BD73" s="14"/>
+      <c r="BE73" s="14"/>
+      <c r="BF73" s="15"/>
+    </row>
+    <row r="74" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C74" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D74" s="10">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="E74" s="14" t="str">
+        <f>IF(MIN(Class_0!B21,Class_1!B21,Class_2!B21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F74" s="14" t="str">
+        <f>IF(MIN(Class_0!C21,Class_1!C21,Class_2!C21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G74" s="14" t="str">
+        <f>IF(MIN(Class_0!D21,Class_1!D21,Class_2!D21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H74" s="14" t="str">
+        <f>IF(MIN(Class_0!E21,Class_1!E21,Class_2!E21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I74" s="14" t="str">
+        <f>IF(MIN(Class_0!F21,Class_1!F21,Class_2!F21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J74" s="14" t="str">
+        <f>IF(MIN(Class_0!G21,Class_1!G21,Class_2!G21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K74" s="14" t="str">
+        <f>IF(MIN(Class_0!H21,Class_1!H21,Class_2!H21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L74" s="14" t="str">
+        <f>IF(MIN(Class_0!I21,Class_1!I21,Class_2!I21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M74" s="14" t="str">
+        <f>IF(MIN(Class_0!J21,Class_1!J21,Class_2!J21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N74" s="14" t="str">
+        <f>IF(MIN(Class_0!K21,Class_1!K21,Class_2!K21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O74" s="14" t="str">
+        <f>IF(MIN(Class_0!L21,Class_1!L21,Class_2!L21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P74" s="14" t="str">
+        <f>IF(MIN(Class_0!M21,Class_1!M21,Class_2!M21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q74" s="14" t="str">
+        <f>IF(MIN(Class_0!N21,Class_1!N21,Class_2!N21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R74" s="14" t="str">
+        <f>IF(MIN(Class_0!O21,Class_1!O21,Class_2!O21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S74" s="14" t="str">
+        <f>IF(MIN(Class_0!P21,Class_1!P21,Class_2!P21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T74" s="14" t="str">
+        <f>IF(MIN(Class_0!Q21,Class_1!Q21,Class_2!Q21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U74" s="14" t="str">
+        <f>IF(MIN(Class_0!R21,Class_1!R21,Class_2!R21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V74" s="14" t="str">
+        <f>IF(MIN(Class_0!S21,Class_1!S21,Class_2!S21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W74" s="14" t="str">
+        <f>IF(MIN(Class_0!T21,Class_1!T21,Class_2!T21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X74" s="14" t="str">
+        <f>IF(MIN(Class_0!U21,Class_1!U21,Class_2!U21) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y74" s="14"/>
+      <c r="Z74" s="14"/>
+      <c r="AA74" s="14"/>
+      <c r="AB74" s="14"/>
+      <c r="AC74" s="14"/>
+      <c r="AD74" s="14"/>
+      <c r="AE74" s="14"/>
+      <c r="AF74" s="14"/>
+      <c r="AG74" s="14"/>
+      <c r="AH74" s="14"/>
+      <c r="AI74" s="14"/>
+      <c r="AJ74" s="14"/>
+      <c r="AK74" s="14"/>
+      <c r="AL74" s="14"/>
+      <c r="AM74" s="14"/>
+      <c r="AN74" s="14"/>
+      <c r="AO74" s="14"/>
+      <c r="AP74" s="14"/>
+      <c r="AQ74" s="14"/>
+      <c r="AR74" s="14"/>
+      <c r="AS74" s="14"/>
+      <c r="AT74" s="14"/>
+      <c r="AU74" s="14"/>
+      <c r="AV74" s="14"/>
+      <c r="AW74" s="14"/>
+      <c r="AX74" s="14"/>
+      <c r="AY74" s="14"/>
+      <c r="AZ74" s="14"/>
+      <c r="BA74" s="14"/>
+      <c r="BB74" s="14"/>
+      <c r="BC74" s="14"/>
+      <c r="BD74" s="14"/>
+      <c r="BE74" s="14"/>
+      <c r="BF74" s="15"/>
+    </row>
+    <row r="75" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C75" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" s="10">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="E75" s="14" t="str">
+        <f>IF(MIN(Class_0!B22,Class_1!B22,Class_2!B22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F75" s="14" t="str">
+        <f>IF(MIN(Class_0!C22,Class_1!C22,Class_2!C22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G75" s="14" t="str">
+        <f>IF(MIN(Class_0!D22,Class_1!D22,Class_2!D22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H75" s="14" t="str">
+        <f>IF(MIN(Class_0!E22,Class_1!E22,Class_2!E22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I75" s="14" t="str">
+        <f>IF(MIN(Class_0!F22,Class_1!F22,Class_2!F22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J75" s="14" t="str">
+        <f>IF(MIN(Class_0!G22,Class_1!G22,Class_2!G22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K75" s="14" t="str">
+        <f>IF(MIN(Class_0!H22,Class_1!H22,Class_2!H22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L75" s="14" t="str">
+        <f>IF(MIN(Class_0!I22,Class_1!I22,Class_2!I22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M75" s="14" t="str">
+        <f>IF(MIN(Class_0!J22,Class_1!J22,Class_2!J22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N75" s="14" t="str">
+        <f>IF(MIN(Class_0!K22,Class_1!K22,Class_2!K22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O75" s="14" t="str">
+        <f>IF(MIN(Class_0!L22,Class_1!L22,Class_2!L22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P75" s="14" t="str">
+        <f>IF(MIN(Class_0!M22,Class_1!M22,Class_2!M22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q75" s="14" t="str">
+        <f>IF(MIN(Class_0!N22,Class_1!N22,Class_2!N22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R75" s="14" t="str">
+        <f>IF(MIN(Class_0!O22,Class_1!O22,Class_2!O22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S75" s="14" t="str">
+        <f>IF(MIN(Class_0!P22,Class_1!P22,Class_2!P22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T75" s="14" t="str">
+        <f>IF(MIN(Class_0!Q22,Class_1!Q22,Class_2!Q22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U75" s="14" t="str">
+        <f>IF(MIN(Class_0!R22,Class_1!R22,Class_2!R22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V75" s="14" t="str">
+        <f>IF(MIN(Class_0!S22,Class_1!S22,Class_2!S22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W75" s="14" t="str">
+        <f>IF(MIN(Class_0!T22,Class_1!T22,Class_2!T22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X75" s="14" t="str">
+        <f>IF(MIN(Class_0!U22,Class_1!U22,Class_2!U22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y75" s="14" t="str">
+        <f>IF(MIN(Class_0!V22,Class_1!V22,Class_2!V22) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z75" s="14"/>
+      <c r="AA75" s="14"/>
+      <c r="AB75" s="14"/>
+      <c r="AC75" s="14"/>
+      <c r="AD75" s="14"/>
+      <c r="AE75" s="14"/>
+      <c r="AF75" s="14"/>
+      <c r="AG75" s="14"/>
+      <c r="AH75" s="14"/>
+      <c r="AI75" s="14"/>
+      <c r="AJ75" s="14"/>
+      <c r="AK75" s="14"/>
+      <c r="AL75" s="14"/>
+      <c r="AM75" s="14"/>
+      <c r="AN75" s="14"/>
+      <c r="AO75" s="14"/>
+      <c r="AP75" s="14"/>
+      <c r="AQ75" s="14"/>
+      <c r="AR75" s="14"/>
+      <c r="AS75" s="14"/>
+      <c r="AT75" s="14"/>
+      <c r="AU75" s="14"/>
+      <c r="AV75" s="14"/>
+      <c r="AW75" s="14"/>
+      <c r="AX75" s="14"/>
+      <c r="AY75" s="14"/>
+      <c r="AZ75" s="14"/>
+      <c r="BA75" s="14"/>
+      <c r="BB75" s="14"/>
+      <c r="BC75" s="14"/>
+      <c r="BD75" s="14"/>
+      <c r="BE75" s="14"/>
+      <c r="BF75" s="15"/>
+    </row>
+    <row r="76" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C76" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" s="10">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="E76" s="14" t="str">
+        <f>IF(MIN(Class_0!B23,Class_1!B23,Class_2!B23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F76" s="14" t="str">
+        <f>IF(MIN(Class_0!C23,Class_1!C23,Class_2!C23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G76" s="14" t="str">
+        <f>IF(MIN(Class_0!D23,Class_1!D23,Class_2!D23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H76" s="14" t="str">
+        <f>IF(MIN(Class_0!E23,Class_1!E23,Class_2!E23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I76" s="14" t="str">
+        <f>IF(MIN(Class_0!F23,Class_1!F23,Class_2!F23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J76" s="14" t="str">
+        <f>IF(MIN(Class_0!G23,Class_1!G23,Class_2!G23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K76" s="14" t="str">
+        <f>IF(MIN(Class_0!H23,Class_1!H23,Class_2!H23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L76" s="14" t="str">
+        <f>IF(MIN(Class_0!I23,Class_1!I23,Class_2!I23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M76" s="14" t="str">
+        <f>IF(MIN(Class_0!J23,Class_1!J23,Class_2!J23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N76" s="14" t="str">
+        <f>IF(MIN(Class_0!K23,Class_1!K23,Class_2!K23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O76" s="14" t="str">
+        <f>IF(MIN(Class_0!L23,Class_1!L23,Class_2!L23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P76" s="14" t="str">
+        <f>IF(MIN(Class_0!M23,Class_1!M23,Class_2!M23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q76" s="14" t="str">
+        <f>IF(MIN(Class_0!N23,Class_1!N23,Class_2!N23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R76" s="14" t="str">
+        <f>IF(MIN(Class_0!O23,Class_1!O23,Class_2!O23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S76" s="14" t="str">
+        <f>IF(MIN(Class_0!P23,Class_1!P23,Class_2!P23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T76" s="14" t="str">
+        <f>IF(MIN(Class_0!Q23,Class_1!Q23,Class_2!Q23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U76" s="14" t="str">
+        <f>IF(MIN(Class_0!R23,Class_1!R23,Class_2!R23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V76" s="14" t="str">
+        <f>IF(MIN(Class_0!S23,Class_1!S23,Class_2!S23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W76" s="14" t="str">
+        <f>IF(MIN(Class_0!T23,Class_1!T23,Class_2!T23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X76" s="14" t="str">
+        <f>IF(MIN(Class_0!U23,Class_1!U23,Class_2!U23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y76" s="14" t="str">
+        <f>IF(MIN(Class_0!V23,Class_1!V23,Class_2!V23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z76" s="14" t="str">
+        <f>IF(MIN(Class_0!W23,Class_1!W23,Class_2!W23) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA76" s="14"/>
+      <c r="AB76" s="14"/>
+      <c r="AC76" s="14"/>
+      <c r="AD76" s="14"/>
+      <c r="AE76" s="14"/>
+      <c r="AF76" s="14"/>
+      <c r="AG76" s="14"/>
+      <c r="AH76" s="14"/>
+      <c r="AI76" s="14"/>
+      <c r="AJ76" s="14"/>
+      <c r="AK76" s="14"/>
+      <c r="AL76" s="14"/>
+      <c r="AM76" s="14"/>
+      <c r="AN76" s="14"/>
+      <c r="AO76" s="14"/>
+      <c r="AP76" s="14"/>
+      <c r="AQ76" s="14"/>
+      <c r="AR76" s="14"/>
+      <c r="AS76" s="14"/>
+      <c r="AT76" s="14"/>
+      <c r="AU76" s="14"/>
+      <c r="AV76" s="14"/>
+      <c r="AW76" s="14"/>
+      <c r="AX76" s="14"/>
+      <c r="AY76" s="14"/>
+      <c r="AZ76" s="14"/>
+      <c r="BA76" s="14"/>
+      <c r="BB76" s="14"/>
+      <c r="BC76" s="14"/>
+      <c r="BD76" s="14"/>
+      <c r="BE76" s="14"/>
+      <c r="BF76" s="15"/>
+    </row>
+    <row r="77" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C77" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D77" s="10">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="E77" s="14" t="str">
+        <f>IF(MIN(Class_0!B24,Class_1!B24,Class_2!B24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F77" s="14" t="str">
+        <f>IF(MIN(Class_0!C24,Class_1!C24,Class_2!C24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G77" s="14" t="str">
+        <f>IF(MIN(Class_0!D24,Class_1!D24,Class_2!D24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H77" s="14" t="str">
+        <f>IF(MIN(Class_0!E24,Class_1!E24,Class_2!E24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I77" s="14" t="str">
+        <f>IF(MIN(Class_0!F24,Class_1!F24,Class_2!F24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J77" s="14" t="str">
+        <f>IF(MIN(Class_0!G24,Class_1!G24,Class_2!G24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K77" s="14" t="str">
+        <f>IF(MIN(Class_0!H24,Class_1!H24,Class_2!H24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L77" s="14" t="str">
+        <f>IF(MIN(Class_0!I24,Class_1!I24,Class_2!I24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M77" s="14" t="str">
+        <f>IF(MIN(Class_0!J24,Class_1!J24,Class_2!J24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N77" s="14" t="str">
+        <f>IF(MIN(Class_0!K24,Class_1!K24,Class_2!K24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O77" s="14" t="str">
+        <f>IF(MIN(Class_0!L24,Class_1!L24,Class_2!L24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P77" s="14" t="str">
+        <f>IF(MIN(Class_0!M24,Class_1!M24,Class_2!M24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q77" s="14" t="str">
+        <f>IF(MIN(Class_0!N24,Class_1!N24,Class_2!N24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R77" s="14" t="str">
+        <f>IF(MIN(Class_0!O24,Class_1!O24,Class_2!O24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S77" s="14" t="str">
+        <f>IF(MIN(Class_0!P24,Class_1!P24,Class_2!P24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T77" s="14" t="str">
+        <f>IF(MIN(Class_0!Q24,Class_1!Q24,Class_2!Q24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U77" s="14" t="str">
+        <f>IF(MIN(Class_0!R24,Class_1!R24,Class_2!R24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V77" s="14" t="str">
+        <f>IF(MIN(Class_0!S24,Class_1!S24,Class_2!S24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W77" s="14" t="str">
+        <f>IF(MIN(Class_0!T24,Class_1!T24,Class_2!T24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X77" s="14" t="str">
+        <f>IF(MIN(Class_0!U24,Class_1!U24,Class_2!U24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y77" s="14" t="str">
+        <f>IF(MIN(Class_0!V24,Class_1!V24,Class_2!V24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z77" s="14" t="str">
+        <f>IF(MIN(Class_0!W24,Class_1!W24,Class_2!W24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA77" s="14" t="str">
+        <f>IF(MIN(Class_0!X24,Class_1!X24,Class_2!X24) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB77" s="14"/>
+      <c r="AC77" s="14"/>
+      <c r="AD77" s="14"/>
+      <c r="AE77" s="14"/>
+      <c r="AF77" s="14"/>
+      <c r="AG77" s="14"/>
+      <c r="AH77" s="14"/>
+      <c r="AI77" s="14"/>
+      <c r="AJ77" s="14"/>
+      <c r="AK77" s="14"/>
+      <c r="AL77" s="14"/>
+      <c r="AM77" s="14"/>
+      <c r="AN77" s="14"/>
+      <c r="AO77" s="14"/>
+      <c r="AP77" s="14"/>
+      <c r="AQ77" s="14"/>
+      <c r="AR77" s="14"/>
+      <c r="AS77" s="14"/>
+      <c r="AT77" s="14"/>
+      <c r="AU77" s="14"/>
+      <c r="AV77" s="14"/>
+      <c r="AW77" s="14"/>
+      <c r="AX77" s="14"/>
+      <c r="AY77" s="14"/>
+      <c r="AZ77" s="14"/>
+      <c r="BA77" s="14"/>
+      <c r="BB77" s="14"/>
+      <c r="BC77" s="14"/>
+      <c r="BD77" s="14"/>
+      <c r="BE77" s="14"/>
+      <c r="BF77" s="15"/>
+    </row>
+    <row r="78" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C78" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" s="10">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="E78" s="14" t="str">
+        <f>IF(MIN(Class_0!B25,Class_1!B25,Class_2!B25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F78" s="14" t="str">
+        <f>IF(MIN(Class_0!C25,Class_1!C25,Class_2!C25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G78" s="14" t="str">
+        <f>IF(MIN(Class_0!D25,Class_1!D25,Class_2!D25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H78" s="14" t="str">
+        <f>IF(MIN(Class_0!E25,Class_1!E25,Class_2!E25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="I78" s="14" t="str">
+        <f>IF(MIN(Class_0!F25,Class_1!F25,Class_2!F25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J78" s="14" t="str">
+        <f>IF(MIN(Class_0!G25,Class_1!G25,Class_2!G25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K78" s="14" t="str">
+        <f>IF(MIN(Class_0!H25,Class_1!H25,Class_2!H25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L78" s="14" t="str">
+        <f>IF(MIN(Class_0!I25,Class_1!I25,Class_2!I25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M78" s="14" t="str">
+        <f>IF(MIN(Class_0!J25,Class_1!J25,Class_2!J25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N78" s="14" t="str">
+        <f>IF(MIN(Class_0!K25,Class_1!K25,Class_2!K25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O78" s="14" t="str">
+        <f>IF(MIN(Class_0!L25,Class_1!L25,Class_2!L25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P78" s="14" t="str">
+        <f>IF(MIN(Class_0!M25,Class_1!M25,Class_2!M25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q78" s="14" t="str">
+        <f>IF(MIN(Class_0!N25,Class_1!N25,Class_2!N25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R78" s="14" t="str">
+        <f>IF(MIN(Class_0!O25,Class_1!O25,Class_2!O25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S78" s="14" t="str">
+        <f>IF(MIN(Class_0!P25,Class_1!P25,Class_2!P25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T78" s="14" t="str">
+        <f>IF(MIN(Class_0!Q25,Class_1!Q25,Class_2!Q25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U78" s="14" t="str">
+        <f>IF(MIN(Class_0!R25,Class_1!R25,Class_2!R25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V78" s="14" t="str">
+        <f>IF(MIN(Class_0!S25,Class_1!S25,Class_2!S25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W78" s="14" t="str">
+        <f>IF(MIN(Class_0!T25,Class_1!T25,Class_2!T25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X78" s="14" t="str">
+        <f>IF(MIN(Class_0!U25,Class_1!U25,Class_2!U25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y78" s="14" t="str">
+        <f>IF(MIN(Class_0!V25,Class_1!V25,Class_2!V25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z78" s="14" t="str">
+        <f>IF(MIN(Class_0!W25,Class_1!W25,Class_2!W25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA78" s="14" t="str">
+        <f>IF(MIN(Class_0!X25,Class_1!X25,Class_2!X25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB78" s="14" t="str">
+        <f>IF(MIN(Class_0!Y25,Class_1!Y25,Class_2!Y25) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC78" s="14"/>
+      <c r="AD78" s="14"/>
+      <c r="AE78" s="14"/>
+      <c r="AF78" s="14"/>
+      <c r="AG78" s="14"/>
+      <c r="AH78" s="14"/>
+      <c r="AI78" s="14"/>
+      <c r="AJ78" s="14"/>
+      <c r="AK78" s="14"/>
+      <c r="AL78" s="14"/>
+      <c r="AM78" s="14"/>
+      <c r="AN78" s="14"/>
+      <c r="AO78" s="14"/>
+      <c r="AP78" s="14"/>
+      <c r="AQ78" s="14"/>
+      <c r="AR78" s="14"/>
+      <c r="AS78" s="14"/>
+      <c r="AT78" s="14"/>
+      <c r="AU78" s="14"/>
+      <c r="AV78" s="14"/>
+      <c r="AW78" s="14"/>
+      <c r="AX78" s="14"/>
+      <c r="AY78" s="14"/>
+      <c r="AZ78" s="14"/>
+      <c r="BA78" s="14"/>
+      <c r="BB78" s="14"/>
+      <c r="BC78" s="14"/>
+      <c r="BD78" s="14"/>
+      <c r="BE78" s="14"/>
+      <c r="BF78" s="15"/>
+    </row>
+    <row r="79" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C79" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D79" s="10">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="E79" s="14" t="str">
+        <f>IF(MIN(Class_0!B26,Class_1!B26,Class_2!B26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F79" s="14" t="str">
+        <f>IF(MIN(Class_0!C26,Class_1!C26,Class_2!C26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G79" s="14" t="str">
+        <f>IF(MIN(Class_0!D26,Class_1!D26,Class_2!D26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H79" s="14" t="str">
+        <f>IF(MIN(Class_0!E26,Class_1!E26,Class_2!E26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I79" s="14" t="str">
+        <f>IF(MIN(Class_0!F26,Class_1!F26,Class_2!F26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J79" s="14" t="str">
+        <f>IF(MIN(Class_0!G26,Class_1!G26,Class_2!G26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K79" s="14" t="str">
+        <f>IF(MIN(Class_0!H26,Class_1!H26,Class_2!H26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="L79" s="14" t="str">
+        <f>IF(MIN(Class_0!I26,Class_1!I26,Class_2!I26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M79" s="14" t="str">
+        <f>IF(MIN(Class_0!J26,Class_1!J26,Class_2!J26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N79" s="14" t="str">
+        <f>IF(MIN(Class_0!K26,Class_1!K26,Class_2!K26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O79" s="14" t="str">
+        <f>IF(MIN(Class_0!L26,Class_1!L26,Class_2!L26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P79" s="14" t="str">
+        <f>IF(MIN(Class_0!M26,Class_1!M26,Class_2!M26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q79" s="14" t="str">
+        <f>IF(MIN(Class_0!N26,Class_1!N26,Class_2!N26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R79" s="14" t="str">
+        <f>IF(MIN(Class_0!O26,Class_1!O26,Class_2!O26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S79" s="14" t="str">
+        <f>IF(MIN(Class_0!P26,Class_1!P26,Class_2!P26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T79" s="14" t="str">
+        <f>IF(MIN(Class_0!Q26,Class_1!Q26,Class_2!Q26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U79" s="14" t="str">
+        <f>IF(MIN(Class_0!R26,Class_1!R26,Class_2!R26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V79" s="14" t="str">
+        <f>IF(MIN(Class_0!S26,Class_1!S26,Class_2!S26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W79" s="14" t="str">
+        <f>IF(MIN(Class_0!T26,Class_1!T26,Class_2!T26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X79" s="14" t="str">
+        <f>IF(MIN(Class_0!U26,Class_1!U26,Class_2!U26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y79" s="14" t="str">
+        <f>IF(MIN(Class_0!V26,Class_1!V26,Class_2!V26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z79" s="14" t="str">
+        <f>IF(MIN(Class_0!W26,Class_1!W26,Class_2!W26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA79" s="14" t="str">
+        <f>IF(MIN(Class_0!X26,Class_1!X26,Class_2!X26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB79" s="14" t="str">
+        <f>IF(MIN(Class_0!Y26,Class_1!Y26,Class_2!Y26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC79" s="14" t="str">
+        <f>IF(MIN(Class_0!Z26,Class_1!Z26,Class_2!Z26) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD79" s="14"/>
+      <c r="AE79" s="14"/>
+      <c r="AF79" s="14"/>
+      <c r="AG79" s="14"/>
+      <c r="AH79" s="14"/>
+      <c r="AI79" s="14"/>
+      <c r="AJ79" s="14"/>
+      <c r="AK79" s="14"/>
+      <c r="AL79" s="14"/>
+      <c r="AM79" s="14"/>
+      <c r="AN79" s="14"/>
+      <c r="AO79" s="14"/>
+      <c r="AP79" s="14"/>
+      <c r="AQ79" s="14"/>
+      <c r="AR79" s="14"/>
+      <c r="AS79" s="14"/>
+      <c r="AT79" s="14"/>
+      <c r="AU79" s="14"/>
+      <c r="AV79" s="14"/>
+      <c r="AW79" s="14"/>
+      <c r="AX79" s="14"/>
+      <c r="AY79" s="14"/>
+      <c r="AZ79" s="14"/>
+      <c r="BA79" s="14"/>
+      <c r="BB79" s="14"/>
+      <c r="BC79" s="14"/>
+      <c r="BD79" s="14"/>
+      <c r="BE79" s="14"/>
+      <c r="BF79" s="15"/>
+    </row>
+    <row r="80" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C80" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D80" s="10">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="E80" s="14" t="str">
+        <f>IF(MIN(Class_0!B27,Class_1!B27,Class_2!B27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F80" s="14" t="str">
+        <f>IF(MIN(Class_0!C27,Class_1!C27,Class_2!C27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G80" s="14" t="str">
+        <f>IF(MIN(Class_0!D27,Class_1!D27,Class_2!D27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H80" s="14" t="str">
+        <f>IF(MIN(Class_0!E27,Class_1!E27,Class_2!E27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I80" s="14" t="str">
+        <f>IF(MIN(Class_0!F27,Class_1!F27,Class_2!F27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J80" s="14" t="str">
+        <f>IF(MIN(Class_0!G27,Class_1!G27,Class_2!G27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K80" s="14" t="str">
+        <f>IF(MIN(Class_0!H27,Class_1!H27,Class_2!H27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L80" s="14" t="str">
+        <f>IF(MIN(Class_0!I27,Class_1!I27,Class_2!I27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M80" s="14" t="str">
+        <f>IF(MIN(Class_0!J27,Class_1!J27,Class_2!J27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N80" s="14" t="str">
+        <f>IF(MIN(Class_0!K27,Class_1!K27,Class_2!K27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O80" s="14" t="str">
+        <f>IF(MIN(Class_0!L27,Class_1!L27,Class_2!L27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P80" s="14" t="str">
+        <f>IF(MIN(Class_0!M27,Class_1!M27,Class_2!M27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q80" s="14" t="str">
+        <f>IF(MIN(Class_0!N27,Class_1!N27,Class_2!N27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R80" s="14" t="str">
+        <f>IF(MIN(Class_0!O27,Class_1!O27,Class_2!O27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S80" s="14" t="str">
+        <f>IF(MIN(Class_0!P27,Class_1!P27,Class_2!P27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T80" s="14" t="str">
+        <f>IF(MIN(Class_0!Q27,Class_1!Q27,Class_2!Q27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U80" s="14" t="str">
+        <f>IF(MIN(Class_0!R27,Class_1!R27,Class_2!R27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V80" s="14" t="str">
+        <f>IF(MIN(Class_0!S27,Class_1!S27,Class_2!S27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W80" s="14" t="str">
+        <f>IF(MIN(Class_0!T27,Class_1!T27,Class_2!T27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X80" s="14" t="str">
+        <f>IF(MIN(Class_0!U27,Class_1!U27,Class_2!U27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y80" s="14" t="str">
+        <f>IF(MIN(Class_0!V27,Class_1!V27,Class_2!V27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z80" s="14" t="str">
+        <f>IF(MIN(Class_0!W27,Class_1!W27,Class_2!W27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA80" s="14" t="str">
+        <f>IF(MIN(Class_0!X27,Class_1!X27,Class_2!X27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB80" s="14" t="str">
+        <f>IF(MIN(Class_0!Y27,Class_1!Y27,Class_2!Y27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC80" s="14" t="str">
+        <f>IF(MIN(Class_0!Z27,Class_1!Z27,Class_2!Z27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD80" s="14" t="str">
+        <f>IF(MIN(Class_0!AA27,Class_1!AA27,Class_2!AA27) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE80" s="14"/>
+      <c r="AF80" s="14"/>
+      <c r="AG80" s="14"/>
+      <c r="AH80" s="14"/>
+      <c r="AI80" s="14"/>
+      <c r="AJ80" s="14"/>
+      <c r="AK80" s="14"/>
+      <c r="AL80" s="14"/>
+      <c r="AM80" s="14"/>
+      <c r="AN80" s="14"/>
+      <c r="AO80" s="14"/>
+      <c r="AP80" s="14"/>
+      <c r="AQ80" s="14"/>
+      <c r="AR80" s="14"/>
+      <c r="AS80" s="14"/>
+      <c r="AT80" s="14"/>
+      <c r="AU80" s="14"/>
+      <c r="AV80" s="14"/>
+      <c r="AW80" s="14"/>
+      <c r="AX80" s="14"/>
+      <c r="AY80" s="14"/>
+      <c r="AZ80" s="14"/>
+      <c r="BA80" s="14"/>
+      <c r="BB80" s="14"/>
+      <c r="BC80" s="14"/>
+      <c r="BD80" s="14"/>
+      <c r="BE80" s="14"/>
+      <c r="BF80" s="15"/>
+    </row>
+    <row r="81" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C81" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" s="10">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="E81" s="14" t="str">
+        <f>IF(MIN(Class_0!B28,Class_1!B28,Class_2!B28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F81" s="14" t="str">
+        <f>IF(MIN(Class_0!C28,Class_1!C28,Class_2!C28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G81" s="14" t="str">
+        <f>IF(MIN(Class_0!D28,Class_1!D28,Class_2!D28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H81" s="14" t="str">
+        <f>IF(MIN(Class_0!E28,Class_1!E28,Class_2!E28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I81" s="14" t="str">
+        <f>IF(MIN(Class_0!F28,Class_1!F28,Class_2!F28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J81" s="14" t="str">
+        <f>IF(MIN(Class_0!G28,Class_1!G28,Class_2!G28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K81" s="14" t="str">
+        <f>IF(MIN(Class_0!H28,Class_1!H28,Class_2!H28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L81" s="14" t="str">
+        <f>IF(MIN(Class_0!I28,Class_1!I28,Class_2!I28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M81" s="14" t="str">
+        <f>IF(MIN(Class_0!J28,Class_1!J28,Class_2!J28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N81" s="14" t="str">
+        <f>IF(MIN(Class_0!K28,Class_1!K28,Class_2!K28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O81" s="14" t="str">
+        <f>IF(MIN(Class_0!L28,Class_1!L28,Class_2!L28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P81" s="14" t="str">
+        <f>IF(MIN(Class_0!M28,Class_1!M28,Class_2!M28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q81" s="14" t="str">
+        <f>IF(MIN(Class_0!N28,Class_1!N28,Class_2!N28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R81" s="14" t="str">
+        <f>IF(MIN(Class_0!O28,Class_1!O28,Class_2!O28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S81" s="14" t="str">
+        <f>IF(MIN(Class_0!P28,Class_1!P28,Class_2!P28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T81" s="14" t="str">
+        <f>IF(MIN(Class_0!Q28,Class_1!Q28,Class_2!Q28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U81" s="14" t="str">
+        <f>IF(MIN(Class_0!R28,Class_1!R28,Class_2!R28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V81" s="14" t="str">
+        <f>IF(MIN(Class_0!S28,Class_1!S28,Class_2!S28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W81" s="14" t="str">
+        <f>IF(MIN(Class_0!T28,Class_1!T28,Class_2!T28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X81" s="14" t="str">
+        <f>IF(MIN(Class_0!U28,Class_1!U28,Class_2!U28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y81" s="14" t="str">
+        <f>IF(MIN(Class_0!V28,Class_1!V28,Class_2!V28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z81" s="14" t="str">
+        <f>IF(MIN(Class_0!W28,Class_1!W28,Class_2!W28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA81" s="14" t="str">
+        <f>IF(MIN(Class_0!X28,Class_1!X28,Class_2!X28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB81" s="14" t="str">
+        <f>IF(MIN(Class_0!Y28,Class_1!Y28,Class_2!Y28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC81" s="14" t="str">
+        <f>IF(MIN(Class_0!Z28,Class_1!Z28,Class_2!Z28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD81" s="14" t="str">
+        <f>IF(MIN(Class_0!AA28,Class_1!AA28,Class_2!AA28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE81" s="14" t="str">
+        <f>IF(MIN(Class_0!AB28,Class_1!AB28,Class_2!AB28) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF81" s="14"/>
+      <c r="AG81" s="14"/>
+      <c r="AH81" s="14"/>
+      <c r="AI81" s="14"/>
+      <c r="AJ81" s="14"/>
+      <c r="AK81" s="14"/>
+      <c r="AL81" s="14"/>
+      <c r="AM81" s="14"/>
+      <c r="AN81" s="14"/>
+      <c r="AO81" s="14"/>
+      <c r="AP81" s="14"/>
+      <c r="AQ81" s="14"/>
+      <c r="AR81" s="14"/>
+      <c r="AS81" s="14"/>
+      <c r="AT81" s="14"/>
+      <c r="AU81" s="14"/>
+      <c r="AV81" s="14"/>
+      <c r="AW81" s="14"/>
+      <c r="AX81" s="14"/>
+      <c r="AY81" s="14"/>
+      <c r="AZ81" s="14"/>
+      <c r="BA81" s="14"/>
+      <c r="BB81" s="14"/>
+      <c r="BC81" s="14"/>
+      <c r="BD81" s="14"/>
+      <c r="BE81" s="14"/>
+      <c r="BF81" s="15"/>
+    </row>
+    <row r="82" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C82" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" s="10">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="E82" s="14" t="str">
+        <f>IF(MIN(Class_0!B29,Class_1!B29,Class_2!B29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F82" s="14" t="str">
+        <f>IF(MIN(Class_0!C29,Class_1!C29,Class_2!C29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G82" s="14" t="str">
+        <f>IF(MIN(Class_0!D29,Class_1!D29,Class_2!D29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H82" s="14" t="str">
+        <f>IF(MIN(Class_0!E29,Class_1!E29,Class_2!E29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I82" s="14" t="str">
+        <f>IF(MIN(Class_0!F29,Class_1!F29,Class_2!F29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J82" s="14" t="str">
+        <f>IF(MIN(Class_0!G29,Class_1!G29,Class_2!G29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K82" s="14" t="str">
+        <f>IF(MIN(Class_0!H29,Class_1!H29,Class_2!H29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L82" s="14" t="str">
+        <f>IF(MIN(Class_0!I29,Class_1!I29,Class_2!I29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M82" s="14" t="str">
+        <f>IF(MIN(Class_0!J29,Class_1!J29,Class_2!J29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N82" s="14" t="str">
+        <f>IF(MIN(Class_0!K29,Class_1!K29,Class_2!K29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O82" s="14" t="str">
+        <f>IF(MIN(Class_0!L29,Class_1!L29,Class_2!L29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P82" s="14" t="str">
+        <f>IF(MIN(Class_0!M29,Class_1!M29,Class_2!M29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q82" s="14" t="str">
+        <f>IF(MIN(Class_0!N29,Class_1!N29,Class_2!N29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R82" s="14" t="str">
+        <f>IF(MIN(Class_0!O29,Class_1!O29,Class_2!O29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S82" s="14" t="str">
+        <f>IF(MIN(Class_0!P29,Class_1!P29,Class_2!P29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T82" s="14" t="str">
+        <f>IF(MIN(Class_0!Q29,Class_1!Q29,Class_2!Q29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U82" s="14" t="str">
+        <f>IF(MIN(Class_0!R29,Class_1!R29,Class_2!R29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V82" s="14" t="str">
+        <f>IF(MIN(Class_0!S29,Class_1!S29,Class_2!S29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W82" s="14" t="str">
+        <f>IF(MIN(Class_0!T29,Class_1!T29,Class_2!T29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X82" s="14" t="str">
+        <f>IF(MIN(Class_0!U29,Class_1!U29,Class_2!U29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y82" s="14" t="str">
+        <f>IF(MIN(Class_0!V29,Class_1!V29,Class_2!V29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z82" s="14" t="str">
+        <f>IF(MIN(Class_0!W29,Class_1!W29,Class_2!W29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA82" s="14" t="str">
+        <f>IF(MIN(Class_0!X29,Class_1!X29,Class_2!X29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB82" s="14" t="str">
+        <f>IF(MIN(Class_0!Y29,Class_1!Y29,Class_2!Y29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC82" s="14" t="str">
+        <f>IF(MIN(Class_0!Z29,Class_1!Z29,Class_2!Z29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD82" s="14" t="str">
+        <f>IF(MIN(Class_0!AA29,Class_1!AA29,Class_2!AA29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE82" s="14" t="str">
+        <f>IF(MIN(Class_0!AB29,Class_1!AB29,Class_2!AB29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF82" s="14" t="str">
+        <f>IF(MIN(Class_0!AC29,Class_1!AC29,Class_2!AC29) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG82" s="14"/>
+      <c r="AH82" s="14"/>
+      <c r="AI82" s="14"/>
+      <c r="AJ82" s="14"/>
+      <c r="AK82" s="14"/>
+      <c r="AL82" s="14"/>
+      <c r="AM82" s="14"/>
+      <c r="AN82" s="14"/>
+      <c r="AO82" s="14"/>
+      <c r="AP82" s="14"/>
+      <c r="AQ82" s="14"/>
+      <c r="AR82" s="14"/>
+      <c r="AS82" s="14"/>
+      <c r="AT82" s="14"/>
+      <c r="AU82" s="14"/>
+      <c r="AV82" s="14"/>
+      <c r="AW82" s="14"/>
+      <c r="AX82" s="14"/>
+      <c r="AY82" s="14"/>
+      <c r="AZ82" s="14"/>
+      <c r="BA82" s="14"/>
+      <c r="BB82" s="14"/>
+      <c r="BC82" s="14"/>
+      <c r="BD82" s="14"/>
+      <c r="BE82" s="14"/>
+      <c r="BF82" s="15"/>
+    </row>
+    <row r="83" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C83" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D83" s="10">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="E83" s="14" t="str">
+        <f>IF(MIN(Class_0!B30,Class_1!B30,Class_2!B30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F83" s="14" t="str">
+        <f>IF(MIN(Class_0!C30,Class_1!C30,Class_2!C30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G83" s="14" t="str">
+        <f>IF(MIN(Class_0!D30,Class_1!D30,Class_2!D30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H83" s="14" t="str">
+        <f>IF(MIN(Class_0!E30,Class_1!E30,Class_2!E30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I83" s="14" t="str">
+        <f>IF(MIN(Class_0!F30,Class_1!F30,Class_2!F30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J83" s="14" t="str">
+        <f>IF(MIN(Class_0!G30,Class_1!G30,Class_2!G30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K83" s="14" t="str">
+        <f>IF(MIN(Class_0!H30,Class_1!H30,Class_2!H30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L83" s="14" t="str">
+        <f>IF(MIN(Class_0!I30,Class_1!I30,Class_2!I30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M83" s="14" t="str">
+        <f>IF(MIN(Class_0!J30,Class_1!J30,Class_2!J30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N83" s="14" t="str">
+        <f>IF(MIN(Class_0!K30,Class_1!K30,Class_2!K30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O83" s="14" t="str">
+        <f>IF(MIN(Class_0!L30,Class_1!L30,Class_2!L30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P83" s="14" t="str">
+        <f>IF(MIN(Class_0!M30,Class_1!M30,Class_2!M30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q83" s="14" t="str">
+        <f>IF(MIN(Class_0!N30,Class_1!N30,Class_2!N30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R83" s="14" t="str">
+        <f>IF(MIN(Class_0!O30,Class_1!O30,Class_2!O30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S83" s="14" t="str">
+        <f>IF(MIN(Class_0!P30,Class_1!P30,Class_2!P30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T83" s="14" t="str">
+        <f>IF(MIN(Class_0!Q30,Class_1!Q30,Class_2!Q30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U83" s="14" t="str">
+        <f>IF(MIN(Class_0!R30,Class_1!R30,Class_2!R30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V83" s="14" t="str">
+        <f>IF(MIN(Class_0!S30,Class_1!S30,Class_2!S30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W83" s="14" t="str">
+        <f>IF(MIN(Class_0!T30,Class_1!T30,Class_2!T30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X83" s="14" t="str">
+        <f>IF(MIN(Class_0!U30,Class_1!U30,Class_2!U30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y83" s="14" t="str">
+        <f>IF(MIN(Class_0!V30,Class_1!V30,Class_2!V30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z83" s="14" t="str">
+        <f>IF(MIN(Class_0!W30,Class_1!W30,Class_2!W30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA83" s="14" t="str">
+        <f>IF(MIN(Class_0!X30,Class_1!X30,Class_2!X30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB83" s="14" t="str">
+        <f>IF(MIN(Class_0!Y30,Class_1!Y30,Class_2!Y30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC83" s="14" t="str">
+        <f>IF(MIN(Class_0!Z30,Class_1!Z30,Class_2!Z30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD83" s="14" t="str">
+        <f>IF(MIN(Class_0!AA30,Class_1!AA30,Class_2!AA30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE83" s="14" t="str">
+        <f>IF(MIN(Class_0!AB30,Class_1!AB30,Class_2!AB30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF83" s="14" t="str">
+        <f>IF(MIN(Class_0!AC30,Class_1!AC30,Class_2!AC30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG83" s="14" t="str">
+        <f>IF(MIN(Class_0!AD30,Class_1!AD30,Class_2!AD30) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH83" s="14"/>
+      <c r="AI83" s="14"/>
+      <c r="AJ83" s="14"/>
+      <c r="AK83" s="14"/>
+      <c r="AL83" s="14"/>
+      <c r="AM83" s="14"/>
+      <c r="AN83" s="14"/>
+      <c r="AO83" s="14"/>
+      <c r="AP83" s="14"/>
+      <c r="AQ83" s="14"/>
+      <c r="AR83" s="14"/>
+      <c r="AS83" s="14"/>
+      <c r="AT83" s="14"/>
+      <c r="AU83" s="14"/>
+      <c r="AV83" s="14"/>
+      <c r="AW83" s="14"/>
+      <c r="AX83" s="14"/>
+      <c r="AY83" s="14"/>
+      <c r="AZ83" s="14"/>
+      <c r="BA83" s="14"/>
+      <c r="BB83" s="14"/>
+      <c r="BC83" s="14"/>
+      <c r="BD83" s="14"/>
+      <c r="BE83" s="14"/>
+      <c r="BF83" s="15"/>
+    </row>
+    <row r="84" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C84" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D84" s="10">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="E84" s="14" t="str">
+        <f>IF(MIN(Class_0!B31,Class_1!B31,Class_2!B31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F84" s="14" t="str">
+        <f>IF(MIN(Class_0!C31,Class_1!C31,Class_2!C31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G84" s="14" t="str">
+        <f>IF(MIN(Class_0!D31,Class_1!D31,Class_2!D31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H84" s="14" t="str">
+        <f>IF(MIN(Class_0!E31,Class_1!E31,Class_2!E31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I84" s="14" t="str">
+        <f>IF(MIN(Class_0!F31,Class_1!F31,Class_2!F31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J84" s="14" t="str">
+        <f>IF(MIN(Class_0!G31,Class_1!G31,Class_2!G31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K84" s="14" t="str">
+        <f>IF(MIN(Class_0!H31,Class_1!H31,Class_2!H31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L84" s="14" t="str">
+        <f>IF(MIN(Class_0!I31,Class_1!I31,Class_2!I31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M84" s="14" t="str">
+        <f>IF(MIN(Class_0!J31,Class_1!J31,Class_2!J31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N84" s="14" t="str">
+        <f>IF(MIN(Class_0!K31,Class_1!K31,Class_2!K31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O84" s="14" t="str">
+        <f>IF(MIN(Class_0!L31,Class_1!L31,Class_2!L31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P84" s="14" t="str">
+        <f>IF(MIN(Class_0!M31,Class_1!M31,Class_2!M31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q84" s="14" t="str">
+        <f>IF(MIN(Class_0!N31,Class_1!N31,Class_2!N31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R84" s="14" t="str">
+        <f>IF(MIN(Class_0!O31,Class_1!O31,Class_2!O31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S84" s="14" t="str">
+        <f>IF(MIN(Class_0!P31,Class_1!P31,Class_2!P31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T84" s="14" t="str">
+        <f>IF(MIN(Class_0!Q31,Class_1!Q31,Class_2!Q31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U84" s="14" t="str">
+        <f>IF(MIN(Class_0!R31,Class_1!R31,Class_2!R31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V84" s="14" t="str">
+        <f>IF(MIN(Class_0!S31,Class_1!S31,Class_2!S31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W84" s="14" t="str">
+        <f>IF(MIN(Class_0!T31,Class_1!T31,Class_2!T31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X84" s="14" t="str">
+        <f>IF(MIN(Class_0!U31,Class_1!U31,Class_2!U31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y84" s="14" t="str">
+        <f>IF(MIN(Class_0!V31,Class_1!V31,Class_2!V31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z84" s="14" t="str">
+        <f>IF(MIN(Class_0!W31,Class_1!W31,Class_2!W31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA84" s="14" t="str">
+        <f>IF(MIN(Class_0!X31,Class_1!X31,Class_2!X31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB84" s="14" t="str">
+        <f>IF(MIN(Class_0!Y31,Class_1!Y31,Class_2!Y31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC84" s="14" t="str">
+        <f>IF(MIN(Class_0!Z31,Class_1!Z31,Class_2!Z31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD84" s="14" t="str">
+        <f>IF(MIN(Class_0!AA31,Class_1!AA31,Class_2!AA31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE84" s="14" t="str">
+        <f>IF(MIN(Class_0!AB31,Class_1!AB31,Class_2!AB31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF84" s="14" t="str">
+        <f>IF(MIN(Class_0!AC31,Class_1!AC31,Class_2!AC31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG84" s="14" t="str">
+        <f>IF(MIN(Class_0!AD31,Class_1!AD31,Class_2!AD31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH84" s="14" t="str">
+        <f>IF(MIN(Class_0!AE31,Class_1!AE31,Class_2!AE31) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI84" s="14"/>
+      <c r="AJ84" s="14"/>
+      <c r="AK84" s="14"/>
+      <c r="AL84" s="14"/>
+      <c r="AM84" s="14"/>
+      <c r="AN84" s="14"/>
+      <c r="AO84" s="14"/>
+      <c r="AP84" s="14"/>
+      <c r="AQ84" s="14"/>
+      <c r="AR84" s="14"/>
+      <c r="AS84" s="14"/>
+      <c r="AT84" s="14"/>
+      <c r="AU84" s="14"/>
+      <c r="AV84" s="14"/>
+      <c r="AW84" s="14"/>
+      <c r="AX84" s="14"/>
+      <c r="AY84" s="14"/>
+      <c r="AZ84" s="14"/>
+      <c r="BA84" s="14"/>
+      <c r="BB84" s="14"/>
+      <c r="BC84" s="14"/>
+      <c r="BD84" s="14"/>
+      <c r="BE84" s="14"/>
+      <c r="BF84" s="15"/>
+    </row>
+    <row r="85" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C85" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" s="10">
+        <f t="shared" si="6"/>
+        <v>31</v>
+      </c>
+      <c r="E85" s="14" t="str">
+        <f>IF(MIN(Class_0!B32,Class_1!B32,Class_2!B32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F85" s="14" t="str">
+        <f>IF(MIN(Class_0!C32,Class_1!C32,Class_2!C32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G85" s="14" t="str">
+        <f>IF(MIN(Class_0!D32,Class_1!D32,Class_2!D32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H85" s="14" t="str">
+        <f>IF(MIN(Class_0!E32,Class_1!E32,Class_2!E32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I85" s="14" t="str">
+        <f>IF(MIN(Class_0!F32,Class_1!F32,Class_2!F32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J85" s="14" t="str">
+        <f>IF(MIN(Class_0!G32,Class_1!G32,Class_2!G32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K85" s="14" t="str">
+        <f>IF(MIN(Class_0!H32,Class_1!H32,Class_2!H32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L85" s="14" t="str">
+        <f>IF(MIN(Class_0!I32,Class_1!I32,Class_2!I32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M85" s="14" t="str">
+        <f>IF(MIN(Class_0!J32,Class_1!J32,Class_2!J32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N85" s="14" t="str">
+        <f>IF(MIN(Class_0!K32,Class_1!K32,Class_2!K32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O85" s="14" t="str">
+        <f>IF(MIN(Class_0!L32,Class_1!L32,Class_2!L32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P85" s="14" t="str">
+        <f>IF(MIN(Class_0!M32,Class_1!M32,Class_2!M32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q85" s="14" t="str">
+        <f>IF(MIN(Class_0!N32,Class_1!N32,Class_2!N32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R85" s="14" t="str">
+        <f>IF(MIN(Class_0!O32,Class_1!O32,Class_2!O32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S85" s="14" t="str">
+        <f>IF(MIN(Class_0!P32,Class_1!P32,Class_2!P32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T85" s="14" t="str">
+        <f>IF(MIN(Class_0!Q32,Class_1!Q32,Class_2!Q32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U85" s="14" t="str">
+        <f>IF(MIN(Class_0!R32,Class_1!R32,Class_2!R32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V85" s="14" t="str">
+        <f>IF(MIN(Class_0!S32,Class_1!S32,Class_2!S32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W85" s="14" t="str">
+        <f>IF(MIN(Class_0!T32,Class_1!T32,Class_2!T32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X85" s="14" t="str">
+        <f>IF(MIN(Class_0!U32,Class_1!U32,Class_2!U32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y85" s="14" t="str">
+        <f>IF(MIN(Class_0!V32,Class_1!V32,Class_2!V32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z85" s="14" t="str">
+        <f>IF(MIN(Class_0!W32,Class_1!W32,Class_2!W32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA85" s="14" t="str">
+        <f>IF(MIN(Class_0!X32,Class_1!X32,Class_2!X32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB85" s="14" t="str">
+        <f>IF(MIN(Class_0!Y32,Class_1!Y32,Class_2!Y32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC85" s="14" t="str">
+        <f>IF(MIN(Class_0!Z32,Class_1!Z32,Class_2!Z32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD85" s="14" t="str">
+        <f>IF(MIN(Class_0!AA32,Class_1!AA32,Class_2!AA32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE85" s="14" t="str">
+        <f>IF(MIN(Class_0!AB32,Class_1!AB32,Class_2!AB32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF85" s="14" t="str">
+        <f>IF(MIN(Class_0!AC32,Class_1!AC32,Class_2!AC32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG85" s="14" t="str">
+        <f>IF(MIN(Class_0!AD32,Class_1!AD32,Class_2!AD32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH85" s="14" t="str">
+        <f>IF(MIN(Class_0!AE32,Class_1!AE32,Class_2!AE32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI85" s="14" t="str">
+        <f>IF(MIN(Class_0!AF32,Class_1!AF32,Class_2!AF32) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ85" s="14"/>
+      <c r="AK85" s="14"/>
+      <c r="AL85" s="14"/>
+      <c r="AM85" s="14"/>
+      <c r="AN85" s="14"/>
+      <c r="AO85" s="14"/>
+      <c r="AP85" s="14"/>
+      <c r="AQ85" s="14"/>
+      <c r="AR85" s="14"/>
+      <c r="AS85" s="14"/>
+      <c r="AT85" s="14"/>
+      <c r="AU85" s="14"/>
+      <c r="AV85" s="14"/>
+      <c r="AW85" s="14"/>
+      <c r="AX85" s="14"/>
+      <c r="AY85" s="14"/>
+      <c r="AZ85" s="14"/>
+      <c r="BA85" s="14"/>
+      <c r="BB85" s="14"/>
+      <c r="BC85" s="14"/>
+      <c r="BD85" s="14"/>
+      <c r="BE85" s="14"/>
+      <c r="BF85" s="15"/>
+    </row>
+    <row r="86" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C86" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D86" s="10">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="E86" s="14" t="str">
+        <f>IF(MIN(Class_0!B33,Class_1!B33,Class_2!B33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F86" s="14" t="str">
+        <f>IF(MIN(Class_0!C33,Class_1!C33,Class_2!C33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G86" s="14" t="str">
+        <f>IF(MIN(Class_0!D33,Class_1!D33,Class_2!D33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H86" s="14" t="str">
+        <f>IF(MIN(Class_0!E33,Class_1!E33,Class_2!E33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I86" s="14" t="str">
+        <f>IF(MIN(Class_0!F33,Class_1!F33,Class_2!F33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J86" s="14" t="str">
+        <f>IF(MIN(Class_0!G33,Class_1!G33,Class_2!G33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K86" s="14" t="str">
+        <f>IF(MIN(Class_0!H33,Class_1!H33,Class_2!H33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L86" s="14" t="str">
+        <f>IF(MIN(Class_0!I33,Class_1!I33,Class_2!I33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M86" s="14" t="str">
+        <f>IF(MIN(Class_0!J33,Class_1!J33,Class_2!J33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N86" s="14" t="str">
+        <f>IF(MIN(Class_0!K33,Class_1!K33,Class_2!K33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O86" s="14" t="str">
+        <f>IF(MIN(Class_0!L33,Class_1!L33,Class_2!L33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P86" s="14" t="str">
+        <f>IF(MIN(Class_0!M33,Class_1!M33,Class_2!M33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q86" s="14" t="str">
+        <f>IF(MIN(Class_0!N33,Class_1!N33,Class_2!N33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R86" s="14" t="str">
+        <f>IF(MIN(Class_0!O33,Class_1!O33,Class_2!O33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S86" s="14" t="str">
+        <f>IF(MIN(Class_0!P33,Class_1!P33,Class_2!P33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T86" s="14" t="str">
+        <f>IF(MIN(Class_0!Q33,Class_1!Q33,Class_2!Q33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U86" s="14" t="str">
+        <f>IF(MIN(Class_0!R33,Class_1!R33,Class_2!R33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V86" s="14" t="str">
+        <f>IF(MIN(Class_0!S33,Class_1!S33,Class_2!S33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W86" s="14" t="str">
+        <f>IF(MIN(Class_0!T33,Class_1!T33,Class_2!T33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X86" s="14" t="str">
+        <f>IF(MIN(Class_0!U33,Class_1!U33,Class_2!U33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y86" s="14" t="str">
+        <f>IF(MIN(Class_0!V33,Class_1!V33,Class_2!V33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z86" s="14" t="str">
+        <f>IF(MIN(Class_0!W33,Class_1!W33,Class_2!W33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA86" s="14" t="str">
+        <f>IF(MIN(Class_0!X33,Class_1!X33,Class_2!X33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB86" s="14" t="str">
+        <f>IF(MIN(Class_0!Y33,Class_1!Y33,Class_2!Y33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC86" s="14" t="str">
+        <f>IF(MIN(Class_0!Z33,Class_1!Z33,Class_2!Z33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD86" s="14" t="str">
+        <f>IF(MIN(Class_0!AA33,Class_1!AA33,Class_2!AA33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE86" s="14" t="str">
+        <f>IF(MIN(Class_0!AB33,Class_1!AB33,Class_2!AB33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF86" s="14" t="str">
+        <f>IF(MIN(Class_0!AC33,Class_1!AC33,Class_2!AC33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG86" s="14" t="str">
+        <f>IF(MIN(Class_0!AD33,Class_1!AD33,Class_2!AD33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH86" s="14" t="str">
+        <f>IF(MIN(Class_0!AE33,Class_1!AE33,Class_2!AE33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI86" s="14" t="str">
+        <f>IF(MIN(Class_0!AF33,Class_1!AF33,Class_2!AF33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ86" s="14" t="str">
+        <f>IF(MIN(Class_0!AG33,Class_1!AG33,Class_2!AG33) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK86" s="14"/>
+      <c r="AL86" s="14"/>
+      <c r="AM86" s="14"/>
+      <c r="AN86" s="14"/>
+      <c r="AO86" s="14"/>
+      <c r="AP86" s="14"/>
+      <c r="AQ86" s="14"/>
+      <c r="AR86" s="14"/>
+      <c r="AS86" s="14"/>
+      <c r="AT86" s="14"/>
+      <c r="AU86" s="14"/>
+      <c r="AV86" s="14"/>
+      <c r="AW86" s="14"/>
+      <c r="AX86" s="14"/>
+      <c r="AY86" s="14"/>
+      <c r="AZ86" s="14"/>
+      <c r="BA86" s="14"/>
+      <c r="BB86" s="14"/>
+      <c r="BC86" s="14"/>
+      <c r="BD86" s="14"/>
+      <c r="BE86" s="14"/>
+      <c r="BF86" s="15"/>
+    </row>
+    <row r="87" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C87" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D87" s="10">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="E87" s="14" t="str">
+        <f>IF(MIN(Class_0!B34,Class_1!B34,Class_2!B34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F87" s="14" t="str">
+        <f>IF(MIN(Class_0!C34,Class_1!C34,Class_2!C34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G87" s="14" t="str">
+        <f>IF(MIN(Class_0!D34,Class_1!D34,Class_2!D34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H87" s="14" t="str">
+        <f>IF(MIN(Class_0!E34,Class_1!E34,Class_2!E34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I87" s="14" t="str">
+        <f>IF(MIN(Class_0!F34,Class_1!F34,Class_2!F34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J87" s="14" t="str">
+        <f>IF(MIN(Class_0!G34,Class_1!G34,Class_2!G34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K87" s="14" t="str">
+        <f>IF(MIN(Class_0!H34,Class_1!H34,Class_2!H34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L87" s="14" t="str">
+        <f>IF(MIN(Class_0!I34,Class_1!I34,Class_2!I34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M87" s="14" t="str">
+        <f>IF(MIN(Class_0!J34,Class_1!J34,Class_2!J34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N87" s="14" t="str">
+        <f>IF(MIN(Class_0!K34,Class_1!K34,Class_2!K34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O87" s="14" t="str">
+        <f>IF(MIN(Class_0!L34,Class_1!L34,Class_2!L34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P87" s="14" t="str">
+        <f>IF(MIN(Class_0!M34,Class_1!M34,Class_2!M34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q87" s="14" t="str">
+        <f>IF(MIN(Class_0!N34,Class_1!N34,Class_2!N34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R87" s="14" t="str">
+        <f>IF(MIN(Class_0!O34,Class_1!O34,Class_2!O34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S87" s="14" t="str">
+        <f>IF(MIN(Class_0!P34,Class_1!P34,Class_2!P34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T87" s="14" t="str">
+        <f>IF(MIN(Class_0!Q34,Class_1!Q34,Class_2!Q34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U87" s="14" t="str">
+        <f>IF(MIN(Class_0!R34,Class_1!R34,Class_2!R34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V87" s="14" t="str">
+        <f>IF(MIN(Class_0!S34,Class_1!S34,Class_2!S34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W87" s="14" t="str">
+        <f>IF(MIN(Class_0!T34,Class_1!T34,Class_2!T34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X87" s="14" t="str">
+        <f>IF(MIN(Class_0!U34,Class_1!U34,Class_2!U34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y87" s="14" t="str">
+        <f>IF(MIN(Class_0!V34,Class_1!V34,Class_2!V34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z87" s="14" t="str">
+        <f>IF(MIN(Class_0!W34,Class_1!W34,Class_2!W34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA87" s="14" t="str">
+        <f>IF(MIN(Class_0!X34,Class_1!X34,Class_2!X34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB87" s="14" t="str">
+        <f>IF(MIN(Class_0!Y34,Class_1!Y34,Class_2!Y34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC87" s="14" t="str">
+        <f>IF(MIN(Class_0!Z34,Class_1!Z34,Class_2!Z34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD87" s="14" t="str">
+        <f>IF(MIN(Class_0!AA34,Class_1!AA34,Class_2!AA34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE87" s="14" t="str">
+        <f>IF(MIN(Class_0!AB34,Class_1!AB34,Class_2!AB34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF87" s="14" t="str">
+        <f>IF(MIN(Class_0!AC34,Class_1!AC34,Class_2!AC34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG87" s="14" t="str">
+        <f>IF(MIN(Class_0!AD34,Class_1!AD34,Class_2!AD34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH87" s="14" t="str">
+        <f>IF(MIN(Class_0!AE34,Class_1!AE34,Class_2!AE34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI87" s="14" t="str">
+        <f>IF(MIN(Class_0!AF34,Class_1!AF34,Class_2!AF34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ87" s="14" t="str">
+        <f>IF(MIN(Class_0!AG34,Class_1!AG34,Class_2!AG34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK87" s="14" t="str">
+        <f>IF(MIN(Class_0!AH34,Class_1!AH34,Class_2!AH34) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL87" s="14"/>
+      <c r="AM87" s="14"/>
+      <c r="AN87" s="14"/>
+      <c r="AO87" s="14"/>
+      <c r="AP87" s="14"/>
+      <c r="AQ87" s="14"/>
+      <c r="AR87" s="14"/>
+      <c r="AS87" s="14"/>
+      <c r="AT87" s="14"/>
+      <c r="AU87" s="14"/>
+      <c r="AV87" s="14"/>
+      <c r="AW87" s="14"/>
+      <c r="AX87" s="14"/>
+      <c r="AY87" s="14"/>
+      <c r="AZ87" s="14"/>
+      <c r="BA87" s="14"/>
+      <c r="BB87" s="14"/>
+      <c r="BC87" s="14"/>
+      <c r="BD87" s="14"/>
+      <c r="BE87" s="14"/>
+      <c r="BF87" s="15"/>
+    </row>
+    <row r="88" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C88" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D88" s="10">
+        <f t="shared" si="6"/>
+        <v>34</v>
+      </c>
+      <c r="E88" s="14" t="str">
+        <f>IF(MIN(Class_0!B35,Class_1!B35,Class_2!B35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F88" s="14" t="str">
+        <f>IF(MIN(Class_0!C35,Class_1!C35,Class_2!C35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G88" s="14" t="str">
+        <f>IF(MIN(Class_0!D35,Class_1!D35,Class_2!D35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H88" s="14" t="str">
+        <f>IF(MIN(Class_0!E35,Class_1!E35,Class_2!E35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I88" s="14" t="str">
+        <f>IF(MIN(Class_0!F35,Class_1!F35,Class_2!F35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J88" s="14" t="str">
+        <f>IF(MIN(Class_0!G35,Class_1!G35,Class_2!G35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K88" s="14" t="str">
+        <f>IF(MIN(Class_0!H35,Class_1!H35,Class_2!H35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L88" s="14" t="str">
+        <f>IF(MIN(Class_0!I35,Class_1!I35,Class_2!I35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M88" s="14" t="str">
+        <f>IF(MIN(Class_0!J35,Class_1!J35,Class_2!J35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N88" s="14" t="str">
+        <f>IF(MIN(Class_0!K35,Class_1!K35,Class_2!K35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O88" s="14" t="str">
+        <f>IF(MIN(Class_0!L35,Class_1!L35,Class_2!L35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P88" s="14" t="str">
+        <f>IF(MIN(Class_0!M35,Class_1!M35,Class_2!M35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q88" s="14" t="str">
+        <f>IF(MIN(Class_0!N35,Class_1!N35,Class_2!N35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R88" s="14" t="str">
+        <f>IF(MIN(Class_0!O35,Class_1!O35,Class_2!O35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S88" s="14" t="str">
+        <f>IF(MIN(Class_0!P35,Class_1!P35,Class_2!P35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T88" s="14" t="str">
+        <f>IF(MIN(Class_0!Q35,Class_1!Q35,Class_2!Q35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U88" s="14" t="str">
+        <f>IF(MIN(Class_0!R35,Class_1!R35,Class_2!R35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V88" s="14" t="str">
+        <f>IF(MIN(Class_0!S35,Class_1!S35,Class_2!S35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W88" s="14" t="str">
+        <f>IF(MIN(Class_0!T35,Class_1!T35,Class_2!T35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X88" s="14" t="str">
+        <f>IF(MIN(Class_0!U35,Class_1!U35,Class_2!U35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y88" s="14" t="str">
+        <f>IF(MIN(Class_0!V35,Class_1!V35,Class_2!V35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z88" s="14" t="str">
+        <f>IF(MIN(Class_0!W35,Class_1!W35,Class_2!W35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA88" s="14" t="str">
+        <f>IF(MIN(Class_0!X35,Class_1!X35,Class_2!X35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB88" s="14" t="str">
+        <f>IF(MIN(Class_0!Y35,Class_1!Y35,Class_2!Y35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC88" s="14" t="str">
+        <f>IF(MIN(Class_0!Z35,Class_1!Z35,Class_2!Z35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD88" s="14" t="str">
+        <f>IF(MIN(Class_0!AA35,Class_1!AA35,Class_2!AA35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE88" s="14" t="str">
+        <f>IF(MIN(Class_0!AB35,Class_1!AB35,Class_2!AB35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF88" s="14" t="str">
+        <f>IF(MIN(Class_0!AC35,Class_1!AC35,Class_2!AC35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG88" s="14" t="str">
+        <f>IF(MIN(Class_0!AD35,Class_1!AD35,Class_2!AD35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH88" s="14" t="str">
+        <f>IF(MIN(Class_0!AE35,Class_1!AE35,Class_2!AE35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI88" s="14" t="str">
+        <f>IF(MIN(Class_0!AF35,Class_1!AF35,Class_2!AF35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ88" s="14" t="str">
+        <f>IF(MIN(Class_0!AG35,Class_1!AG35,Class_2!AG35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK88" s="14" t="str">
+        <f>IF(MIN(Class_0!AH35,Class_1!AH35,Class_2!AH35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL88" s="14" t="str">
+        <f>IF(MIN(Class_0!AI35,Class_1!AI35,Class_2!AI35) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM88" s="14"/>
+      <c r="AN88" s="14"/>
+      <c r="AO88" s="14"/>
+      <c r="AP88" s="14"/>
+      <c r="AQ88" s="14"/>
+      <c r="AR88" s="14"/>
+      <c r="AS88" s="14"/>
+      <c r="AT88" s="14"/>
+      <c r="AU88" s="14"/>
+      <c r="AV88" s="14"/>
+      <c r="AW88" s="14"/>
+      <c r="AX88" s="14"/>
+      <c r="AY88" s="14"/>
+      <c r="AZ88" s="14"/>
+      <c r="BA88" s="14"/>
+      <c r="BB88" s="14"/>
+      <c r="BC88" s="14"/>
+      <c r="BD88" s="14"/>
+      <c r="BE88" s="14"/>
+      <c r="BF88" s="15"/>
+    </row>
+    <row r="89" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C89" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89" s="10">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="E89" s="14" t="str">
+        <f>IF(MIN(Class_0!B36,Class_1!B36,Class_2!B36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F89" s="14" t="str">
+        <f>IF(MIN(Class_0!C36,Class_1!C36,Class_2!C36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G89" s="14" t="str">
+        <f>IF(MIN(Class_0!D36,Class_1!D36,Class_2!D36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H89" s="14" t="str">
+        <f>IF(MIN(Class_0!E36,Class_1!E36,Class_2!E36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I89" s="14" t="str">
+        <f>IF(MIN(Class_0!F36,Class_1!F36,Class_2!F36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J89" s="14" t="str">
+        <f>IF(MIN(Class_0!G36,Class_1!G36,Class_2!G36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K89" s="14" t="str">
+        <f>IF(MIN(Class_0!H36,Class_1!H36,Class_2!H36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L89" s="14" t="str">
+        <f>IF(MIN(Class_0!I36,Class_1!I36,Class_2!I36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M89" s="14" t="str">
+        <f>IF(MIN(Class_0!J36,Class_1!J36,Class_2!J36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N89" s="14" t="str">
+        <f>IF(MIN(Class_0!K36,Class_1!K36,Class_2!K36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O89" s="14" t="str">
+        <f>IF(MIN(Class_0!L36,Class_1!L36,Class_2!L36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P89" s="14" t="str">
+        <f>IF(MIN(Class_0!M36,Class_1!M36,Class_2!M36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q89" s="14" t="str">
+        <f>IF(MIN(Class_0!N36,Class_1!N36,Class_2!N36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R89" s="14" t="str">
+        <f>IF(MIN(Class_0!O36,Class_1!O36,Class_2!O36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S89" s="14" t="str">
+        <f>IF(MIN(Class_0!P36,Class_1!P36,Class_2!P36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T89" s="14" t="str">
+        <f>IF(MIN(Class_0!Q36,Class_1!Q36,Class_2!Q36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U89" s="14" t="str">
+        <f>IF(MIN(Class_0!R36,Class_1!R36,Class_2!R36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V89" s="14" t="str">
+        <f>IF(MIN(Class_0!S36,Class_1!S36,Class_2!S36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W89" s="14" t="str">
+        <f>IF(MIN(Class_0!T36,Class_1!T36,Class_2!T36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X89" s="14" t="str">
+        <f>IF(MIN(Class_0!U36,Class_1!U36,Class_2!U36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y89" s="14" t="str">
+        <f>IF(MIN(Class_0!V36,Class_1!V36,Class_2!V36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z89" s="14" t="str">
+        <f>IF(MIN(Class_0!W36,Class_1!W36,Class_2!W36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA89" s="14" t="str">
+        <f>IF(MIN(Class_0!X36,Class_1!X36,Class_2!X36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB89" s="14" t="str">
+        <f>IF(MIN(Class_0!Y36,Class_1!Y36,Class_2!Y36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC89" s="14" t="str">
+        <f>IF(MIN(Class_0!Z36,Class_1!Z36,Class_2!Z36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD89" s="14" t="str">
+        <f>IF(MIN(Class_0!AA36,Class_1!AA36,Class_2!AA36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE89" s="14" t="str">
+        <f>IF(MIN(Class_0!AB36,Class_1!AB36,Class_2!AB36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF89" s="14" t="str">
+        <f>IF(MIN(Class_0!AC36,Class_1!AC36,Class_2!AC36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG89" s="14" t="str">
+        <f>IF(MIN(Class_0!AD36,Class_1!AD36,Class_2!AD36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH89" s="14" t="str">
+        <f>IF(MIN(Class_0!AE36,Class_1!AE36,Class_2!AE36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI89" s="14" t="str">
+        <f>IF(MIN(Class_0!AF36,Class_1!AF36,Class_2!AF36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ89" s="14" t="str">
+        <f>IF(MIN(Class_0!AG36,Class_1!AG36,Class_2!AG36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK89" s="14" t="str">
+        <f>IF(MIN(Class_0!AH36,Class_1!AH36,Class_2!AH36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL89" s="14" t="str">
+        <f>IF(MIN(Class_0!AI36,Class_1!AI36,Class_2!AI36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM89" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ36,Class_1!AJ36,Class_2!AJ36) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN89" s="14"/>
+      <c r="AO89" s="14"/>
+      <c r="AP89" s="14"/>
+      <c r="AQ89" s="14"/>
+      <c r="AR89" s="14"/>
+      <c r="AS89" s="14"/>
+      <c r="AT89" s="14"/>
+      <c r="AU89" s="14"/>
+      <c r="AV89" s="14"/>
+      <c r="AW89" s="14"/>
+      <c r="AX89" s="14"/>
+      <c r="AY89" s="14"/>
+      <c r="AZ89" s="14"/>
+      <c r="BA89" s="14"/>
+      <c r="BB89" s="14"/>
+      <c r="BC89" s="14"/>
+      <c r="BD89" s="14"/>
+      <c r="BE89" s="14"/>
+      <c r="BF89" s="15"/>
+    </row>
+    <row r="90" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C90" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D90" s="10">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+      <c r="E90" s="14" t="str">
+        <f>IF(MIN(Class_0!B37,Class_1!B37,Class_2!B37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F90" s="14" t="str">
+        <f>IF(MIN(Class_0!C37,Class_1!C37,Class_2!C37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G90" s="14" t="str">
+        <f>IF(MIN(Class_0!D37,Class_1!D37,Class_2!D37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H90" s="14" t="str">
+        <f>IF(MIN(Class_0!E37,Class_1!E37,Class_2!E37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I90" s="14" t="str">
+        <f>IF(MIN(Class_0!F37,Class_1!F37,Class_2!F37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J90" s="14" t="str">
+        <f>IF(MIN(Class_0!G37,Class_1!G37,Class_2!G37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K90" s="14" t="str">
+        <f>IF(MIN(Class_0!H37,Class_1!H37,Class_2!H37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L90" s="14" t="str">
+        <f>IF(MIN(Class_0!I37,Class_1!I37,Class_2!I37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M90" s="14" t="str">
+        <f>IF(MIN(Class_0!J37,Class_1!J37,Class_2!J37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N90" s="14" t="str">
+        <f>IF(MIN(Class_0!K37,Class_1!K37,Class_2!K37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O90" s="14" t="str">
+        <f>IF(MIN(Class_0!L37,Class_1!L37,Class_2!L37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P90" s="14" t="str">
+        <f>IF(MIN(Class_0!M37,Class_1!M37,Class_2!M37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q90" s="14" t="str">
+        <f>IF(MIN(Class_0!N37,Class_1!N37,Class_2!N37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R90" s="14" t="str">
+        <f>IF(MIN(Class_0!O37,Class_1!O37,Class_2!O37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S90" s="14" t="str">
+        <f>IF(MIN(Class_0!P37,Class_1!P37,Class_2!P37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T90" s="14" t="str">
+        <f>IF(MIN(Class_0!Q37,Class_1!Q37,Class_2!Q37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U90" s="14" t="str">
+        <f>IF(MIN(Class_0!R37,Class_1!R37,Class_2!R37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V90" s="14" t="str">
+        <f>IF(MIN(Class_0!S37,Class_1!S37,Class_2!S37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W90" s="14" t="str">
+        <f>IF(MIN(Class_0!T37,Class_1!T37,Class_2!T37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X90" s="14" t="str">
+        <f>IF(MIN(Class_0!U37,Class_1!U37,Class_2!U37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y90" s="14" t="str">
+        <f>IF(MIN(Class_0!V37,Class_1!V37,Class_2!V37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z90" s="14" t="str">
+        <f>IF(MIN(Class_0!W37,Class_1!W37,Class_2!W37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA90" s="14" t="str">
+        <f>IF(MIN(Class_0!X37,Class_1!X37,Class_2!X37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB90" s="14" t="str">
+        <f>IF(MIN(Class_0!Y37,Class_1!Y37,Class_2!Y37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC90" s="14" t="str">
+        <f>IF(MIN(Class_0!Z37,Class_1!Z37,Class_2!Z37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD90" s="14" t="str">
+        <f>IF(MIN(Class_0!AA37,Class_1!AA37,Class_2!AA37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE90" s="14" t="str">
+        <f>IF(MIN(Class_0!AB37,Class_1!AB37,Class_2!AB37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF90" s="14" t="str">
+        <f>IF(MIN(Class_0!AC37,Class_1!AC37,Class_2!AC37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG90" s="14" t="str">
+        <f>IF(MIN(Class_0!AD37,Class_1!AD37,Class_2!AD37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH90" s="14" t="str">
+        <f>IF(MIN(Class_0!AE37,Class_1!AE37,Class_2!AE37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI90" s="14" t="str">
+        <f>IF(MIN(Class_0!AF37,Class_1!AF37,Class_2!AF37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ90" s="14" t="str">
+        <f>IF(MIN(Class_0!AG37,Class_1!AG37,Class_2!AG37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK90" s="14" t="str">
+        <f>IF(MIN(Class_0!AH37,Class_1!AH37,Class_2!AH37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL90" s="14" t="str">
+        <f>IF(MIN(Class_0!AI37,Class_1!AI37,Class_2!AI37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM90" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ37,Class_1!AJ37,Class_2!AJ37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN90" s="14" t="str">
+        <f>IF(MIN(Class_0!AK37,Class_1!AK37,Class_2!AK37) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO90" s="14"/>
+      <c r="AP90" s="14"/>
+      <c r="AQ90" s="14"/>
+      <c r="AR90" s="14"/>
+      <c r="AS90" s="14"/>
+      <c r="AT90" s="14"/>
+      <c r="AU90" s="14"/>
+      <c r="AV90" s="14"/>
+      <c r="AW90" s="14"/>
+      <c r="AX90" s="14"/>
+      <c r="AY90" s="14"/>
+      <c r="AZ90" s="14"/>
+      <c r="BA90" s="14"/>
+      <c r="BB90" s="14"/>
+      <c r="BC90" s="14"/>
+      <c r="BD90" s="14"/>
+      <c r="BE90" s="14"/>
+      <c r="BF90" s="15"/>
+    </row>
+    <row r="91" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C91" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D91" s="10">
+        <f t="shared" si="6"/>
+        <v>37</v>
+      </c>
+      <c r="E91" s="14" t="str">
+        <f>IF(MIN(Class_0!B38,Class_1!B38,Class_2!B38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F91" s="14" t="str">
+        <f>IF(MIN(Class_0!C38,Class_1!C38,Class_2!C38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G91" s="14" t="str">
+        <f>IF(MIN(Class_0!D38,Class_1!D38,Class_2!D38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H91" s="14" t="str">
+        <f>IF(MIN(Class_0!E38,Class_1!E38,Class_2!E38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I91" s="14" t="str">
+        <f>IF(MIN(Class_0!F38,Class_1!F38,Class_2!F38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J91" s="14" t="str">
+        <f>IF(MIN(Class_0!G38,Class_1!G38,Class_2!G38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K91" s="14" t="str">
+        <f>IF(MIN(Class_0!H38,Class_1!H38,Class_2!H38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L91" s="14" t="str">
+        <f>IF(MIN(Class_0!I38,Class_1!I38,Class_2!I38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M91" s="14" t="str">
+        <f>IF(MIN(Class_0!J38,Class_1!J38,Class_2!J38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N91" s="14" t="str">
+        <f>IF(MIN(Class_0!K38,Class_1!K38,Class_2!K38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O91" s="14" t="str">
+        <f>IF(MIN(Class_0!L38,Class_1!L38,Class_2!L38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P91" s="14" t="str">
+        <f>IF(MIN(Class_0!M38,Class_1!M38,Class_2!M38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q91" s="14" t="str">
+        <f>IF(MIN(Class_0!N38,Class_1!N38,Class_2!N38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R91" s="14" t="str">
+        <f>IF(MIN(Class_0!O38,Class_1!O38,Class_2!O38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S91" s="14" t="str">
+        <f>IF(MIN(Class_0!P38,Class_1!P38,Class_2!P38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T91" s="14" t="str">
+        <f>IF(MIN(Class_0!Q38,Class_1!Q38,Class_2!Q38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U91" s="14" t="str">
+        <f>IF(MIN(Class_0!R38,Class_1!R38,Class_2!R38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V91" s="14" t="str">
+        <f>IF(MIN(Class_0!S38,Class_1!S38,Class_2!S38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W91" s="14" t="str">
+        <f>IF(MIN(Class_0!T38,Class_1!T38,Class_2!T38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X91" s="14" t="str">
+        <f>IF(MIN(Class_0!U38,Class_1!U38,Class_2!U38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y91" s="14" t="str">
+        <f>IF(MIN(Class_0!V38,Class_1!V38,Class_2!V38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z91" s="14" t="str">
+        <f>IF(MIN(Class_0!W38,Class_1!W38,Class_2!W38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA91" s="14" t="str">
+        <f>IF(MIN(Class_0!X38,Class_1!X38,Class_2!X38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB91" s="14" t="str">
+        <f>IF(MIN(Class_0!Y38,Class_1!Y38,Class_2!Y38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC91" s="14" t="str">
+        <f>IF(MIN(Class_0!Z38,Class_1!Z38,Class_2!Z38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD91" s="14" t="str">
+        <f>IF(MIN(Class_0!AA38,Class_1!AA38,Class_2!AA38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE91" s="14" t="str">
+        <f>IF(MIN(Class_0!AB38,Class_1!AB38,Class_2!AB38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF91" s="14" t="str">
+        <f>IF(MIN(Class_0!AC38,Class_1!AC38,Class_2!AC38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG91" s="14" t="str">
+        <f>IF(MIN(Class_0!AD38,Class_1!AD38,Class_2!AD38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH91" s="14" t="str">
+        <f>IF(MIN(Class_0!AE38,Class_1!AE38,Class_2!AE38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI91" s="14" t="str">
+        <f>IF(MIN(Class_0!AF38,Class_1!AF38,Class_2!AF38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ91" s="14" t="str">
+        <f>IF(MIN(Class_0!AG38,Class_1!AG38,Class_2!AG38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK91" s="14" t="str">
+        <f>IF(MIN(Class_0!AH38,Class_1!AH38,Class_2!AH38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL91" s="14" t="str">
+        <f>IF(MIN(Class_0!AI38,Class_1!AI38,Class_2!AI38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM91" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ38,Class_1!AJ38,Class_2!AJ38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN91" s="14" t="str">
+        <f>IF(MIN(Class_0!AK38,Class_1!AK38,Class_2!AK38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO91" s="14" t="str">
+        <f>IF(MIN(Class_0!AL38,Class_1!AL38,Class_2!AL38) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP91" s="14"/>
+      <c r="AQ91" s="14"/>
+      <c r="AR91" s="14"/>
+      <c r="AS91" s="14"/>
+      <c r="AT91" s="14"/>
+      <c r="AU91" s="14"/>
+      <c r="AV91" s="14"/>
+      <c r="AW91" s="14"/>
+      <c r="AX91" s="14"/>
+      <c r="AY91" s="14"/>
+      <c r="AZ91" s="14"/>
+      <c r="BA91" s="14"/>
+      <c r="BB91" s="14"/>
+      <c r="BC91" s="14"/>
+      <c r="BD91" s="14"/>
+      <c r="BE91" s="14"/>
+      <c r="BF91" s="15"/>
+    </row>
+    <row r="92" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C92" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D92" s="10">
+        <f t="shared" si="6"/>
+        <v>38</v>
+      </c>
+      <c r="E92" s="14" t="str">
+        <f>IF(MIN(Class_0!B39,Class_1!B39,Class_2!B39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F92" s="14" t="str">
+        <f>IF(MIN(Class_0!C39,Class_1!C39,Class_2!C39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G92" s="14" t="str">
+        <f>IF(MIN(Class_0!D39,Class_1!D39,Class_2!D39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H92" s="14" t="str">
+        <f>IF(MIN(Class_0!E39,Class_1!E39,Class_2!E39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I92" s="14" t="str">
+        <f>IF(MIN(Class_0!F39,Class_1!F39,Class_2!F39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J92" s="14" t="str">
+        <f>IF(MIN(Class_0!G39,Class_1!G39,Class_2!G39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K92" s="14" t="str">
+        <f>IF(MIN(Class_0!H39,Class_1!H39,Class_2!H39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L92" s="14" t="str">
+        <f>IF(MIN(Class_0!I39,Class_1!I39,Class_2!I39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M92" s="14" t="str">
+        <f>IF(MIN(Class_0!J39,Class_1!J39,Class_2!J39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N92" s="14" t="str">
+        <f>IF(MIN(Class_0!K39,Class_1!K39,Class_2!K39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O92" s="14" t="str">
+        <f>IF(MIN(Class_0!L39,Class_1!L39,Class_2!L39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P92" s="14" t="str">
+        <f>IF(MIN(Class_0!M39,Class_1!M39,Class_2!M39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q92" s="14" t="str">
+        <f>IF(MIN(Class_0!N39,Class_1!N39,Class_2!N39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R92" s="14" t="str">
+        <f>IF(MIN(Class_0!O39,Class_1!O39,Class_2!O39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S92" s="14" t="str">
+        <f>IF(MIN(Class_0!P39,Class_1!P39,Class_2!P39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T92" s="14" t="str">
+        <f>IF(MIN(Class_0!Q39,Class_1!Q39,Class_2!Q39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U92" s="14" t="str">
+        <f>IF(MIN(Class_0!R39,Class_1!R39,Class_2!R39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V92" s="14" t="str">
+        <f>IF(MIN(Class_0!S39,Class_1!S39,Class_2!S39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W92" s="14" t="str">
+        <f>IF(MIN(Class_0!T39,Class_1!T39,Class_2!T39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X92" s="14" t="str">
+        <f>IF(MIN(Class_0!U39,Class_1!U39,Class_2!U39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y92" s="14" t="str">
+        <f>IF(MIN(Class_0!V39,Class_1!V39,Class_2!V39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z92" s="14" t="str">
+        <f>IF(MIN(Class_0!W39,Class_1!W39,Class_2!W39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA92" s="14" t="str">
+        <f>IF(MIN(Class_0!X39,Class_1!X39,Class_2!X39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB92" s="14" t="str">
+        <f>IF(MIN(Class_0!Y39,Class_1!Y39,Class_2!Y39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC92" s="14" t="str">
+        <f>IF(MIN(Class_0!Z39,Class_1!Z39,Class_2!Z39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD92" s="14" t="str">
+        <f>IF(MIN(Class_0!AA39,Class_1!AA39,Class_2!AA39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE92" s="14" t="str">
+        <f>IF(MIN(Class_0!AB39,Class_1!AB39,Class_2!AB39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF92" s="14" t="str">
+        <f>IF(MIN(Class_0!AC39,Class_1!AC39,Class_2!AC39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG92" s="14" t="str">
+        <f>IF(MIN(Class_0!AD39,Class_1!AD39,Class_2!AD39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH92" s="14" t="str">
+        <f>IF(MIN(Class_0!AE39,Class_1!AE39,Class_2!AE39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI92" s="14" t="str">
+        <f>IF(MIN(Class_0!AF39,Class_1!AF39,Class_2!AF39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ92" s="14" t="str">
+        <f>IF(MIN(Class_0!AG39,Class_1!AG39,Class_2!AG39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK92" s="14" t="str">
+        <f>IF(MIN(Class_0!AH39,Class_1!AH39,Class_2!AH39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL92" s="14" t="str">
+        <f>IF(MIN(Class_0!AI39,Class_1!AI39,Class_2!AI39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM92" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ39,Class_1!AJ39,Class_2!AJ39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN92" s="14" t="str">
+        <f>IF(MIN(Class_0!AK39,Class_1!AK39,Class_2!AK39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO92" s="14" t="str">
+        <f>IF(MIN(Class_0!AL39,Class_1!AL39,Class_2!AL39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP92" s="14" t="str">
+        <f>IF(MIN(Class_0!AM39,Class_1!AM39,Class_2!AM39) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ92" s="14"/>
+      <c r="AR92" s="14"/>
+      <c r="AS92" s="14"/>
+      <c r="AT92" s="14"/>
+      <c r="AU92" s="14"/>
+      <c r="AV92" s="14"/>
+      <c r="AW92" s="14"/>
+      <c r="AX92" s="14"/>
+      <c r="AY92" s="14"/>
+      <c r="AZ92" s="14"/>
+      <c r="BA92" s="14"/>
+      <c r="BB92" s="14"/>
+      <c r="BC92" s="14"/>
+      <c r="BD92" s="14"/>
+      <c r="BE92" s="14"/>
+      <c r="BF92" s="15"/>
+    </row>
+    <row r="93" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C93" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D93" s="10">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
+      <c r="E93" s="14" t="str">
+        <f>IF(MIN(Class_0!B40,Class_1!B40,Class_2!B40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F93" s="14" t="str">
+        <f>IF(MIN(Class_0!C40,Class_1!C40,Class_2!C40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G93" s="14" t="str">
+        <f>IF(MIN(Class_0!D40,Class_1!D40,Class_2!D40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H93" s="14" t="str">
+        <f>IF(MIN(Class_0!E40,Class_1!E40,Class_2!E40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I93" s="14" t="str">
+        <f>IF(MIN(Class_0!F40,Class_1!F40,Class_2!F40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J93" s="14" t="str">
+        <f>IF(MIN(Class_0!G40,Class_1!G40,Class_2!G40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K93" s="14" t="str">
+        <f>IF(MIN(Class_0!H40,Class_1!H40,Class_2!H40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L93" s="14" t="str">
+        <f>IF(MIN(Class_0!I40,Class_1!I40,Class_2!I40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M93" s="14" t="str">
+        <f>IF(MIN(Class_0!J40,Class_1!J40,Class_2!J40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N93" s="14" t="str">
+        <f>IF(MIN(Class_0!K40,Class_1!K40,Class_2!K40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O93" s="14" t="str">
+        <f>IF(MIN(Class_0!L40,Class_1!L40,Class_2!L40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P93" s="14" t="str">
+        <f>IF(MIN(Class_0!M40,Class_1!M40,Class_2!M40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q93" s="14" t="str">
+        <f>IF(MIN(Class_0!N40,Class_1!N40,Class_2!N40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R93" s="14" t="str">
+        <f>IF(MIN(Class_0!O40,Class_1!O40,Class_2!O40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S93" s="14" t="str">
+        <f>IF(MIN(Class_0!P40,Class_1!P40,Class_2!P40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T93" s="14" t="str">
+        <f>IF(MIN(Class_0!Q40,Class_1!Q40,Class_2!Q40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U93" s="14" t="str">
+        <f>IF(MIN(Class_0!R40,Class_1!R40,Class_2!R40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V93" s="14" t="str">
+        <f>IF(MIN(Class_0!S40,Class_1!S40,Class_2!S40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W93" s="14" t="str">
+        <f>IF(MIN(Class_0!T40,Class_1!T40,Class_2!T40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X93" s="14" t="str">
+        <f>IF(MIN(Class_0!U40,Class_1!U40,Class_2!U40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y93" s="14" t="str">
+        <f>IF(MIN(Class_0!V40,Class_1!V40,Class_2!V40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z93" s="14" t="str">
+        <f>IF(MIN(Class_0!W40,Class_1!W40,Class_2!W40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA93" s="14" t="str">
+        <f>IF(MIN(Class_0!X40,Class_1!X40,Class_2!X40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB93" s="14" t="str">
+        <f>IF(MIN(Class_0!Y40,Class_1!Y40,Class_2!Y40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC93" s="14" t="str">
+        <f>IF(MIN(Class_0!Z40,Class_1!Z40,Class_2!Z40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD93" s="14" t="str">
+        <f>IF(MIN(Class_0!AA40,Class_1!AA40,Class_2!AA40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE93" s="14" t="str">
+        <f>IF(MIN(Class_0!AB40,Class_1!AB40,Class_2!AB40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF93" s="14" t="str">
+        <f>IF(MIN(Class_0!AC40,Class_1!AC40,Class_2!AC40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG93" s="14" t="str">
+        <f>IF(MIN(Class_0!AD40,Class_1!AD40,Class_2!AD40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH93" s="14" t="str">
+        <f>IF(MIN(Class_0!AE40,Class_1!AE40,Class_2!AE40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI93" s="14" t="str">
+        <f>IF(MIN(Class_0!AF40,Class_1!AF40,Class_2!AF40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ93" s="14" t="str">
+        <f>IF(MIN(Class_0!AG40,Class_1!AG40,Class_2!AG40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK93" s="14" t="str">
+        <f>IF(MIN(Class_0!AH40,Class_1!AH40,Class_2!AH40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL93" s="14" t="str">
+        <f>IF(MIN(Class_0!AI40,Class_1!AI40,Class_2!AI40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM93" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ40,Class_1!AJ40,Class_2!AJ40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN93" s="14" t="str">
+        <f>IF(MIN(Class_0!AK40,Class_1!AK40,Class_2!AK40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO93" s="14" t="str">
+        <f>IF(MIN(Class_0!AL40,Class_1!AL40,Class_2!AL40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP93" s="14" t="str">
+        <f>IF(MIN(Class_0!AM40,Class_1!AM40,Class_2!AM40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ93" s="14" t="str">
+        <f>IF(MIN(Class_0!AN40,Class_1!AN40,Class_2!AN40) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR93" s="14"/>
+      <c r="AS93" s="14"/>
+      <c r="AT93" s="14"/>
+      <c r="AU93" s="14"/>
+      <c r="AV93" s="14"/>
+      <c r="AW93" s="14"/>
+      <c r="AX93" s="14"/>
+      <c r="AY93" s="14"/>
+      <c r="AZ93" s="14"/>
+      <c r="BA93" s="14"/>
+      <c r="BB93" s="14"/>
+      <c r="BC93" s="14"/>
+      <c r="BD93" s="14"/>
+      <c r="BE93" s="14"/>
+      <c r="BF93" s="15"/>
+    </row>
+    <row r="94" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C94" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" s="10">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+      <c r="E94" s="14" t="str">
+        <f>IF(MIN(Class_0!B41,Class_1!B41,Class_2!B41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F94" s="14" t="str">
+        <f>IF(MIN(Class_0!C41,Class_1!C41,Class_2!C41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G94" s="14" t="str">
+        <f>IF(MIN(Class_0!D41,Class_1!D41,Class_2!D41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H94" s="14" t="str">
+        <f>IF(MIN(Class_0!E41,Class_1!E41,Class_2!E41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I94" s="14" t="str">
+        <f>IF(MIN(Class_0!F41,Class_1!F41,Class_2!F41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J94" s="14" t="str">
+        <f>IF(MIN(Class_0!G41,Class_1!G41,Class_2!G41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K94" s="14" t="str">
+        <f>IF(MIN(Class_0!H41,Class_1!H41,Class_2!H41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L94" s="14" t="str">
+        <f>IF(MIN(Class_0!I41,Class_1!I41,Class_2!I41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M94" s="14" t="str">
+        <f>IF(MIN(Class_0!J41,Class_1!J41,Class_2!J41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N94" s="14" t="str">
+        <f>IF(MIN(Class_0!K41,Class_1!K41,Class_2!K41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O94" s="14" t="str">
+        <f>IF(MIN(Class_0!L41,Class_1!L41,Class_2!L41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P94" s="14" t="str">
+        <f>IF(MIN(Class_0!M41,Class_1!M41,Class_2!M41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q94" s="14" t="str">
+        <f>IF(MIN(Class_0!N41,Class_1!N41,Class_2!N41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R94" s="14" t="str">
+        <f>IF(MIN(Class_0!O41,Class_1!O41,Class_2!O41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S94" s="14" t="str">
+        <f>IF(MIN(Class_0!P41,Class_1!P41,Class_2!P41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T94" s="14" t="str">
+        <f>IF(MIN(Class_0!Q41,Class_1!Q41,Class_2!Q41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U94" s="14" t="str">
+        <f>IF(MIN(Class_0!R41,Class_1!R41,Class_2!R41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V94" s="14" t="str">
+        <f>IF(MIN(Class_0!S41,Class_1!S41,Class_2!S41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W94" s="14" t="str">
+        <f>IF(MIN(Class_0!T41,Class_1!T41,Class_2!T41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X94" s="14" t="str">
+        <f>IF(MIN(Class_0!U41,Class_1!U41,Class_2!U41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y94" s="14" t="str">
+        <f>IF(MIN(Class_0!V41,Class_1!V41,Class_2!V41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z94" s="14" t="str">
+        <f>IF(MIN(Class_0!W41,Class_1!W41,Class_2!W41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA94" s="14" t="str">
+        <f>IF(MIN(Class_0!X41,Class_1!X41,Class_2!X41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB94" s="14" t="str">
+        <f>IF(MIN(Class_0!Y41,Class_1!Y41,Class_2!Y41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC94" s="14" t="str">
+        <f>IF(MIN(Class_0!Z41,Class_1!Z41,Class_2!Z41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD94" s="14" t="str">
+        <f>IF(MIN(Class_0!AA41,Class_1!AA41,Class_2!AA41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE94" s="14" t="str">
+        <f>IF(MIN(Class_0!AB41,Class_1!AB41,Class_2!AB41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF94" s="14" t="str">
+        <f>IF(MIN(Class_0!AC41,Class_1!AC41,Class_2!AC41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG94" s="14" t="str">
+        <f>IF(MIN(Class_0!AD41,Class_1!AD41,Class_2!AD41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH94" s="14" t="str">
+        <f>IF(MIN(Class_0!AE41,Class_1!AE41,Class_2!AE41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI94" s="14" t="str">
+        <f>IF(MIN(Class_0!AF41,Class_1!AF41,Class_2!AF41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ94" s="14" t="str">
+        <f>IF(MIN(Class_0!AG41,Class_1!AG41,Class_2!AG41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK94" s="14" t="str">
+        <f>IF(MIN(Class_0!AH41,Class_1!AH41,Class_2!AH41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL94" s="14" t="str">
+        <f>IF(MIN(Class_0!AI41,Class_1!AI41,Class_2!AI41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM94" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ41,Class_1!AJ41,Class_2!AJ41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN94" s="14" t="str">
+        <f>IF(MIN(Class_0!AK41,Class_1!AK41,Class_2!AK41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO94" s="14" t="str">
+        <f>IF(MIN(Class_0!AL41,Class_1!AL41,Class_2!AL41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP94" s="14" t="str">
+        <f>IF(MIN(Class_0!AM41,Class_1!AM41,Class_2!AM41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ94" s="14" t="str">
+        <f>IF(MIN(Class_0!AN41,Class_1!AN41,Class_2!AN41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR94" s="14" t="str">
+        <f>IF(MIN(Class_0!AO41,Class_1!AO41,Class_2!AO41) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS94" s="14"/>
+      <c r="AT94" s="14"/>
+      <c r="AU94" s="14"/>
+      <c r="AV94" s="14"/>
+      <c r="AW94" s="14"/>
+      <c r="AX94" s="14"/>
+      <c r="AY94" s="14"/>
+      <c r="AZ94" s="14"/>
+      <c r="BA94" s="14"/>
+      <c r="BB94" s="14"/>
+      <c r="BC94" s="14"/>
+      <c r="BD94" s="14"/>
+      <c r="BE94" s="14"/>
+      <c r="BF94" s="15"/>
+    </row>
+    <row r="95" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C95" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D95" s="10">
+        <f t="shared" si="6"/>
+        <v>41</v>
+      </c>
+      <c r="E95" s="14" t="str">
+        <f>IF(MIN(Class_0!B42,Class_1!B42,Class_2!B42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F95" s="14" t="str">
+        <f>IF(MIN(Class_0!C42,Class_1!C42,Class_2!C42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G95" s="14" t="str">
+        <f>IF(MIN(Class_0!D42,Class_1!D42,Class_2!D42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H95" s="14" t="str">
+        <f>IF(MIN(Class_0!E42,Class_1!E42,Class_2!E42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I95" s="14" t="str">
+        <f>IF(MIN(Class_0!F42,Class_1!F42,Class_2!F42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J95" s="14" t="str">
+        <f>IF(MIN(Class_0!G42,Class_1!G42,Class_2!G42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K95" s="14" t="str">
+        <f>IF(MIN(Class_0!H42,Class_1!H42,Class_2!H42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L95" s="14" t="str">
+        <f>IF(MIN(Class_0!I42,Class_1!I42,Class_2!I42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M95" s="14" t="str">
+        <f>IF(MIN(Class_0!J42,Class_1!J42,Class_2!J42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N95" s="14" t="str">
+        <f>IF(MIN(Class_0!K42,Class_1!K42,Class_2!K42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O95" s="14" t="str">
+        <f>IF(MIN(Class_0!L42,Class_1!L42,Class_2!L42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P95" s="14" t="str">
+        <f>IF(MIN(Class_0!M42,Class_1!M42,Class_2!M42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Q95" s="14" t="str">
+        <f>IF(MIN(Class_0!N42,Class_1!N42,Class_2!N42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R95" s="14" t="str">
+        <f>IF(MIN(Class_0!O42,Class_1!O42,Class_2!O42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S95" s="14" t="str">
+        <f>IF(MIN(Class_0!P42,Class_1!P42,Class_2!P42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T95" s="14" t="str">
+        <f>IF(MIN(Class_0!Q42,Class_1!Q42,Class_2!Q42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U95" s="14" t="str">
+        <f>IF(MIN(Class_0!R42,Class_1!R42,Class_2!R42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V95" s="14" t="str">
+        <f>IF(MIN(Class_0!S42,Class_1!S42,Class_2!S42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W95" s="14" t="str">
+        <f>IF(MIN(Class_0!T42,Class_1!T42,Class_2!T42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X95" s="14" t="str">
+        <f>IF(MIN(Class_0!U42,Class_1!U42,Class_2!U42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y95" s="14" t="str">
+        <f>IF(MIN(Class_0!V42,Class_1!V42,Class_2!V42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z95" s="14" t="str">
+        <f>IF(MIN(Class_0!W42,Class_1!W42,Class_2!W42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA95" s="14" t="str">
+        <f>IF(MIN(Class_0!X42,Class_1!X42,Class_2!X42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB95" s="14" t="str">
+        <f>IF(MIN(Class_0!Y42,Class_1!Y42,Class_2!Y42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC95" s="14" t="str">
+        <f>IF(MIN(Class_0!Z42,Class_1!Z42,Class_2!Z42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD95" s="14" t="str">
+        <f>IF(MIN(Class_0!AA42,Class_1!AA42,Class_2!AA42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE95" s="14" t="str">
+        <f>IF(MIN(Class_0!AB42,Class_1!AB42,Class_2!AB42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF95" s="14" t="str">
+        <f>IF(MIN(Class_0!AC42,Class_1!AC42,Class_2!AC42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG95" s="14" t="str">
+        <f>IF(MIN(Class_0!AD42,Class_1!AD42,Class_2!AD42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH95" s="14" t="str">
+        <f>IF(MIN(Class_0!AE42,Class_1!AE42,Class_2!AE42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI95" s="14" t="str">
+        <f>IF(MIN(Class_0!AF42,Class_1!AF42,Class_2!AF42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ95" s="14" t="str">
+        <f>IF(MIN(Class_0!AG42,Class_1!AG42,Class_2!AG42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK95" s="14" t="str">
+        <f>IF(MIN(Class_0!AH42,Class_1!AH42,Class_2!AH42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL95" s="14" t="str">
+        <f>IF(MIN(Class_0!AI42,Class_1!AI42,Class_2!AI42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM95" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ42,Class_1!AJ42,Class_2!AJ42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN95" s="14" t="str">
+        <f>IF(MIN(Class_0!AK42,Class_1!AK42,Class_2!AK42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO95" s="14" t="str">
+        <f>IF(MIN(Class_0!AL42,Class_1!AL42,Class_2!AL42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP95" s="14" t="str">
+        <f>IF(MIN(Class_0!AM42,Class_1!AM42,Class_2!AM42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ95" s="14" t="str">
+        <f>IF(MIN(Class_0!AN42,Class_1!AN42,Class_2!AN42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR95" s="14" t="str">
+        <f>IF(MIN(Class_0!AO42,Class_1!AO42,Class_2!AO42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS95" s="14" t="str">
+        <f>IF(MIN(Class_0!AP42,Class_1!AP42,Class_2!AP42) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT95" s="14"/>
+      <c r="AU95" s="14"/>
+      <c r="AV95" s="14"/>
+      <c r="AW95" s="14"/>
+      <c r="AX95" s="14"/>
+      <c r="AY95" s="14"/>
+      <c r="AZ95" s="14"/>
+      <c r="BA95" s="14"/>
+      <c r="BB95" s="14"/>
+      <c r="BC95" s="14"/>
+      <c r="BD95" s="14"/>
+      <c r="BE95" s="14"/>
+      <c r="BF95" s="15"/>
+    </row>
+    <row r="96" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C96" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D96" s="10">
+        <f t="shared" si="6"/>
+        <v>42</v>
+      </c>
+      <c r="E96" s="14" t="str">
+        <f>IF(MIN(Class_0!B43,Class_1!B43,Class_2!B43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F96" s="14" t="str">
+        <f>IF(MIN(Class_0!C43,Class_1!C43,Class_2!C43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G96" s="14" t="str">
+        <f>IF(MIN(Class_0!D43,Class_1!D43,Class_2!D43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H96" s="14" t="str">
+        <f>IF(MIN(Class_0!E43,Class_1!E43,Class_2!E43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I96" s="14" t="str">
+        <f>IF(MIN(Class_0!F43,Class_1!F43,Class_2!F43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J96" s="14" t="str">
+        <f>IF(MIN(Class_0!G43,Class_1!G43,Class_2!G43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K96" s="14" t="str">
+        <f>IF(MIN(Class_0!H43,Class_1!H43,Class_2!H43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L96" s="14" t="str">
+        <f>IF(MIN(Class_0!I43,Class_1!I43,Class_2!I43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M96" s="14" t="str">
+        <f>IF(MIN(Class_0!J43,Class_1!J43,Class_2!J43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N96" s="14" t="str">
+        <f>IF(MIN(Class_0!K43,Class_1!K43,Class_2!K43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O96" s="14" t="str">
+        <f>IF(MIN(Class_0!L43,Class_1!L43,Class_2!L43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P96" s="14" t="str">
+        <f>IF(MIN(Class_0!M43,Class_1!M43,Class_2!M43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q96" s="14" t="str">
+        <f>IF(MIN(Class_0!N43,Class_1!N43,Class_2!N43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R96" s="14" t="str">
+        <f>IF(MIN(Class_0!O43,Class_1!O43,Class_2!O43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S96" s="14" t="str">
+        <f>IF(MIN(Class_0!P43,Class_1!P43,Class_2!P43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T96" s="14" t="str">
+        <f>IF(MIN(Class_0!Q43,Class_1!Q43,Class_2!Q43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U96" s="14" t="str">
+        <f>IF(MIN(Class_0!R43,Class_1!R43,Class_2!R43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V96" s="14" t="str">
+        <f>IF(MIN(Class_0!S43,Class_1!S43,Class_2!S43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W96" s="14" t="str">
+        <f>IF(MIN(Class_0!T43,Class_1!T43,Class_2!T43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X96" s="14" t="str">
+        <f>IF(MIN(Class_0!U43,Class_1!U43,Class_2!U43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y96" s="14" t="str">
+        <f>IF(MIN(Class_0!V43,Class_1!V43,Class_2!V43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z96" s="14" t="str">
+        <f>IF(MIN(Class_0!W43,Class_1!W43,Class_2!W43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA96" s="14" t="str">
+        <f>IF(MIN(Class_0!X43,Class_1!X43,Class_2!X43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB96" s="14" t="str">
+        <f>IF(MIN(Class_0!Y43,Class_1!Y43,Class_2!Y43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC96" s="14" t="str">
+        <f>IF(MIN(Class_0!Z43,Class_1!Z43,Class_2!Z43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD96" s="14" t="str">
+        <f>IF(MIN(Class_0!AA43,Class_1!AA43,Class_2!AA43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE96" s="14" t="str">
+        <f>IF(MIN(Class_0!AB43,Class_1!AB43,Class_2!AB43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF96" s="14" t="str">
+        <f>IF(MIN(Class_0!AC43,Class_1!AC43,Class_2!AC43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG96" s="14" t="str">
+        <f>IF(MIN(Class_0!AD43,Class_1!AD43,Class_2!AD43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH96" s="14" t="str">
+        <f>IF(MIN(Class_0!AE43,Class_1!AE43,Class_2!AE43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI96" s="14" t="str">
+        <f>IF(MIN(Class_0!AF43,Class_1!AF43,Class_2!AF43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ96" s="14" t="str">
+        <f>IF(MIN(Class_0!AG43,Class_1!AG43,Class_2!AG43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK96" s="14" t="str">
+        <f>IF(MIN(Class_0!AH43,Class_1!AH43,Class_2!AH43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL96" s="14" t="str">
+        <f>IF(MIN(Class_0!AI43,Class_1!AI43,Class_2!AI43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM96" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ43,Class_1!AJ43,Class_2!AJ43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN96" s="14" t="str">
+        <f>IF(MIN(Class_0!AK43,Class_1!AK43,Class_2!AK43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO96" s="14" t="str">
+        <f>IF(MIN(Class_0!AL43,Class_1!AL43,Class_2!AL43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP96" s="14" t="str">
+        <f>IF(MIN(Class_0!AM43,Class_1!AM43,Class_2!AM43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ96" s="14" t="str">
+        <f>IF(MIN(Class_0!AN43,Class_1!AN43,Class_2!AN43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR96" s="14" t="str">
+        <f>IF(MIN(Class_0!AO43,Class_1!AO43,Class_2!AO43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS96" s="14" t="str">
+        <f>IF(MIN(Class_0!AP43,Class_1!AP43,Class_2!AP43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT96" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ43,Class_1!AQ43,Class_2!AQ43) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU96" s="14"/>
+      <c r="AV96" s="14"/>
+      <c r="AW96" s="14"/>
+      <c r="AX96" s="14"/>
+      <c r="AY96" s="14"/>
+      <c r="AZ96" s="14"/>
+      <c r="BA96" s="14"/>
+      <c r="BB96" s="14"/>
+      <c r="BC96" s="14"/>
+      <c r="BD96" s="14"/>
+      <c r="BE96" s="14"/>
+      <c r="BF96" s="15"/>
+    </row>
+    <row r="97" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C97" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D97" s="10">
+        <f t="shared" si="6"/>
+        <v>43</v>
+      </c>
+      <c r="E97" s="14" t="str">
+        <f>IF(MIN(Class_0!B44,Class_1!B44,Class_2!B44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F97" s="14" t="str">
+        <f>IF(MIN(Class_0!C44,Class_1!C44,Class_2!C44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G97" s="14" t="str">
+        <f>IF(MIN(Class_0!D44,Class_1!D44,Class_2!D44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H97" s="14" t="str">
+        <f>IF(MIN(Class_0!E44,Class_1!E44,Class_2!E44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I97" s="14" t="str">
+        <f>IF(MIN(Class_0!F44,Class_1!F44,Class_2!F44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J97" s="14" t="str">
+        <f>IF(MIN(Class_0!G44,Class_1!G44,Class_2!G44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K97" s="14" t="str">
+        <f>IF(MIN(Class_0!H44,Class_1!H44,Class_2!H44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L97" s="14" t="str">
+        <f>IF(MIN(Class_0!I44,Class_1!I44,Class_2!I44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M97" s="14" t="str">
+        <f>IF(MIN(Class_0!J44,Class_1!J44,Class_2!J44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N97" s="14" t="str">
+        <f>IF(MIN(Class_0!K44,Class_1!K44,Class_2!K44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O97" s="14" t="str">
+        <f>IF(MIN(Class_0!L44,Class_1!L44,Class_2!L44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P97" s="14" t="str">
+        <f>IF(MIN(Class_0!M44,Class_1!M44,Class_2!M44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q97" s="14" t="str">
+        <f>IF(MIN(Class_0!N44,Class_1!N44,Class_2!N44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R97" s="14" t="str">
+        <f>IF(MIN(Class_0!O44,Class_1!O44,Class_2!O44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S97" s="14" t="str">
+        <f>IF(MIN(Class_0!P44,Class_1!P44,Class_2!P44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T97" s="14" t="str">
+        <f>IF(MIN(Class_0!Q44,Class_1!Q44,Class_2!Q44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U97" s="14" t="str">
+        <f>IF(MIN(Class_0!R44,Class_1!R44,Class_2!R44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V97" s="14" t="str">
+        <f>IF(MIN(Class_0!S44,Class_1!S44,Class_2!S44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W97" s="14" t="str">
+        <f>IF(MIN(Class_0!T44,Class_1!T44,Class_2!T44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X97" s="14" t="str">
+        <f>IF(MIN(Class_0!U44,Class_1!U44,Class_2!U44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y97" s="14" t="str">
+        <f>IF(MIN(Class_0!V44,Class_1!V44,Class_2!V44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z97" s="14" t="str">
+        <f>IF(MIN(Class_0!W44,Class_1!W44,Class_2!W44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA97" s="14" t="str">
+        <f>IF(MIN(Class_0!X44,Class_1!X44,Class_2!X44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB97" s="14" t="str">
+        <f>IF(MIN(Class_0!Y44,Class_1!Y44,Class_2!Y44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC97" s="14" t="str">
+        <f>IF(MIN(Class_0!Z44,Class_1!Z44,Class_2!Z44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD97" s="14" t="str">
+        <f>IF(MIN(Class_0!AA44,Class_1!AA44,Class_2!AA44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE97" s="14" t="str">
+        <f>IF(MIN(Class_0!AB44,Class_1!AB44,Class_2!AB44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF97" s="14" t="str">
+        <f>IF(MIN(Class_0!AC44,Class_1!AC44,Class_2!AC44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG97" s="14" t="str">
+        <f>IF(MIN(Class_0!AD44,Class_1!AD44,Class_2!AD44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH97" s="14" t="str">
+        <f>IF(MIN(Class_0!AE44,Class_1!AE44,Class_2!AE44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI97" s="14" t="str">
+        <f>IF(MIN(Class_0!AF44,Class_1!AF44,Class_2!AF44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ97" s="14" t="str">
+        <f>IF(MIN(Class_0!AG44,Class_1!AG44,Class_2!AG44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK97" s="14" t="str">
+        <f>IF(MIN(Class_0!AH44,Class_1!AH44,Class_2!AH44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL97" s="14" t="str">
+        <f>IF(MIN(Class_0!AI44,Class_1!AI44,Class_2!AI44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM97" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ44,Class_1!AJ44,Class_2!AJ44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN97" s="14" t="str">
+        <f>IF(MIN(Class_0!AK44,Class_1!AK44,Class_2!AK44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO97" s="14" t="str">
+        <f>IF(MIN(Class_0!AL44,Class_1!AL44,Class_2!AL44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP97" s="14" t="str">
+        <f>IF(MIN(Class_0!AM44,Class_1!AM44,Class_2!AM44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ97" s="14" t="str">
+        <f>IF(MIN(Class_0!AN44,Class_1!AN44,Class_2!AN44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR97" s="14" t="str">
+        <f>IF(MIN(Class_0!AO44,Class_1!AO44,Class_2!AO44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS97" s="14" t="str">
+        <f>IF(MIN(Class_0!AP44,Class_1!AP44,Class_2!AP44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT97" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ44,Class_1!AQ44,Class_2!AQ44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU97" s="14" t="str">
+        <f>IF(MIN(Class_0!AR44,Class_1!AR44,Class_2!AR44) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV97" s="14"/>
+      <c r="AW97" s="14"/>
+      <c r="AX97" s="14"/>
+      <c r="AY97" s="14"/>
+      <c r="AZ97" s="14"/>
+      <c r="BA97" s="14"/>
+      <c r="BB97" s="14"/>
+      <c r="BC97" s="14"/>
+      <c r="BD97" s="14"/>
+      <c r="BE97" s="14"/>
+      <c r="BF97" s="15"/>
+    </row>
+    <row r="98" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C98" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="10">
+        <f t="shared" si="6"/>
+        <v>44</v>
+      </c>
+      <c r="E98" s="14" t="str">
+        <f>IF(MIN(Class_0!B45,Class_1!B45,Class_2!B45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F98" s="14" t="str">
+        <f>IF(MIN(Class_0!C45,Class_1!C45,Class_2!C45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G98" s="14" t="str">
+        <f>IF(MIN(Class_0!D45,Class_1!D45,Class_2!D45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H98" s="14" t="str">
+        <f>IF(MIN(Class_0!E45,Class_1!E45,Class_2!E45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I98" s="14" t="str">
+        <f>IF(MIN(Class_0!F45,Class_1!F45,Class_2!F45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J98" s="14" t="str">
+        <f>IF(MIN(Class_0!G45,Class_1!G45,Class_2!G45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K98" s="14" t="str">
+        <f>IF(MIN(Class_0!H45,Class_1!H45,Class_2!H45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L98" s="14" t="str">
+        <f>IF(MIN(Class_0!I45,Class_1!I45,Class_2!I45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M98" s="14" t="str">
+        <f>IF(MIN(Class_0!J45,Class_1!J45,Class_2!J45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N98" s="14" t="str">
+        <f>IF(MIN(Class_0!K45,Class_1!K45,Class_2!K45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O98" s="14" t="str">
+        <f>IF(MIN(Class_0!L45,Class_1!L45,Class_2!L45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P98" s="14" t="str">
+        <f>IF(MIN(Class_0!M45,Class_1!M45,Class_2!M45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q98" s="14" t="str">
+        <f>IF(MIN(Class_0!N45,Class_1!N45,Class_2!N45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R98" s="14" t="str">
+        <f>IF(MIN(Class_0!O45,Class_1!O45,Class_2!O45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S98" s="14" t="str">
+        <f>IF(MIN(Class_0!P45,Class_1!P45,Class_2!P45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T98" s="14" t="str">
+        <f>IF(MIN(Class_0!Q45,Class_1!Q45,Class_2!Q45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U98" s="14" t="str">
+        <f>IF(MIN(Class_0!R45,Class_1!R45,Class_2!R45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V98" s="14" t="str">
+        <f>IF(MIN(Class_0!S45,Class_1!S45,Class_2!S45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W98" s="14" t="str">
+        <f>IF(MIN(Class_0!T45,Class_1!T45,Class_2!T45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X98" s="14" t="str">
+        <f>IF(MIN(Class_0!U45,Class_1!U45,Class_2!U45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y98" s="14" t="str">
+        <f>IF(MIN(Class_0!V45,Class_1!V45,Class_2!V45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z98" s="14" t="str">
+        <f>IF(MIN(Class_0!W45,Class_1!W45,Class_2!W45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA98" s="14" t="str">
+        <f>IF(MIN(Class_0!X45,Class_1!X45,Class_2!X45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB98" s="14" t="str">
+        <f>IF(MIN(Class_0!Y45,Class_1!Y45,Class_2!Y45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC98" s="14" t="str">
+        <f>IF(MIN(Class_0!Z45,Class_1!Z45,Class_2!Z45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD98" s="14" t="str">
+        <f>IF(MIN(Class_0!AA45,Class_1!AA45,Class_2!AA45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE98" s="14" t="str">
+        <f>IF(MIN(Class_0!AB45,Class_1!AB45,Class_2!AB45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF98" s="14" t="str">
+        <f>IF(MIN(Class_0!AC45,Class_1!AC45,Class_2!AC45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG98" s="14" t="str">
+        <f>IF(MIN(Class_0!AD45,Class_1!AD45,Class_2!AD45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH98" s="14" t="str">
+        <f>IF(MIN(Class_0!AE45,Class_1!AE45,Class_2!AE45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI98" s="14" t="str">
+        <f>IF(MIN(Class_0!AF45,Class_1!AF45,Class_2!AF45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ98" s="14" t="str">
+        <f>IF(MIN(Class_0!AG45,Class_1!AG45,Class_2!AG45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK98" s="14" t="str">
+        <f>IF(MIN(Class_0!AH45,Class_1!AH45,Class_2!AH45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL98" s="14" t="str">
+        <f>IF(MIN(Class_0!AI45,Class_1!AI45,Class_2!AI45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM98" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ45,Class_1!AJ45,Class_2!AJ45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN98" s="14" t="str">
+        <f>IF(MIN(Class_0!AK45,Class_1!AK45,Class_2!AK45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO98" s="14" t="str">
+        <f>IF(MIN(Class_0!AL45,Class_1!AL45,Class_2!AL45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP98" s="14" t="str">
+        <f>IF(MIN(Class_0!AM45,Class_1!AM45,Class_2!AM45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ98" s="14" t="str">
+        <f>IF(MIN(Class_0!AN45,Class_1!AN45,Class_2!AN45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR98" s="14" t="str">
+        <f>IF(MIN(Class_0!AO45,Class_1!AO45,Class_2!AO45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS98" s="14" t="str">
+        <f>IF(MIN(Class_0!AP45,Class_1!AP45,Class_2!AP45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT98" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ45,Class_1!AQ45,Class_2!AQ45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU98" s="14" t="str">
+        <f>IF(MIN(Class_0!AR45,Class_1!AR45,Class_2!AR45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV98" s="14" t="str">
+        <f>IF(MIN(Class_0!AS45,Class_1!AS45,Class_2!AS45) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW98" s="14"/>
+      <c r="AX98" s="14"/>
+      <c r="AY98" s="14"/>
+      <c r="AZ98" s="14"/>
+      <c r="BA98" s="14"/>
+      <c r="BB98" s="14"/>
+      <c r="BC98" s="14"/>
+      <c r="BD98" s="14"/>
+      <c r="BE98" s="14"/>
+      <c r="BF98" s="15"/>
+    </row>
+    <row r="99" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C99" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="10">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+      <c r="E99" s="14" t="str">
+        <f>IF(MIN(Class_0!B46,Class_1!B46,Class_2!B46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F99" s="14" t="str">
+        <f>IF(MIN(Class_0!C46,Class_1!C46,Class_2!C46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="G99" s="14" t="str">
+        <f>IF(MIN(Class_0!D46,Class_1!D46,Class_2!D46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H99" s="14" t="str">
+        <f>IF(MIN(Class_0!E46,Class_1!E46,Class_2!E46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I99" s="14" t="str">
+        <f>IF(MIN(Class_0!F46,Class_1!F46,Class_2!F46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J99" s="14" t="str">
+        <f>IF(MIN(Class_0!G46,Class_1!G46,Class_2!G46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K99" s="14" t="str">
+        <f>IF(MIN(Class_0!H46,Class_1!H46,Class_2!H46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L99" s="14" t="str">
+        <f>IF(MIN(Class_0!I46,Class_1!I46,Class_2!I46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M99" s="14" t="str">
+        <f>IF(MIN(Class_0!J46,Class_1!J46,Class_2!J46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N99" s="14" t="str">
+        <f>IF(MIN(Class_0!K46,Class_1!K46,Class_2!K46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O99" s="14" t="str">
+        <f>IF(MIN(Class_0!L46,Class_1!L46,Class_2!L46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P99" s="14" t="str">
+        <f>IF(MIN(Class_0!M46,Class_1!M46,Class_2!M46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q99" s="14" t="str">
+        <f>IF(MIN(Class_0!N46,Class_1!N46,Class_2!N46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R99" s="14" t="str">
+        <f>IF(MIN(Class_0!O46,Class_1!O46,Class_2!O46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S99" s="14" t="str">
+        <f>IF(MIN(Class_0!P46,Class_1!P46,Class_2!P46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T99" s="14" t="str">
+        <f>IF(MIN(Class_0!Q46,Class_1!Q46,Class_2!Q46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U99" s="14" t="str">
+        <f>IF(MIN(Class_0!R46,Class_1!R46,Class_2!R46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V99" s="14" t="str">
+        <f>IF(MIN(Class_0!S46,Class_1!S46,Class_2!S46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W99" s="14" t="str">
+        <f>IF(MIN(Class_0!T46,Class_1!T46,Class_2!T46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X99" s="14" t="str">
+        <f>IF(MIN(Class_0!U46,Class_1!U46,Class_2!U46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y99" s="14" t="str">
+        <f>IF(MIN(Class_0!V46,Class_1!V46,Class_2!V46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z99" s="14" t="str">
+        <f>IF(MIN(Class_0!W46,Class_1!W46,Class_2!W46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA99" s="14" t="str">
+        <f>IF(MIN(Class_0!X46,Class_1!X46,Class_2!X46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB99" s="14" t="str">
+        <f>IF(MIN(Class_0!Y46,Class_1!Y46,Class_2!Y46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC99" s="14" t="str">
+        <f>IF(MIN(Class_0!Z46,Class_1!Z46,Class_2!Z46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD99" s="14" t="str">
+        <f>IF(MIN(Class_0!AA46,Class_1!AA46,Class_2!AA46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE99" s="14" t="str">
+        <f>IF(MIN(Class_0!AB46,Class_1!AB46,Class_2!AB46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF99" s="14" t="str">
+        <f>IF(MIN(Class_0!AC46,Class_1!AC46,Class_2!AC46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG99" s="14" t="str">
+        <f>IF(MIN(Class_0!AD46,Class_1!AD46,Class_2!AD46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH99" s="14" t="str">
+        <f>IF(MIN(Class_0!AE46,Class_1!AE46,Class_2!AE46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI99" s="14" t="str">
+        <f>IF(MIN(Class_0!AF46,Class_1!AF46,Class_2!AF46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ99" s="14" t="str">
+        <f>IF(MIN(Class_0!AG46,Class_1!AG46,Class_2!AG46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK99" s="14" t="str">
+        <f>IF(MIN(Class_0!AH46,Class_1!AH46,Class_2!AH46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL99" s="14" t="str">
+        <f>IF(MIN(Class_0!AI46,Class_1!AI46,Class_2!AI46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM99" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ46,Class_1!AJ46,Class_2!AJ46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN99" s="14" t="str">
+        <f>IF(MIN(Class_0!AK46,Class_1!AK46,Class_2!AK46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO99" s="14" t="str">
+        <f>IF(MIN(Class_0!AL46,Class_1!AL46,Class_2!AL46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP99" s="14" t="str">
+        <f>IF(MIN(Class_0!AM46,Class_1!AM46,Class_2!AM46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ99" s="14" t="str">
+        <f>IF(MIN(Class_0!AN46,Class_1!AN46,Class_2!AN46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR99" s="14" t="str">
+        <f>IF(MIN(Class_0!AO46,Class_1!AO46,Class_2!AO46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS99" s="14" t="str">
+        <f>IF(MIN(Class_0!AP46,Class_1!AP46,Class_2!AP46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT99" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ46,Class_1!AQ46,Class_2!AQ46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU99" s="14" t="str">
+        <f>IF(MIN(Class_0!AR46,Class_1!AR46,Class_2!AR46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV99" s="14" t="str">
+        <f>IF(MIN(Class_0!AS46,Class_1!AS46,Class_2!AS46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW99" s="14" t="str">
+        <f>IF(MIN(Class_0!AT46,Class_1!AT46,Class_2!AT46) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX99" s="14"/>
+      <c r="AY99" s="14"/>
+      <c r="AZ99" s="14"/>
+      <c r="BA99" s="14"/>
+      <c r="BB99" s="14"/>
+      <c r="BC99" s="14"/>
+      <c r="BD99" s="14"/>
+      <c r="BE99" s="14"/>
+      <c r="BF99" s="15"/>
+    </row>
+    <row r="100" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C100" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D100" s="10">
+        <f t="shared" si="6"/>
+        <v>46</v>
+      </c>
+      <c r="E100" s="14" t="str">
+        <f>IF(MIN(Class_0!B47,Class_1!B47,Class_2!B47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F100" s="14" t="str">
+        <f>IF(MIN(Class_0!C47,Class_1!C47,Class_2!C47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G100" s="14" t="str">
+        <f>IF(MIN(Class_0!D47,Class_1!D47,Class_2!D47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H100" s="14" t="str">
+        <f>IF(MIN(Class_0!E47,Class_1!E47,Class_2!E47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I100" s="14" t="str">
+        <f>IF(MIN(Class_0!F47,Class_1!F47,Class_2!F47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J100" s="14" t="str">
+        <f>IF(MIN(Class_0!G47,Class_1!G47,Class_2!G47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K100" s="14" t="str">
+        <f>IF(MIN(Class_0!H47,Class_1!H47,Class_2!H47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L100" s="14" t="str">
+        <f>IF(MIN(Class_0!I47,Class_1!I47,Class_2!I47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M100" s="14" t="str">
+        <f>IF(MIN(Class_0!J47,Class_1!J47,Class_2!J47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N100" s="14" t="str">
+        <f>IF(MIN(Class_0!K47,Class_1!K47,Class_2!K47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O100" s="14" t="str">
+        <f>IF(MIN(Class_0!L47,Class_1!L47,Class_2!L47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P100" s="14" t="str">
+        <f>IF(MIN(Class_0!M47,Class_1!M47,Class_2!M47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q100" s="14" t="str">
+        <f>IF(MIN(Class_0!N47,Class_1!N47,Class_2!N47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="R100" s="14" t="str">
+        <f>IF(MIN(Class_0!O47,Class_1!O47,Class_2!O47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S100" s="14" t="str">
+        <f>IF(MIN(Class_0!P47,Class_1!P47,Class_2!P47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T100" s="14" t="str">
+        <f>IF(MIN(Class_0!Q47,Class_1!Q47,Class_2!Q47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U100" s="14" t="str">
+        <f>IF(MIN(Class_0!R47,Class_1!R47,Class_2!R47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V100" s="14" t="str">
+        <f>IF(MIN(Class_0!S47,Class_1!S47,Class_2!S47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W100" s="14" t="str">
+        <f>IF(MIN(Class_0!T47,Class_1!T47,Class_2!T47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X100" s="14" t="str">
+        <f>IF(MIN(Class_0!U47,Class_1!U47,Class_2!U47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y100" s="14" t="str">
+        <f>IF(MIN(Class_0!V47,Class_1!V47,Class_2!V47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z100" s="14" t="str">
+        <f>IF(MIN(Class_0!W47,Class_1!W47,Class_2!W47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA100" s="14" t="str">
+        <f>IF(MIN(Class_0!X47,Class_1!X47,Class_2!X47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB100" s="14" t="str">
+        <f>IF(MIN(Class_0!Y47,Class_1!Y47,Class_2!Y47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC100" s="14" t="str">
+        <f>IF(MIN(Class_0!Z47,Class_1!Z47,Class_2!Z47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD100" s="14" t="str">
+        <f>IF(MIN(Class_0!AA47,Class_1!AA47,Class_2!AA47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE100" s="14" t="str">
+        <f>IF(MIN(Class_0!AB47,Class_1!AB47,Class_2!AB47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF100" s="14" t="str">
+        <f>IF(MIN(Class_0!AC47,Class_1!AC47,Class_2!AC47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG100" s="14" t="str">
+        <f>IF(MIN(Class_0!AD47,Class_1!AD47,Class_2!AD47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH100" s="14" t="str">
+        <f>IF(MIN(Class_0!AE47,Class_1!AE47,Class_2!AE47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI100" s="14" t="str">
+        <f>IF(MIN(Class_0!AF47,Class_1!AF47,Class_2!AF47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ100" s="14" t="str">
+        <f>IF(MIN(Class_0!AG47,Class_1!AG47,Class_2!AG47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK100" s="14" t="str">
+        <f>IF(MIN(Class_0!AH47,Class_1!AH47,Class_2!AH47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL100" s="14" t="str">
+        <f>IF(MIN(Class_0!AI47,Class_1!AI47,Class_2!AI47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM100" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ47,Class_1!AJ47,Class_2!AJ47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN100" s="14" t="str">
+        <f>IF(MIN(Class_0!AK47,Class_1!AK47,Class_2!AK47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO100" s="14" t="str">
+        <f>IF(MIN(Class_0!AL47,Class_1!AL47,Class_2!AL47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP100" s="14" t="str">
+        <f>IF(MIN(Class_0!AM47,Class_1!AM47,Class_2!AM47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ100" s="14" t="str">
+        <f>IF(MIN(Class_0!AN47,Class_1!AN47,Class_2!AN47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR100" s="14" t="str">
+        <f>IF(MIN(Class_0!AO47,Class_1!AO47,Class_2!AO47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS100" s="14" t="str">
+        <f>IF(MIN(Class_0!AP47,Class_1!AP47,Class_2!AP47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT100" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ47,Class_1!AQ47,Class_2!AQ47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU100" s="14" t="str">
+        <f>IF(MIN(Class_0!AR47,Class_1!AR47,Class_2!AR47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV100" s="14" t="str">
+        <f>IF(MIN(Class_0!AS47,Class_1!AS47,Class_2!AS47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW100" s="14" t="str">
+        <f>IF(MIN(Class_0!AT47,Class_1!AT47,Class_2!AT47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX100" s="14" t="str">
+        <f>IF(MIN(Class_0!AU47,Class_1!AU47,Class_2!AU47) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY100" s="14"/>
+      <c r="AZ100" s="14"/>
+      <c r="BA100" s="14"/>
+      <c r="BB100" s="14"/>
+      <c r="BC100" s="14"/>
+      <c r="BD100" s="14"/>
+      <c r="BE100" s="14"/>
+      <c r="BF100" s="15"/>
+    </row>
+    <row r="101" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C101" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D101" s="10">
+        <f t="shared" si="6"/>
+        <v>47</v>
+      </c>
+      <c r="E101" s="14" t="str">
+        <f>IF(MIN(Class_0!B48,Class_1!B48,Class_2!B48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F101" s="14" t="str">
+        <f>IF(MIN(Class_0!C48,Class_1!C48,Class_2!C48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G101" s="14" t="str">
+        <f>IF(MIN(Class_0!D48,Class_1!D48,Class_2!D48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H101" s="14" t="str">
+        <f>IF(MIN(Class_0!E48,Class_1!E48,Class_2!E48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I101" s="14" t="str">
+        <f>IF(MIN(Class_0!F48,Class_1!F48,Class_2!F48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J101" s="14" t="str">
+        <f>IF(MIN(Class_0!G48,Class_1!G48,Class_2!G48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K101" s="14" t="str">
+        <f>IF(MIN(Class_0!H48,Class_1!H48,Class_2!H48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L101" s="14" t="str">
+        <f>IF(MIN(Class_0!I48,Class_1!I48,Class_2!I48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M101" s="14" t="str">
+        <f>IF(MIN(Class_0!J48,Class_1!J48,Class_2!J48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N101" s="14" t="str">
+        <f>IF(MIN(Class_0!K48,Class_1!K48,Class_2!K48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O101" s="14" t="str">
+        <f>IF(MIN(Class_0!L48,Class_1!L48,Class_2!L48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P101" s="14" t="str">
+        <f>IF(MIN(Class_0!M48,Class_1!M48,Class_2!M48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q101" s="14" t="str">
+        <f>IF(MIN(Class_0!N48,Class_1!N48,Class_2!N48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R101" s="14" t="str">
+        <f>IF(MIN(Class_0!O48,Class_1!O48,Class_2!O48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S101" s="14" t="str">
+        <f>IF(MIN(Class_0!P48,Class_1!P48,Class_2!P48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T101" s="14" t="str">
+        <f>IF(MIN(Class_0!Q48,Class_1!Q48,Class_2!Q48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U101" s="14" t="str">
+        <f>IF(MIN(Class_0!R48,Class_1!R48,Class_2!R48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V101" s="14" t="str">
+        <f>IF(MIN(Class_0!S48,Class_1!S48,Class_2!S48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W101" s="14" t="str">
+        <f>IF(MIN(Class_0!T48,Class_1!T48,Class_2!T48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X101" s="14" t="str">
+        <f>IF(MIN(Class_0!U48,Class_1!U48,Class_2!U48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y101" s="14" t="str">
+        <f>IF(MIN(Class_0!V48,Class_1!V48,Class_2!V48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z101" s="14" t="str">
+        <f>IF(MIN(Class_0!W48,Class_1!W48,Class_2!W48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA101" s="14" t="str">
+        <f>IF(MIN(Class_0!X48,Class_1!X48,Class_2!X48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB101" s="14" t="str">
+        <f>IF(MIN(Class_0!Y48,Class_1!Y48,Class_2!Y48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC101" s="14" t="str">
+        <f>IF(MIN(Class_0!Z48,Class_1!Z48,Class_2!Z48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD101" s="14" t="str">
+        <f>IF(MIN(Class_0!AA48,Class_1!AA48,Class_2!AA48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE101" s="14" t="str">
+        <f>IF(MIN(Class_0!AB48,Class_1!AB48,Class_2!AB48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF101" s="14" t="str">
+        <f>IF(MIN(Class_0!AC48,Class_1!AC48,Class_2!AC48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG101" s="14" t="str">
+        <f>IF(MIN(Class_0!AD48,Class_1!AD48,Class_2!AD48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH101" s="14" t="str">
+        <f>IF(MIN(Class_0!AE48,Class_1!AE48,Class_2!AE48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI101" s="14" t="str">
+        <f>IF(MIN(Class_0!AF48,Class_1!AF48,Class_2!AF48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ101" s="14" t="str">
+        <f>IF(MIN(Class_0!AG48,Class_1!AG48,Class_2!AG48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK101" s="14" t="str">
+        <f>IF(MIN(Class_0!AH48,Class_1!AH48,Class_2!AH48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL101" s="14" t="str">
+        <f>IF(MIN(Class_0!AI48,Class_1!AI48,Class_2!AI48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM101" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ48,Class_1!AJ48,Class_2!AJ48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN101" s="14" t="str">
+        <f>IF(MIN(Class_0!AK48,Class_1!AK48,Class_2!AK48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO101" s="14" t="str">
+        <f>IF(MIN(Class_0!AL48,Class_1!AL48,Class_2!AL48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP101" s="14" t="str">
+        <f>IF(MIN(Class_0!AM48,Class_1!AM48,Class_2!AM48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ101" s="14" t="str">
+        <f>IF(MIN(Class_0!AN48,Class_1!AN48,Class_2!AN48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR101" s="14" t="str">
+        <f>IF(MIN(Class_0!AO48,Class_1!AO48,Class_2!AO48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS101" s="14" t="str">
+        <f>IF(MIN(Class_0!AP48,Class_1!AP48,Class_2!AP48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT101" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ48,Class_1!AQ48,Class_2!AQ48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU101" s="14" t="str">
+        <f>IF(MIN(Class_0!AR48,Class_1!AR48,Class_2!AR48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV101" s="14" t="str">
+        <f>IF(MIN(Class_0!AS48,Class_1!AS48,Class_2!AS48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW101" s="14" t="str">
+        <f>IF(MIN(Class_0!AT48,Class_1!AT48,Class_2!AT48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX101" s="14" t="str">
+        <f>IF(MIN(Class_0!AU48,Class_1!AU48,Class_2!AU48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY101" s="14" t="str">
+        <f>IF(MIN(Class_0!AV48,Class_1!AV48,Class_2!AV48) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ101" s="14"/>
+      <c r="BA101" s="14"/>
+      <c r="BB101" s="14"/>
+      <c r="BC101" s="14"/>
+      <c r="BD101" s="14"/>
+      <c r="BE101" s="14"/>
+      <c r="BF101" s="15"/>
+    </row>
+    <row r="102" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C102" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D102" s="10">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="E102" s="14" t="str">
+        <f>IF(MIN(Class_0!B49,Class_1!B49,Class_2!B49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F102" s="14" t="str">
+        <f>IF(MIN(Class_0!C49,Class_1!C49,Class_2!C49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G102" s="14" t="str">
+        <f>IF(MIN(Class_0!D49,Class_1!D49,Class_2!D49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H102" s="14" t="str">
+        <f>IF(MIN(Class_0!E49,Class_1!E49,Class_2!E49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I102" s="14" t="str">
+        <f>IF(MIN(Class_0!F49,Class_1!F49,Class_2!F49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J102" s="14" t="str">
+        <f>IF(MIN(Class_0!G49,Class_1!G49,Class_2!G49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K102" s="14" t="str">
+        <f>IF(MIN(Class_0!H49,Class_1!H49,Class_2!H49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L102" s="14" t="str">
+        <f>IF(MIN(Class_0!I49,Class_1!I49,Class_2!I49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M102" s="14" t="str">
+        <f>IF(MIN(Class_0!J49,Class_1!J49,Class_2!J49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N102" s="14" t="str">
+        <f>IF(MIN(Class_0!K49,Class_1!K49,Class_2!K49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O102" s="14" t="str">
+        <f>IF(MIN(Class_0!L49,Class_1!L49,Class_2!L49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P102" s="14" t="str">
+        <f>IF(MIN(Class_0!M49,Class_1!M49,Class_2!M49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q102" s="14" t="str">
+        <f>IF(MIN(Class_0!N49,Class_1!N49,Class_2!N49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R102" s="14" t="str">
+        <f>IF(MIN(Class_0!O49,Class_1!O49,Class_2!O49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S102" s="14" t="str">
+        <f>IF(MIN(Class_0!P49,Class_1!P49,Class_2!P49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T102" s="14" t="str">
+        <f>IF(MIN(Class_0!Q49,Class_1!Q49,Class_2!Q49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U102" s="14" t="str">
+        <f>IF(MIN(Class_0!R49,Class_1!R49,Class_2!R49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V102" s="14" t="str">
+        <f>IF(MIN(Class_0!S49,Class_1!S49,Class_2!S49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W102" s="14" t="str">
+        <f>IF(MIN(Class_0!T49,Class_1!T49,Class_2!T49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X102" s="14" t="str">
+        <f>IF(MIN(Class_0!U49,Class_1!U49,Class_2!U49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y102" s="14" t="str">
+        <f>IF(MIN(Class_0!V49,Class_1!V49,Class_2!V49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z102" s="14" t="str">
+        <f>IF(MIN(Class_0!W49,Class_1!W49,Class_2!W49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA102" s="14" t="str">
+        <f>IF(MIN(Class_0!X49,Class_1!X49,Class_2!X49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB102" s="14" t="str">
+        <f>IF(MIN(Class_0!Y49,Class_1!Y49,Class_2!Y49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC102" s="14" t="str">
+        <f>IF(MIN(Class_0!Z49,Class_1!Z49,Class_2!Z49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD102" s="14" t="str">
+        <f>IF(MIN(Class_0!AA49,Class_1!AA49,Class_2!AA49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE102" s="14" t="str">
+        <f>IF(MIN(Class_0!AB49,Class_1!AB49,Class_2!AB49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF102" s="14" t="str">
+        <f>IF(MIN(Class_0!AC49,Class_1!AC49,Class_2!AC49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG102" s="14" t="str">
+        <f>IF(MIN(Class_0!AD49,Class_1!AD49,Class_2!AD49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH102" s="14" t="str">
+        <f>IF(MIN(Class_0!AE49,Class_1!AE49,Class_2!AE49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI102" s="14" t="str">
+        <f>IF(MIN(Class_0!AF49,Class_1!AF49,Class_2!AF49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ102" s="14" t="str">
+        <f>IF(MIN(Class_0!AG49,Class_1!AG49,Class_2!AG49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK102" s="14" t="str">
+        <f>IF(MIN(Class_0!AH49,Class_1!AH49,Class_2!AH49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL102" s="14" t="str">
+        <f>IF(MIN(Class_0!AI49,Class_1!AI49,Class_2!AI49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM102" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ49,Class_1!AJ49,Class_2!AJ49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN102" s="14" t="str">
+        <f>IF(MIN(Class_0!AK49,Class_1!AK49,Class_2!AK49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO102" s="14" t="str">
+        <f>IF(MIN(Class_0!AL49,Class_1!AL49,Class_2!AL49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP102" s="14" t="str">
+        <f>IF(MIN(Class_0!AM49,Class_1!AM49,Class_2!AM49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ102" s="14" t="str">
+        <f>IF(MIN(Class_0!AN49,Class_1!AN49,Class_2!AN49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR102" s="14" t="str">
+        <f>IF(MIN(Class_0!AO49,Class_1!AO49,Class_2!AO49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS102" s="14" t="str">
+        <f>IF(MIN(Class_0!AP49,Class_1!AP49,Class_2!AP49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT102" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ49,Class_1!AQ49,Class_2!AQ49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU102" s="14" t="str">
+        <f>IF(MIN(Class_0!AR49,Class_1!AR49,Class_2!AR49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV102" s="14" t="str">
+        <f>IF(MIN(Class_0!AS49,Class_1!AS49,Class_2!AS49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW102" s="14" t="str">
+        <f>IF(MIN(Class_0!AT49,Class_1!AT49,Class_2!AT49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX102" s="14" t="str">
+        <f>IF(MIN(Class_0!AU49,Class_1!AU49,Class_2!AU49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY102" s="14" t="str">
+        <f>IF(MIN(Class_0!AV49,Class_1!AV49,Class_2!AV49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ102" s="14" t="str">
+        <f>IF(MIN(Class_0!AW49,Class_1!AW49,Class_2!AW49) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA102" s="14"/>
+      <c r="BB102" s="14"/>
+      <c r="BC102" s="14"/>
+      <c r="BD102" s="14"/>
+      <c r="BE102" s="14"/>
+      <c r="BF102" s="15"/>
+    </row>
+    <row r="103" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C103" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D103" s="10">
+        <f t="shared" si="6"/>
+        <v>49</v>
+      </c>
+      <c r="E103" s="14" t="str">
+        <f>IF(MIN(Class_0!B50,Class_1!B50,Class_2!B50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F103" s="14" t="str">
+        <f>IF(MIN(Class_0!C50,Class_1!C50,Class_2!C50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G103" s="14" t="str">
+        <f>IF(MIN(Class_0!D50,Class_1!D50,Class_2!D50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H103" s="14" t="str">
+        <f>IF(MIN(Class_0!E50,Class_1!E50,Class_2!E50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I103" s="14" t="str">
+        <f>IF(MIN(Class_0!F50,Class_1!F50,Class_2!F50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J103" s="14" t="str">
+        <f>IF(MIN(Class_0!G50,Class_1!G50,Class_2!G50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K103" s="14" t="str">
+        <f>IF(MIN(Class_0!H50,Class_1!H50,Class_2!H50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L103" s="14" t="str">
+        <f>IF(MIN(Class_0!I50,Class_1!I50,Class_2!I50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M103" s="14" t="str">
+        <f>IF(MIN(Class_0!J50,Class_1!J50,Class_2!J50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N103" s="14" t="str">
+        <f>IF(MIN(Class_0!K50,Class_1!K50,Class_2!K50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O103" s="14" t="str">
+        <f>IF(MIN(Class_0!L50,Class_1!L50,Class_2!L50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P103" s="14" t="str">
+        <f>IF(MIN(Class_0!M50,Class_1!M50,Class_2!M50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q103" s="14" t="str">
+        <f>IF(MIN(Class_0!N50,Class_1!N50,Class_2!N50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R103" s="14" t="str">
+        <f>IF(MIN(Class_0!O50,Class_1!O50,Class_2!O50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S103" s="14" t="str">
+        <f>IF(MIN(Class_0!P50,Class_1!P50,Class_2!P50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="T103" s="14" t="str">
+        <f>IF(MIN(Class_0!Q50,Class_1!Q50,Class_2!Q50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U103" s="14" t="str">
+        <f>IF(MIN(Class_0!R50,Class_1!R50,Class_2!R50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V103" s="14" t="str">
+        <f>IF(MIN(Class_0!S50,Class_1!S50,Class_2!S50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W103" s="14" t="str">
+        <f>IF(MIN(Class_0!T50,Class_1!T50,Class_2!T50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X103" s="14" t="str">
+        <f>IF(MIN(Class_0!U50,Class_1!U50,Class_2!U50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y103" s="14" t="str">
+        <f>IF(MIN(Class_0!V50,Class_1!V50,Class_2!V50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z103" s="14" t="str">
+        <f>IF(MIN(Class_0!W50,Class_1!W50,Class_2!W50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA103" s="14" t="str">
+        <f>IF(MIN(Class_0!X50,Class_1!X50,Class_2!X50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB103" s="14" t="str">
+        <f>IF(MIN(Class_0!Y50,Class_1!Y50,Class_2!Y50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC103" s="14" t="str">
+        <f>IF(MIN(Class_0!Z50,Class_1!Z50,Class_2!Z50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD103" s="14" t="str">
+        <f>IF(MIN(Class_0!AA50,Class_1!AA50,Class_2!AA50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE103" s="14" t="str">
+        <f>IF(MIN(Class_0!AB50,Class_1!AB50,Class_2!AB50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF103" s="14" t="str">
+        <f>IF(MIN(Class_0!AC50,Class_1!AC50,Class_2!AC50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG103" s="14" t="str">
+        <f>IF(MIN(Class_0!AD50,Class_1!AD50,Class_2!AD50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH103" s="14" t="str">
+        <f>IF(MIN(Class_0!AE50,Class_1!AE50,Class_2!AE50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI103" s="14" t="str">
+        <f>IF(MIN(Class_0!AF50,Class_1!AF50,Class_2!AF50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ103" s="14" t="str">
+        <f>IF(MIN(Class_0!AG50,Class_1!AG50,Class_2!AG50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK103" s="14" t="str">
+        <f>IF(MIN(Class_0!AH50,Class_1!AH50,Class_2!AH50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL103" s="14" t="str">
+        <f>IF(MIN(Class_0!AI50,Class_1!AI50,Class_2!AI50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM103" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ50,Class_1!AJ50,Class_2!AJ50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN103" s="14" t="str">
+        <f>IF(MIN(Class_0!AK50,Class_1!AK50,Class_2!AK50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO103" s="14" t="str">
+        <f>IF(MIN(Class_0!AL50,Class_1!AL50,Class_2!AL50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP103" s="14" t="str">
+        <f>IF(MIN(Class_0!AM50,Class_1!AM50,Class_2!AM50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ103" s="14" t="str">
+        <f>IF(MIN(Class_0!AN50,Class_1!AN50,Class_2!AN50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR103" s="14" t="str">
+        <f>IF(MIN(Class_0!AO50,Class_1!AO50,Class_2!AO50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS103" s="14" t="str">
+        <f>IF(MIN(Class_0!AP50,Class_1!AP50,Class_2!AP50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT103" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ50,Class_1!AQ50,Class_2!AQ50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU103" s="14" t="str">
+        <f>IF(MIN(Class_0!AR50,Class_1!AR50,Class_2!AR50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV103" s="14" t="str">
+        <f>IF(MIN(Class_0!AS50,Class_1!AS50,Class_2!AS50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW103" s="14" t="str">
+        <f>IF(MIN(Class_0!AT50,Class_1!AT50,Class_2!AT50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX103" s="14" t="str">
+        <f>IF(MIN(Class_0!AU50,Class_1!AU50,Class_2!AU50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY103" s="14" t="str">
+        <f>IF(MIN(Class_0!AV50,Class_1!AV50,Class_2!AV50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ103" s="14" t="str">
+        <f>IF(MIN(Class_0!AW50,Class_1!AW50,Class_2!AW50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA103" s="14" t="str">
+        <f>IF(MIN(Class_0!AX50,Class_1!AX50,Class_2!AX50) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB103" s="14"/>
+      <c r="BC103" s="14"/>
+      <c r="BD103" s="14"/>
+      <c r="BE103" s="14"/>
+      <c r="BF103" s="15"/>
+    </row>
+    <row r="104" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C104" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D104" s="10">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="E104" s="14" t="str">
+        <f>IF(MIN(Class_0!B51,Class_1!B51,Class_2!B51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F104" s="14" t="str">
+        <f>IF(MIN(Class_0!C51,Class_1!C51,Class_2!C51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G104" s="14" t="str">
+        <f>IF(MIN(Class_0!D51,Class_1!D51,Class_2!D51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H104" s="14" t="str">
+        <f>IF(MIN(Class_0!E51,Class_1!E51,Class_2!E51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I104" s="14" t="str">
+        <f>IF(MIN(Class_0!F51,Class_1!F51,Class_2!F51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J104" s="14" t="str">
+        <f>IF(MIN(Class_0!G51,Class_1!G51,Class_2!G51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K104" s="14" t="str">
+        <f>IF(MIN(Class_0!H51,Class_1!H51,Class_2!H51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L104" s="14" t="str">
+        <f>IF(MIN(Class_0!I51,Class_1!I51,Class_2!I51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M104" s="14" t="str">
+        <f>IF(MIN(Class_0!J51,Class_1!J51,Class_2!J51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="N104" s="14" t="str">
+        <f>IF(MIN(Class_0!K51,Class_1!K51,Class_2!K51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O104" s="14" t="str">
+        <f>IF(MIN(Class_0!L51,Class_1!L51,Class_2!L51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P104" s="14" t="str">
+        <f>IF(MIN(Class_0!M51,Class_1!M51,Class_2!M51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q104" s="14" t="str">
+        <f>IF(MIN(Class_0!N51,Class_1!N51,Class_2!N51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R104" s="14" t="str">
+        <f>IF(MIN(Class_0!O51,Class_1!O51,Class_2!O51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S104" s="14" t="str">
+        <f>IF(MIN(Class_0!P51,Class_1!P51,Class_2!P51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T104" s="14" t="str">
+        <f>IF(MIN(Class_0!Q51,Class_1!Q51,Class_2!Q51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U104" s="14" t="str">
+        <f>IF(MIN(Class_0!R51,Class_1!R51,Class_2!R51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V104" s="14" t="str">
+        <f>IF(MIN(Class_0!S51,Class_1!S51,Class_2!S51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W104" s="14" t="str">
+        <f>IF(MIN(Class_0!T51,Class_1!T51,Class_2!T51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="X104" s="14" t="str">
+        <f>IF(MIN(Class_0!U51,Class_1!U51,Class_2!U51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y104" s="14" t="str">
+        <f>IF(MIN(Class_0!V51,Class_1!V51,Class_2!V51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z104" s="14" t="str">
+        <f>IF(MIN(Class_0!W51,Class_1!W51,Class_2!W51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA104" s="14" t="str">
+        <f>IF(MIN(Class_0!X51,Class_1!X51,Class_2!X51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB104" s="14" t="str">
+        <f>IF(MIN(Class_0!Y51,Class_1!Y51,Class_2!Y51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC104" s="14" t="str">
+        <f>IF(MIN(Class_0!Z51,Class_1!Z51,Class_2!Z51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD104" s="14" t="str">
+        <f>IF(MIN(Class_0!AA51,Class_1!AA51,Class_2!AA51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE104" s="14" t="str">
+        <f>IF(MIN(Class_0!AB51,Class_1!AB51,Class_2!AB51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF104" s="14" t="str">
+        <f>IF(MIN(Class_0!AC51,Class_1!AC51,Class_2!AC51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG104" s="14" t="str">
+        <f>IF(MIN(Class_0!AD51,Class_1!AD51,Class_2!AD51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH104" s="14" t="str">
+        <f>IF(MIN(Class_0!AE51,Class_1!AE51,Class_2!AE51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI104" s="14" t="str">
+        <f>IF(MIN(Class_0!AF51,Class_1!AF51,Class_2!AF51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ104" s="14" t="str">
+        <f>IF(MIN(Class_0!AG51,Class_1!AG51,Class_2!AG51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK104" s="14" t="str">
+        <f>IF(MIN(Class_0!AH51,Class_1!AH51,Class_2!AH51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL104" s="14" t="str">
+        <f>IF(MIN(Class_0!AI51,Class_1!AI51,Class_2!AI51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM104" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ51,Class_1!AJ51,Class_2!AJ51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN104" s="14" t="str">
+        <f>IF(MIN(Class_0!AK51,Class_1!AK51,Class_2!AK51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO104" s="14" t="str">
+        <f>IF(MIN(Class_0!AL51,Class_1!AL51,Class_2!AL51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP104" s="14" t="str">
+        <f>IF(MIN(Class_0!AM51,Class_1!AM51,Class_2!AM51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ104" s="14" t="str">
+        <f>IF(MIN(Class_0!AN51,Class_1!AN51,Class_2!AN51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR104" s="14" t="str">
+        <f>IF(MIN(Class_0!AO51,Class_1!AO51,Class_2!AO51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS104" s="14" t="str">
+        <f>IF(MIN(Class_0!AP51,Class_1!AP51,Class_2!AP51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT104" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ51,Class_1!AQ51,Class_2!AQ51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU104" s="14" t="str">
+        <f>IF(MIN(Class_0!AR51,Class_1!AR51,Class_2!AR51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV104" s="14" t="str">
+        <f>IF(MIN(Class_0!AS51,Class_1!AS51,Class_2!AS51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW104" s="14" t="str">
+        <f>IF(MIN(Class_0!AT51,Class_1!AT51,Class_2!AT51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX104" s="14" t="str">
+        <f>IF(MIN(Class_0!AU51,Class_1!AU51,Class_2!AU51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY104" s="14" t="str">
+        <f>IF(MIN(Class_0!AV51,Class_1!AV51,Class_2!AV51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ104" s="14" t="str">
+        <f>IF(MIN(Class_0!AW51,Class_1!AW51,Class_2!AW51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA104" s="14" t="str">
+        <f>IF(MIN(Class_0!AX51,Class_1!AX51,Class_2!AX51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB104" s="14" t="str">
+        <f>IF(MIN(Class_0!AY51,Class_1!AY51,Class_2!AY51) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC104" s="14"/>
+      <c r="BD104" s="14"/>
+      <c r="BE104" s="14"/>
+      <c r="BF104" s="15"/>
+    </row>
+    <row r="105" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C105" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D105" s="10">
+        <f t="shared" si="6"/>
+        <v>51</v>
+      </c>
+      <c r="E105" s="14" t="str">
+        <f>IF(MIN(Class_0!B52,Class_1!B52,Class_2!B52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="F105" s="14" t="str">
+        <f>IF(MIN(Class_0!C52,Class_1!C52,Class_2!C52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G105" s="14" t="str">
+        <f>IF(MIN(Class_0!D52,Class_1!D52,Class_2!D52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H105" s="14" t="str">
+        <f>IF(MIN(Class_0!E52,Class_1!E52,Class_2!E52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I105" s="14" t="str">
+        <f>IF(MIN(Class_0!F52,Class_1!F52,Class_2!F52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J105" s="14" t="str">
+        <f>IF(MIN(Class_0!G52,Class_1!G52,Class_2!G52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K105" s="14" t="str">
+        <f>IF(MIN(Class_0!H52,Class_1!H52,Class_2!H52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L105" s="14" t="str">
+        <f>IF(MIN(Class_0!I52,Class_1!I52,Class_2!I52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M105" s="14" t="str">
+        <f>IF(MIN(Class_0!J52,Class_1!J52,Class_2!J52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N105" s="14" t="str">
+        <f>IF(MIN(Class_0!K52,Class_1!K52,Class_2!K52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O105" s="14" t="str">
+        <f>IF(MIN(Class_0!L52,Class_1!L52,Class_2!L52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P105" s="14" t="str">
+        <f>IF(MIN(Class_0!M52,Class_1!M52,Class_2!M52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q105" s="14" t="str">
+        <f>IF(MIN(Class_0!N52,Class_1!N52,Class_2!N52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R105" s="14" t="str">
+        <f>IF(MIN(Class_0!O52,Class_1!O52,Class_2!O52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S105" s="14" t="str">
+        <f>IF(MIN(Class_0!P52,Class_1!P52,Class_2!P52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T105" s="14" t="str">
+        <f>IF(MIN(Class_0!Q52,Class_1!Q52,Class_2!Q52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="U105" s="14" t="str">
+        <f>IF(MIN(Class_0!R52,Class_1!R52,Class_2!R52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V105" s="14" t="str">
+        <f>IF(MIN(Class_0!S52,Class_1!S52,Class_2!S52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W105" s="14" t="str">
+        <f>IF(MIN(Class_0!T52,Class_1!T52,Class_2!T52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X105" s="14" t="str">
+        <f>IF(MIN(Class_0!U52,Class_1!U52,Class_2!U52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y105" s="14" t="str">
+        <f>IF(MIN(Class_0!V52,Class_1!V52,Class_2!V52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z105" s="14" t="str">
+        <f>IF(MIN(Class_0!W52,Class_1!W52,Class_2!W52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA105" s="14" t="str">
+        <f>IF(MIN(Class_0!X52,Class_1!X52,Class_2!X52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB105" s="14" t="str">
+        <f>IF(MIN(Class_0!Y52,Class_1!Y52,Class_2!Y52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC105" s="14" t="str">
+        <f>IF(MIN(Class_0!Z52,Class_1!Z52,Class_2!Z52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD105" s="14" t="str">
+        <f>IF(MIN(Class_0!AA52,Class_1!AA52,Class_2!AA52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE105" s="14" t="str">
+        <f>IF(MIN(Class_0!AB52,Class_1!AB52,Class_2!AB52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF105" s="14" t="str">
+        <f>IF(MIN(Class_0!AC52,Class_1!AC52,Class_2!AC52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG105" s="14" t="str">
+        <f>IF(MIN(Class_0!AD52,Class_1!AD52,Class_2!AD52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH105" s="14" t="str">
+        <f>IF(MIN(Class_0!AE52,Class_1!AE52,Class_2!AE52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI105" s="14" t="str">
+        <f>IF(MIN(Class_0!AF52,Class_1!AF52,Class_2!AF52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ105" s="14" t="str">
+        <f>IF(MIN(Class_0!AG52,Class_1!AG52,Class_2!AG52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK105" s="14" t="str">
+        <f>IF(MIN(Class_0!AH52,Class_1!AH52,Class_2!AH52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL105" s="14" t="str">
+        <f>IF(MIN(Class_0!AI52,Class_1!AI52,Class_2!AI52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM105" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ52,Class_1!AJ52,Class_2!AJ52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN105" s="14" t="str">
+        <f>IF(MIN(Class_0!AK52,Class_1!AK52,Class_2!AK52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO105" s="14" t="str">
+        <f>IF(MIN(Class_0!AL52,Class_1!AL52,Class_2!AL52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP105" s="14" t="str">
+        <f>IF(MIN(Class_0!AM52,Class_1!AM52,Class_2!AM52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ105" s="14" t="str">
+        <f>IF(MIN(Class_0!AN52,Class_1!AN52,Class_2!AN52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR105" s="14" t="str">
+        <f>IF(MIN(Class_0!AO52,Class_1!AO52,Class_2!AO52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS105" s="14" t="str">
+        <f>IF(MIN(Class_0!AP52,Class_1!AP52,Class_2!AP52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT105" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ52,Class_1!AQ52,Class_2!AQ52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU105" s="14" t="str">
+        <f>IF(MIN(Class_0!AR52,Class_1!AR52,Class_2!AR52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV105" s="14" t="str">
+        <f>IF(MIN(Class_0!AS52,Class_1!AS52,Class_2!AS52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW105" s="14" t="str">
+        <f>IF(MIN(Class_0!AT52,Class_1!AT52,Class_2!AT52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX105" s="14" t="str">
+        <f>IF(MIN(Class_0!AU52,Class_1!AU52,Class_2!AU52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY105" s="14" t="str">
+        <f>IF(MIN(Class_0!AV52,Class_1!AV52,Class_2!AV52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ105" s="14" t="str">
+        <f>IF(MIN(Class_0!AW52,Class_1!AW52,Class_2!AW52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA105" s="14" t="str">
+        <f>IF(MIN(Class_0!AX52,Class_1!AX52,Class_2!AX52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB105" s="14" t="str">
+        <f>IF(MIN(Class_0!AY52,Class_1!AY52,Class_2!AY52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC105" s="14" t="str">
+        <f>IF(MIN(Class_0!AZ52,Class_1!AZ52,Class_2!AZ52) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD105" s="14"/>
+      <c r="BE105" s="14"/>
+      <c r="BF105" s="15"/>
+    </row>
+    <row r="106" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C106" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D106" s="10">
+        <f t="shared" si="6"/>
+        <v>52</v>
+      </c>
+      <c r="E106" s="14" t="str">
+        <f>IF(MIN(Class_0!B53,Class_1!B53,Class_2!B53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F106" s="14" t="str">
+        <f>IF(MIN(Class_0!C53,Class_1!C53,Class_2!C53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G106" s="14" t="str">
+        <f>IF(MIN(Class_0!D53,Class_1!D53,Class_2!D53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H106" s="14" t="str">
+        <f>IF(MIN(Class_0!E53,Class_1!E53,Class_2!E53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I106" s="14" t="str">
+        <f>IF(MIN(Class_0!F53,Class_1!F53,Class_2!F53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J106" s="14" t="str">
+        <f>IF(MIN(Class_0!G53,Class_1!G53,Class_2!G53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K106" s="14" t="str">
+        <f>IF(MIN(Class_0!H53,Class_1!H53,Class_2!H53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L106" s="14" t="str">
+        <f>IF(MIN(Class_0!I53,Class_1!I53,Class_2!I53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M106" s="14" t="str">
+        <f>IF(MIN(Class_0!J53,Class_1!J53,Class_2!J53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N106" s="14" t="str">
+        <f>IF(MIN(Class_0!K53,Class_1!K53,Class_2!K53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O106" s="14" t="str">
+        <f>IF(MIN(Class_0!L53,Class_1!L53,Class_2!L53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P106" s="14" t="str">
+        <f>IF(MIN(Class_0!M53,Class_1!M53,Class_2!M53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q106" s="14" t="str">
+        <f>IF(MIN(Class_0!N53,Class_1!N53,Class_2!N53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R106" s="14" t="str">
+        <f>IF(MIN(Class_0!O53,Class_1!O53,Class_2!O53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S106" s="14" t="str">
+        <f>IF(MIN(Class_0!P53,Class_1!P53,Class_2!P53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T106" s="14" t="str">
+        <f>IF(MIN(Class_0!Q53,Class_1!Q53,Class_2!Q53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U106" s="14" t="str">
+        <f>IF(MIN(Class_0!R53,Class_1!R53,Class_2!R53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V106" s="14" t="str">
+        <f>IF(MIN(Class_0!S53,Class_1!S53,Class_2!S53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="W106" s="14" t="str">
+        <f>IF(MIN(Class_0!T53,Class_1!T53,Class_2!T53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X106" s="14" t="str">
+        <f>IF(MIN(Class_0!U53,Class_1!U53,Class_2!U53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y106" s="14" t="str">
+        <f>IF(MIN(Class_0!V53,Class_1!V53,Class_2!V53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z106" s="14" t="str">
+        <f>IF(MIN(Class_0!W53,Class_1!W53,Class_2!W53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA106" s="14" t="str">
+        <f>IF(MIN(Class_0!X53,Class_1!X53,Class_2!X53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB106" s="14" t="str">
+        <f>IF(MIN(Class_0!Y53,Class_1!Y53,Class_2!Y53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC106" s="14" t="str">
+        <f>IF(MIN(Class_0!Z53,Class_1!Z53,Class_2!Z53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD106" s="14" t="str">
+        <f>IF(MIN(Class_0!AA53,Class_1!AA53,Class_2!AA53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE106" s="14" t="str">
+        <f>IF(MIN(Class_0!AB53,Class_1!AB53,Class_2!AB53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF106" s="14" t="str">
+        <f>IF(MIN(Class_0!AC53,Class_1!AC53,Class_2!AC53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG106" s="14" t="str">
+        <f>IF(MIN(Class_0!AD53,Class_1!AD53,Class_2!AD53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH106" s="14" t="str">
+        <f>IF(MIN(Class_0!AE53,Class_1!AE53,Class_2!AE53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI106" s="14" t="str">
+        <f>IF(MIN(Class_0!AF53,Class_1!AF53,Class_2!AF53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ106" s="14" t="str">
+        <f>IF(MIN(Class_0!AG53,Class_1!AG53,Class_2!AG53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK106" s="14" t="str">
+        <f>IF(MIN(Class_0!AH53,Class_1!AH53,Class_2!AH53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL106" s="14" t="str">
+        <f>IF(MIN(Class_0!AI53,Class_1!AI53,Class_2!AI53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM106" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ53,Class_1!AJ53,Class_2!AJ53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN106" s="14" t="str">
+        <f>IF(MIN(Class_0!AK53,Class_1!AK53,Class_2!AK53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO106" s="14" t="str">
+        <f>IF(MIN(Class_0!AL53,Class_1!AL53,Class_2!AL53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP106" s="14" t="str">
+        <f>IF(MIN(Class_0!AM53,Class_1!AM53,Class_2!AM53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ106" s="14" t="str">
+        <f>IF(MIN(Class_0!AN53,Class_1!AN53,Class_2!AN53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR106" s="14" t="str">
+        <f>IF(MIN(Class_0!AO53,Class_1!AO53,Class_2!AO53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS106" s="14" t="str">
+        <f>IF(MIN(Class_0!AP53,Class_1!AP53,Class_2!AP53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT106" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ53,Class_1!AQ53,Class_2!AQ53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU106" s="14" t="str">
+        <f>IF(MIN(Class_0!AR53,Class_1!AR53,Class_2!AR53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV106" s="14" t="str">
+        <f>IF(MIN(Class_0!AS53,Class_1!AS53,Class_2!AS53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW106" s="14" t="str">
+        <f>IF(MIN(Class_0!AT53,Class_1!AT53,Class_2!AT53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX106" s="14" t="str">
+        <f>IF(MIN(Class_0!AU53,Class_1!AU53,Class_2!AU53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY106" s="14" t="str">
+        <f>IF(MIN(Class_0!AV53,Class_1!AV53,Class_2!AV53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ106" s="14" t="str">
+        <f>IF(MIN(Class_0!AW53,Class_1!AW53,Class_2!AW53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA106" s="14" t="str">
+        <f>IF(MIN(Class_0!AX53,Class_1!AX53,Class_2!AX53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB106" s="14" t="str">
+        <f>IF(MIN(Class_0!AY53,Class_1!AY53,Class_2!AY53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC106" s="14" t="str">
+        <f>IF(MIN(Class_0!AZ53,Class_1!AZ53,Class_2!AZ53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD106" s="14" t="str">
+        <f>IF(MIN(Class_0!BA53,Class_1!BA53,Class_2!BA53) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE106" s="14"/>
+      <c r="BF106" s="15"/>
+    </row>
+    <row r="107" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="C107" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D107" s="10">
+        <f t="shared" si="6"/>
+        <v>53</v>
+      </c>
+      <c r="E107" s="14" t="str">
+        <f>IF(MIN(Class_0!B54,Class_1!B54,Class_2!B54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F107" s="14" t="str">
+        <f>IF(MIN(Class_0!C54,Class_1!C54,Class_2!C54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G107" s="14" t="str">
+        <f>IF(MIN(Class_0!D54,Class_1!D54,Class_2!D54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H107" s="14" t="str">
+        <f>IF(MIN(Class_0!E54,Class_1!E54,Class_2!E54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I107" s="14" t="str">
+        <f>IF(MIN(Class_0!F54,Class_1!F54,Class_2!F54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J107" s="14" t="str">
+        <f>IF(MIN(Class_0!G54,Class_1!G54,Class_2!G54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K107" s="14" t="str">
+        <f>IF(MIN(Class_0!H54,Class_1!H54,Class_2!H54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L107" s="14" t="str">
+        <f>IF(MIN(Class_0!I54,Class_1!I54,Class_2!I54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="M107" s="14" t="str">
+        <f>IF(MIN(Class_0!J54,Class_1!J54,Class_2!J54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N107" s="14" t="str">
+        <f>IF(MIN(Class_0!K54,Class_1!K54,Class_2!K54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O107" s="14" t="str">
+        <f>IF(MIN(Class_0!L54,Class_1!L54,Class_2!L54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P107" s="14" t="str">
+        <f>IF(MIN(Class_0!M54,Class_1!M54,Class_2!M54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q107" s="14" t="str">
+        <f>IF(MIN(Class_0!N54,Class_1!N54,Class_2!N54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R107" s="14" t="str">
+        <f>IF(MIN(Class_0!O54,Class_1!O54,Class_2!O54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="S107" s="14" t="str">
+        <f>IF(MIN(Class_0!P54,Class_1!P54,Class_2!P54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T107" s="14" t="str">
+        <f>IF(MIN(Class_0!Q54,Class_1!Q54,Class_2!Q54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U107" s="14" t="str">
+        <f>IF(MIN(Class_0!R54,Class_1!R54,Class_2!R54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="V107" s="14" t="str">
+        <f>IF(MIN(Class_0!S54,Class_1!S54,Class_2!S54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W107" s="14" t="str">
+        <f>IF(MIN(Class_0!T54,Class_1!T54,Class_2!T54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X107" s="14" t="str">
+        <f>IF(MIN(Class_0!U54,Class_1!U54,Class_2!U54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Y107" s="14" t="str">
+        <f>IF(MIN(Class_0!V54,Class_1!V54,Class_2!V54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Z107" s="14" t="str">
+        <f>IF(MIN(Class_0!W54,Class_1!W54,Class_2!W54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA107" s="14" t="str">
+        <f>IF(MIN(Class_0!X54,Class_1!X54,Class_2!X54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB107" s="14" t="str">
+        <f>IF(MIN(Class_0!Y54,Class_1!Y54,Class_2!Y54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC107" s="14" t="str">
+        <f>IF(MIN(Class_0!Z54,Class_1!Z54,Class_2!Z54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD107" s="14" t="str">
+        <f>IF(MIN(Class_0!AA54,Class_1!AA54,Class_2!AA54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE107" s="14" t="str">
+        <f>IF(MIN(Class_0!AB54,Class_1!AB54,Class_2!AB54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF107" s="14" t="str">
+        <f>IF(MIN(Class_0!AC54,Class_1!AC54,Class_2!AC54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG107" s="14" t="str">
+        <f>IF(MIN(Class_0!AD54,Class_1!AD54,Class_2!AD54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH107" s="14" t="str">
+        <f>IF(MIN(Class_0!AE54,Class_1!AE54,Class_2!AE54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI107" s="14" t="str">
+        <f>IF(MIN(Class_0!AF54,Class_1!AF54,Class_2!AF54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ107" s="14" t="str">
+        <f>IF(MIN(Class_0!AG54,Class_1!AG54,Class_2!AG54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK107" s="14" t="str">
+        <f>IF(MIN(Class_0!AH54,Class_1!AH54,Class_2!AH54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL107" s="14" t="str">
+        <f>IF(MIN(Class_0!AI54,Class_1!AI54,Class_2!AI54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM107" s="14" t="str">
+        <f>IF(MIN(Class_0!AJ54,Class_1!AJ54,Class_2!AJ54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN107" s="14" t="str">
+        <f>IF(MIN(Class_0!AK54,Class_1!AK54,Class_2!AK54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO107" s="14" t="str">
+        <f>IF(MIN(Class_0!AL54,Class_1!AL54,Class_2!AL54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP107" s="14" t="str">
+        <f>IF(MIN(Class_0!AM54,Class_1!AM54,Class_2!AM54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ107" s="14" t="str">
+        <f>IF(MIN(Class_0!AN54,Class_1!AN54,Class_2!AN54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR107" s="14" t="str">
+        <f>IF(MIN(Class_0!AO54,Class_1!AO54,Class_2!AO54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS107" s="14" t="str">
+        <f>IF(MIN(Class_0!AP54,Class_1!AP54,Class_2!AP54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT107" s="14" t="str">
+        <f>IF(MIN(Class_0!AQ54,Class_1!AQ54,Class_2!AQ54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU107" s="14" t="str">
+        <f>IF(MIN(Class_0!AR54,Class_1!AR54,Class_2!AR54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV107" s="14" t="str">
+        <f>IF(MIN(Class_0!AS54,Class_1!AS54,Class_2!AS54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW107" s="14" t="str">
+        <f>IF(MIN(Class_0!AT54,Class_1!AT54,Class_2!AT54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX107" s="14" t="str">
+        <f>IF(MIN(Class_0!AU54,Class_1!AU54,Class_2!AU54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY107" s="14" t="str">
+        <f>IF(MIN(Class_0!AV54,Class_1!AV54,Class_2!AV54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ107" s="14" t="str">
+        <f>IF(MIN(Class_0!AW54,Class_1!AW54,Class_2!AW54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA107" s="14" t="str">
+        <f>IF(MIN(Class_0!AX54,Class_1!AX54,Class_2!AX54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB107" s="14" t="str">
+        <f>IF(MIN(Class_0!AY54,Class_1!AY54,Class_2!AY54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC107" s="14" t="str">
+        <f>IF(MIN(Class_0!AZ54,Class_1!AZ54,Class_2!AZ54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD107" s="14" t="str">
+        <f>IF(MIN(Class_0!BA54,Class_1!BA54,Class_2!BA54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE107" s="14" t="str">
+        <f>IF(MIN(Class_0!BB54,Class_1!BB54,Class_2!BB54) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF107" s="15"/>
+    </row>
+    <row r="108" spans="3:58" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C108" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D108" s="17">
+        <f t="shared" si="6"/>
+        <v>54</v>
+      </c>
+      <c r="E108" s="18" t="str">
+        <f>IF(MIN(Class_0!B55,Class_1!B55,Class_2!B55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="F108" s="18" t="str">
+        <f>IF(MIN(Class_0!C55,Class_1!C55,Class_2!C55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="G108" s="18" t="str">
+        <f>IF(MIN(Class_0!D55,Class_1!D55,Class_2!D55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="H108" s="18" t="str">
+        <f>IF(MIN(Class_0!E55,Class_1!E55,Class_2!E55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="I108" s="18" t="str">
+        <f>IF(MIN(Class_0!F55,Class_1!F55,Class_2!F55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="J108" s="18" t="str">
+        <f>IF(MIN(Class_0!G55,Class_1!G55,Class_2!G55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="K108" s="18" t="str">
+        <f>IF(MIN(Class_0!H55,Class_1!H55,Class_2!H55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="L108" s="18" t="str">
+        <f>IF(MIN(Class_0!I55,Class_1!I55,Class_2!I55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="M108" s="18" t="str">
+        <f>IF(MIN(Class_0!J55,Class_1!J55,Class_2!J55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="N108" s="18" t="str">
+        <f>IF(MIN(Class_0!K55,Class_1!K55,Class_2!K55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="O108" s="18" t="str">
+        <f>IF(MIN(Class_0!L55,Class_1!L55,Class_2!L55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="P108" s="18" t="str">
+        <f>IF(MIN(Class_0!M55,Class_1!M55,Class_2!M55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Q108" s="18" t="str">
+        <f>IF(MIN(Class_0!N55,Class_1!N55,Class_2!N55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="R108" s="18" t="str">
+        <f>IF(MIN(Class_0!O55,Class_1!O55,Class_2!O55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="S108" s="18" t="str">
+        <f>IF(MIN(Class_0!P55,Class_1!P55,Class_2!P55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="T108" s="18" t="str">
+        <f>IF(MIN(Class_0!Q55,Class_1!Q55,Class_2!Q55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="U108" s="18" t="str">
+        <f>IF(MIN(Class_0!R55,Class_1!R55,Class_2!R55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="V108" s="18" t="str">
+        <f>IF(MIN(Class_0!S55,Class_1!S55,Class_2!S55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="W108" s="18" t="str">
+        <f>IF(MIN(Class_0!T55,Class_1!T55,Class_2!T55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="X108" s="18" t="str">
+        <f>IF(MIN(Class_0!U55,Class_1!U55,Class_2!U55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="Y108" s="18" t="str">
+        <f>IF(MIN(Class_0!V55,Class_1!V55,Class_2!V55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="Z108" s="18" t="str">
+        <f>IF(MIN(Class_0!W55,Class_1!W55,Class_2!W55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA108" s="18" t="str">
+        <f>IF(MIN(Class_0!X55,Class_1!X55,Class_2!X55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB108" s="18" t="str">
+        <f>IF(MIN(Class_0!Y55,Class_1!Y55,Class_2!Y55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AC108" s="18" t="str">
+        <f>IF(MIN(Class_0!Z55,Class_1!Z55,Class_2!Z55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD108" s="18" t="str">
+        <f>IF(MIN(Class_0!AA55,Class_1!AA55,Class_2!AA55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE108" s="18" t="str">
+        <f>IF(MIN(Class_0!AB55,Class_1!AB55,Class_2!AB55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF108" s="18" t="str">
+        <f>IF(MIN(Class_0!AC55,Class_1!AC55,Class_2!AC55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG108" s="18" t="str">
+        <f>IF(MIN(Class_0!AD55,Class_1!AD55,Class_2!AD55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH108" s="18" t="str">
+        <f>IF(MIN(Class_0!AE55,Class_1!AE55,Class_2!AE55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI108" s="18" t="str">
+        <f>IF(MIN(Class_0!AF55,Class_1!AF55,Class_2!AF55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ108" s="18" t="str">
+        <f>IF(MIN(Class_0!AG55,Class_1!AG55,Class_2!AG55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK108" s="18" t="str">
+        <f>IF(MIN(Class_0!AH55,Class_1!AH55,Class_2!AH55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL108" s="18" t="str">
+        <f>IF(MIN(Class_0!AI55,Class_1!AI55,Class_2!AI55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM108" s="18" t="str">
+        <f>IF(MIN(Class_0!AJ55,Class_1!AJ55,Class_2!AJ55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN108" s="18" t="str">
+        <f>IF(MIN(Class_0!AK55,Class_1!AK55,Class_2!AK55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO108" s="18" t="str">
+        <f>IF(MIN(Class_0!AL55,Class_1!AL55,Class_2!AL55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP108" s="18" t="str">
+        <f>IF(MIN(Class_0!AM55,Class_1!AM55,Class_2!AM55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ108" s="18" t="str">
+        <f>IF(MIN(Class_0!AN55,Class_1!AN55,Class_2!AN55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR108" s="18" t="str">
+        <f>IF(MIN(Class_0!AO55,Class_1!AO55,Class_2!AO55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS108" s="18" t="str">
+        <f>IF(MIN(Class_0!AP55,Class_1!AP55,Class_2!AP55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT108" s="18" t="str">
+        <f>IF(MIN(Class_0!AQ55,Class_1!AQ55,Class_2!AQ55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU108" s="18" t="str">
+        <f>IF(MIN(Class_0!AR55,Class_1!AR55,Class_2!AR55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV108" s="18" t="str">
+        <f>IF(MIN(Class_0!AS55,Class_1!AS55,Class_2!AS55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW108" s="18" t="str">
+        <f>IF(MIN(Class_0!AT55,Class_1!AT55,Class_2!AT55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX108" s="18" t="str">
+        <f>IF(MIN(Class_0!AU55,Class_1!AU55,Class_2!AU55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY108" s="18" t="str">
+        <f>IF(MIN(Class_0!AV55,Class_1!AV55,Class_2!AV55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ108" s="18" t="str">
+        <f>IF(MIN(Class_0!AW55,Class_1!AW55,Class_2!AW55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA108" s="18" t="str">
+        <f>IF(MIN(Class_0!AX55,Class_1!AX55,Class_2!AX55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB108" s="18" t="str">
+        <f>IF(MIN(Class_0!AY55,Class_1!AY55,Class_2!AY55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC108" s="18" t="str">
+        <f>IF(MIN(Class_0!AZ55,Class_1!AZ55,Class_2!AZ55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD108" s="18" t="str">
+        <f>IF(MIN(Class_0!BA55,Class_1!BA55,Class_2!BA55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE108" s="18" t="str">
+        <f>IF(MIN(Class_0!BB55,Class_1!BB55,Class_2!BB55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF108" s="19" t="str">
+        <f>IF(MIN(Class_0!BC55,Class_1!BC55,Class_2!BC55) &gt;0, CHAR(43), CHAR(45))</f>
+        <v>+</v>
+      </c>
+    </row>
+    <row r="109" spans="3:58" x14ac:dyDescent="0.35">
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
+      <c r="R109" s="3"/>
+      <c r="S109" s="3"/>
+      <c r="T109" s="3"/>
+      <c r="U109" s="3"/>
+      <c r="V109" s="3"/>
+      <c r="W109" s="3"/>
+      <c r="X109" s="3"/>
+      <c r="Y109" s="3"/>
+      <c r="Z109" s="3"/>
+      <c r="AA109" s="3"/>
+      <c r="AB109" s="3"/>
+      <c r="AC109" s="3"/>
+      <c r="AD109" s="3"/>
+      <c r="AE109" s="3"/>
+      <c r="AF109" s="3"/>
+      <c r="AG109" s="3"/>
+      <c r="AH109" s="3"/>
+      <c r="AI109" s="3"/>
+      <c r="AJ109" s="3"/>
+      <c r="AK109" s="3"/>
+      <c r="AL109" s="3"/>
+      <c r="AM109" s="3"/>
+      <c r="AN109" s="3"/>
+      <c r="AO109" s="3"/>
+      <c r="AP109" s="3"/>
+      <c r="AQ109" s="3"/>
+      <c r="AR109" s="3"/>
+      <c r="AS109" s="3"/>
+      <c r="AT109" s="3"/>
+      <c r="AU109" s="3"/>
+      <c r="AV109" s="3"/>
+      <c r="AW109" s="3"/>
+      <c r="AX109" s="3"/>
+      <c r="AY109" s="3"/>
+      <c r="AZ109" s="3"/>
+      <c r="BA109" s="3"/>
+      <c r="BB109" s="3"/>
+      <c r="BC109" s="3"/>
+      <c r="BD109" s="3"/>
+      <c r="BE109" s="3"/>
+      <c r="BF109" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:BB6">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:BB7">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:BB9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E56:BF109">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"+"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
